--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,35 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5924E58-E528-4150-BA2D-E2A4072A6ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A6AA3A-1486-46C9-87C0-54CF5F023E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
-    <sheet name="неизменные" sheetId="2" r:id="rId2"/>
+    <sheet name="Составные" sheetId="3" r:id="rId2"/>
+    <sheet name="простые" sheetId="4" r:id="rId3"/>
+    <sheet name="неизменные" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -65,6 +64,234 @@
   </si>
   <si>
     <t>Имеющиеся средства либо не подходили, либо были в недостаточном количестве, либо их просто было</t>
+  </si>
+  <si>
+    <t>лучшая импровизация именно та, которую</t>
+  </si>
+  <si>
+    <t>лучшее произвведение искусства именно то, которое</t>
+  </si>
+  <si>
+    <t>грифы, находящихся там документов</t>
+  </si>
+  <si>
+    <t>уровни тайн, находящихся там документов</t>
+  </si>
+  <si>
+    <t>Измайловском комплексе</t>
+  </si>
+  <si>
+    <t>Измайловском учреждении</t>
+  </si>
+  <si>
+    <t>Кстати о комплексе</t>
+  </si>
+  <si>
+    <t>Кстати о учреждении</t>
+  </si>
+  <si>
+    <t>Дисциплина была</t>
+  </si>
+  <si>
+    <t>Свод правил был</t>
+  </si>
+  <si>
+    <t>дисциплина!</t>
+  </si>
+  <si>
+    <t>обязательное соблюдение правил!</t>
+  </si>
+  <si>
+    <t>а дисциплина из железной перешла в рамки репрессивной</t>
+  </si>
+  <si>
+    <t>а железное соблюдение правил перешло в рамки угнетения</t>
+  </si>
+  <si>
+    <t>ни одна хорошо разработанная схема, как бы жестко ее ни приводили в жизнь, как бы скрупулёзно ее</t>
+  </si>
+  <si>
+    <t>разработанный чертёж, как бы жёстко его ни приводили в жизнь, как бы тщательно за ним не следили</t>
+  </si>
+  <si>
+    <t>констатируюсь отбросом</t>
+  </si>
+  <si>
+    <t>являюсь отбросом</t>
+  </si>
+  <si>
+    <t>главшпаном этой уже организованной структуры</t>
+  </si>
+  <si>
+    <t>вожаком этой уже собранной дружины</t>
+  </si>
+  <si>
+    <t>ошарашенные ждали команды</t>
+  </si>
+  <si>
+    <t>ошарашенные ждали приказа</t>
+  </si>
+  <si>
+    <t>в командах под руководством</t>
+  </si>
+  <si>
+    <t>в отрядах под руководством</t>
+  </si>
+  <si>
+    <t>до выстрела последовала команда</t>
+  </si>
+  <si>
+    <t>до выстрела последовал приказ</t>
+  </si>
+  <si>
+    <t>имея такую команду и все</t>
+  </si>
+  <si>
+    <t>имея такой отряд и все</t>
+  </si>
+  <si>
+    <t>одной из его команд</t>
+  </si>
+  <si>
+    <t>одним из его отрядов</t>
+  </si>
+  <si>
+    <t>команду надзора меняют</t>
+  </si>
+  <si>
+    <t>отряд надзора меняют</t>
+  </si>
+  <si>
+    <t>с разными «командами»</t>
+  </si>
+  <si>
+    <t>с разными «отрядами»</t>
+  </si>
+  <si>
+    <t>«бригадами»</t>
+  </si>
+  <si>
+    <t>«дружинами»</t>
+  </si>
+  <si>
+    <t>причитающуюся моей команде</t>
+  </si>
+  <si>
+    <t>причитающуюся моему отряду</t>
+  </si>
+  <si>
+    <t>ответ его команда без</t>
+  </si>
+  <si>
+    <t>ответ его приказа без</t>
+  </si>
+  <si>
+    <t>собрали свои команды</t>
+  </si>
+  <si>
+    <t>собрали свои отряды</t>
+  </si>
+  <si>
+    <t>спортивных команд</t>
+  </si>
+  <si>
+    <t>спортивных содружеств</t>
+  </si>
+  <si>
+    <t>спортивная команда</t>
+  </si>
+  <si>
+    <t>спортивное содружество</t>
+  </si>
+  <si>
+    <t>команда у него была неслабая</t>
+  </si>
+  <si>
+    <t>отряд у него был неслабый</t>
+  </si>
+  <si>
+    <t>в свою команду я</t>
+  </si>
+  <si>
+    <t>в свой отряд я</t>
+  </si>
+  <si>
+    <t>что команды от него</t>
+  </si>
+  <si>
+    <t>что приказа от него</t>
+  </si>
+  <si>
+    <t>Только команды ждёт</t>
+  </si>
+  <si>
+    <t>Только приказа ждёт</t>
+  </si>
+  <si>
+    <t>делили одну команду</t>
+  </si>
+  <si>
+    <t>делили одно содружество</t>
+  </si>
+  <si>
+    <t>Часть бывшей команды</t>
+  </si>
+  <si>
+    <t>Часть бывшего содружества</t>
+  </si>
+  <si>
+    <t>дружественных «команд»</t>
+  </si>
+  <si>
+    <t>дружественных «отрядов»</t>
+  </si>
+  <si>
+    <t>меня без формы</t>
+  </si>
+  <si>
+    <t>меня без военного одеяния</t>
+  </si>
+  <si>
+    <t>официальной версии</t>
+  </si>
+  <si>
+    <t>обнародованной вести</t>
+  </si>
+  <si>
+    <t>ЧОП оформлялся</t>
+  </si>
+  <si>
+    <t>ЧОП узаканивался</t>
+  </si>
+  <si>
+    <t>только оформлялся</t>
+  </si>
+  <si>
+    <t>только узаканивался</t>
+  </si>
+  <si>
+    <t>лелеемую еврейскими банкирами тему</t>
+  </si>
+  <si>
+    <t>лелеемый еврейскими банкирами вопрос</t>
+  </si>
+  <si>
+    <t>был оформлен паспорт</t>
+  </si>
+  <si>
+    <t>был указан паспорт</t>
+  </si>
+  <si>
+    <t>оформленной всевозможными документами</t>
+  </si>
+  <si>
+    <t>узаконенной всевозможными письменными свидетельствами</t>
+  </si>
+  <si>
+    <t>«бригадам» структурами</t>
+  </si>
+  <si>
+    <t>«дружинам» преступным сообществам</t>
   </si>
 </sst>
 </file>
@@ -107,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -115,6 +342,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -395,13 +623,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="48.15234375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -409,7 +637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -417,7 +645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -425,12 +653,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -439,15 +675,70 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="62.69140625" customWidth="1"/>
+    <col min="1" max="1" width="62.7265625" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -455,12 +746,276 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A6AA3A-1486-46C9-87C0-54CF5F023E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F8B1B6-B855-4205-B019-1DFADAB7C712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -88,12 +88,6 @@
   </si>
   <si>
     <t>Кстати о учреждении</t>
-  </si>
-  <si>
-    <t>Дисциплина была</t>
-  </si>
-  <si>
-    <t>Свод правил был</t>
   </si>
   <si>
     <t>дисциплина!</t>
@@ -690,20 +684,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-    </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -718,10 +704,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -772,250 +758,250 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F8B1B6-B855-4205-B019-1DFADAB7C712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D96486-AC21-4631-9E47-E69321AD3FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="129">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -286,6 +289,135 @@
   </si>
   <si>
     <t>«дружинам» преступным сообществам</t>
+  </si>
+  <si>
+    <t>новой субкультуры, отголоски которой</t>
+  </si>
+  <si>
+    <t>нового общественного течения, отголоски которого</t>
+  </si>
+  <si>
+    <t>кучей номеров и</t>
+  </si>
+  <si>
+    <t>кучей палат и</t>
+  </si>
+  <si>
+    <t>пять номеров,</t>
+  </si>
+  <si>
+    <t>пять палат,</t>
+  </si>
+  <si>
+    <t>сидя в номере</t>
+  </si>
+  <si>
+    <t>сидя в палате</t>
+  </si>
+  <si>
+    <t>что до номера им</t>
+  </si>
+  <si>
+    <t>что до палаты им</t>
+  </si>
+  <si>
+    <t>кем-то оплаченные номера</t>
+  </si>
+  <si>
+    <t>кем-то оплаченные палаты</t>
+  </si>
+  <si>
+    <t>уплывали в номера</t>
+  </si>
+  <si>
+    <t>уплывали в палаты</t>
+  </si>
+  <si>
+    <t>из номера в коридор</t>
+  </si>
+  <si>
+    <t>из палаты в коридор</t>
+  </si>
+  <si>
+    <t>Из номера приходилось</t>
+  </si>
+  <si>
+    <t>Из палаты приходилось</t>
+  </si>
+  <si>
+    <t>номер, снимаемый</t>
+  </si>
+  <si>
+    <t>палату, снимаемую</t>
+  </si>
+  <si>
+    <t>психики – она архинормальна, архистабильна, хотя и вся расшатана</t>
+  </si>
+  <si>
+    <t>разум – она крайне обычен, крайне безотказен, хотя и весь расшатан</t>
+  </si>
+  <si>
+    <t>приносили положительные моменты</t>
+  </si>
+  <si>
+    <t>приносили положительные чувства</t>
+  </si>
+  <si>
+    <t>пару каких-то</t>
+  </si>
+  <si>
+    <t>несколько каких-то</t>
+  </si>
+  <si>
+    <t>пару магнитофонов</t>
+  </si>
+  <si>
+    <t>несколько магнитофонов</t>
+  </si>
+  <si>
+    <t>пару представляли</t>
+  </si>
+  <si>
+    <t>семью представляли</t>
+  </si>
+  <si>
+    <t>пару «длинных»</t>
+  </si>
+  <si>
+    <t>несколько «длинных»</t>
+  </si>
+  <si>
+    <t>жаркому пару</t>
+  </si>
+  <si>
+    <t>пару «точек»</t>
+  </si>
+  <si>
+    <t>несколько «точек»</t>
+  </si>
+  <si>
+    <t>отработанная легенда заурчала</t>
+  </si>
+  <si>
+    <t>отработанный рассказ с целью внедрения заурчал</t>
+  </si>
+  <si>
+    <t>счастливо выглядевшей пары</t>
+  </si>
+  <si>
+    <t>счастливо выглядевшей семьи</t>
+  </si>
+  <si>
+    <t>дружественной бригадой</t>
+  </si>
+  <si>
+    <t>дружественным отрядом</t>
+  </si>
+  <si>
+    <t>Картина на удивление мерзка,</t>
+  </si>
+  <si>
+    <t>Зрелище на удивление мерзко,</t>
   </si>
 </sst>
 </file>
@@ -618,12 +750,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.15625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,7 +763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -639,7 +771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -647,7 +779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -655,7 +787,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -671,12 +803,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="26.08984375" customWidth="1"/>
+    <col min="1" max="1" width="26.05078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -684,7 +816,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -700,9 +832,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -717,14 +849,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B57"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="62.7265625" customWidth="1"/>
+    <col min="1" max="1" width="62.68359375" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -732,7 +864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -740,7 +872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -748,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -756,7 +888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -764,7 +896,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -772,7 +904,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -780,7 +912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -788,7 +920,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -796,7 +928,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -804,7 +936,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -812,7 +944,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -820,7 +952,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -828,7 +960,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -836,7 +968,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -844,7 +976,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -852,7 +992,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -860,7 +1000,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -868,7 +1008,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -876,7 +1016,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -884,7 +1024,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -892,7 +1032,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -900,7 +1040,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -908,7 +1048,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -916,7 +1056,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -924,7 +1064,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -932,7 +1072,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -940,7 +1080,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -948,7 +1088,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
         <v>72</v>
       </c>
@@ -956,7 +1096,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -964,7 +1104,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -972,7 +1112,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -980,7 +1120,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -988,7 +1128,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -996,12 +1136,180 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>84</v>
       </c>
       <c r="B36" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>102</v>
+      </c>
+      <c r="B44" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>119</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D96486-AC21-4631-9E47-E69321AD3FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB056C5E-709C-436C-9256-F6AE365F37E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
     <sheet name="Составные" sheetId="3" r:id="rId2"/>
     <sheet name="простые" sheetId="4" r:id="rId3"/>
     <sheet name="неизменные" sheetId="2" r:id="rId4"/>
+    <sheet name="неизменные_длинные" sheetId="5" r:id="rId5"/>
+    <sheet name="неизменные_короткие" sheetId="7" r:id="rId6"/>
+    <sheet name="ошибки" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="160">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -418,6 +421,99 @@
   </si>
   <si>
     <t>Зрелище на удивление мерзко,</t>
+  </si>
+  <si>
+    <t>выехавший на операцию</t>
+  </si>
+  <si>
+    <t>выехавший на захват</t>
+  </si>
+  <si>
+    <t>обговоренная фраза из уст Олега, которая</t>
+  </si>
+  <si>
+    <t>обговоренное выражение из уст Олега, которое</t>
+  </si>
+  <si>
+    <t>экономическое конгломераты</t>
+  </si>
+  <si>
+    <t>Картина на удивление мерзка, но показательна</t>
+  </si>
+  <si>
+    <t>Зрелище на удивление мерзко, но показательно</t>
+  </si>
+  <si>
+    <t>«командами» и «бригадами»</t>
+  </si>
+  <si>
+    <t>«отрядами» и «дружинами»</t>
+  </si>
+  <si>
+    <t>перспективный, здоровый генофонд</t>
+  </si>
+  <si>
+    <t>многообещающая, здоровая родовая наследственность</t>
+  </si>
+  <si>
+    <t>в подобных компаниях</t>
+  </si>
+  <si>
+    <t>в подобных общностях</t>
+  </si>
+  <si>
+    <t>Компания была тёплая</t>
+  </si>
+  <si>
+    <t>Общность была тёплая</t>
+  </si>
+  <si>
+    <t>то в редких компаниях</t>
+  </si>
+  <si>
+    <t>то в редких общностях</t>
+  </si>
+  <si>
+    <t>Грише и компании</t>
+  </si>
+  <si>
+    <t>Грише и дружине</t>
+  </si>
+  <si>
+    <t>в их компании</t>
+  </si>
+  <si>
+    <t>в их кругу</t>
+  </si>
+  <si>
+    <t>от теперешней компании</t>
+  </si>
+  <si>
+    <t>от теперешнего круга</t>
+  </si>
+  <si>
+    <t>присутствие в их компании нужно</t>
+  </si>
+  <si>
+    <t>присутствие в их общности нужно</t>
+  </si>
+  <si>
+    <t>в компании ещё нескольких</t>
+  </si>
+  <si>
+    <t>в кругу ещё нескольких</t>
+  </si>
+  <si>
+    <t>приездами разных компаний</t>
+  </si>
+  <si>
+    <t>приездами разных общностей</t>
+  </si>
+  <si>
+    <t>невозможных компаний, в</t>
+  </si>
+  <si>
+    <t>невозможных общностей, в</t>
   </si>
 </sst>
 </file>
@@ -749,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="48.15625" style="1" customWidth="1"/>
@@ -795,6 +891,62 @@
         <v>19</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -802,10 +954,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="26.05078125" customWidth="1"/>
+    <col min="2" max="2" width="27.68359375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -822,6 +975,38 @@
       </c>
       <c r="B4" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1315,4 +1500,79 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="41.3671875" customWidth="1"/>
+    <col min="2" max="2" width="48.83984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="40.734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.89453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB056C5E-709C-436C-9256-F6AE365F37E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71000450-380B-413E-A4F8-E63DD9DE5852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -26,15 +26,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="166">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -514,6 +511,24 @@
   </si>
   <si>
     <t>невозможных общностей, в</t>
+  </si>
+  <si>
+    <t>Один из денежных хранилищ его знакомых дал согласие</t>
+  </si>
+  <si>
+    <t>Одно из денежных хранилищ его знакомых дало согласие</t>
+  </si>
+  <si>
+    <t>суммой фактического кредита</t>
+  </si>
+  <si>
+    <t>количеством денежных средств взятого долга в рост</t>
+  </si>
+  <si>
+    <t>мягкому, но шумовому фону</t>
+  </si>
+  <si>
+    <t>мягкой, но шумовой обстановке</t>
   </si>
 </sst>
 </file>
@@ -845,13 +860,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="48.15625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -859,7 +874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -867,7 +882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -875,7 +890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -883,7 +898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -891,7 +906,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
@@ -899,7 +914,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -907,7 +922,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -915,7 +930,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>152</v>
       </c>
@@ -923,7 +938,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -931,7 +946,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
@@ -939,12 +954,28 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -955,13 +986,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.05078125" customWidth="1"/>
-    <col min="2" max="2" width="27.68359375" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -969,7 +1000,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -977,7 +1008,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -985,7 +1016,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -993,7 +1024,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -1001,7 +1032,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -1017,9 +1048,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1035,13 +1066,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="62.68359375" customWidth="1"/>
+    <col min="1" max="1" width="62.6328125" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1049,7 +1080,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,7 +1088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1065,7 +1096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1073,7 +1104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1081,7 +1112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1089,7 +1120,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1097,7 +1128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1105,7 +1136,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1113,7 +1144,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1121,7 +1152,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1129,7 +1160,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1137,7 +1168,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1145,7 +1176,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1153,7 +1184,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1161,7 +1192,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -1169,7 +1200,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1177,7 +1208,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1185,7 +1216,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1193,7 +1224,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1201,7 +1232,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1209,7 +1240,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1217,7 +1248,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1225,7 +1256,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1233,7 +1264,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1241,7 +1272,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1249,7 +1280,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1257,7 +1288,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1265,7 +1296,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1273,7 +1304,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>72</v>
       </c>
@@ -1281,7 +1312,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1289,7 +1320,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1297,7 +1328,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -1305,7 +1336,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -1313,7 +1344,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -1321,7 +1352,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -1329,7 +1360,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -1337,7 +1368,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>90</v>
       </c>
@@ -1345,7 +1376,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -1353,7 +1384,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -1361,7 +1392,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -1369,7 +1400,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -1377,7 +1408,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>100</v>
       </c>
@@ -1385,7 +1416,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>102</v>
       </c>
@@ -1393,7 +1424,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>104</v>
       </c>
@@ -1401,7 +1432,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -1409,7 +1440,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>108</v>
       </c>
@@ -1417,7 +1448,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>110</v>
       </c>
@@ -1425,7 +1456,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>112</v>
       </c>
@@ -1433,7 +1464,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -1441,7 +1472,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>116</v>
       </c>
@@ -1449,7 +1480,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>118</v>
       </c>
@@ -1457,7 +1488,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>119</v>
       </c>
@@ -1465,7 +1496,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>121</v>
       </c>
@@ -1473,7 +1504,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>123</v>
       </c>
@@ -1481,7 +1512,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>125</v>
       </c>
@@ -1489,7 +1520,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>127</v>
       </c>
@@ -1505,13 +1536,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.3671875" customWidth="1"/>
-    <col min="2" max="2" width="48.83984375" customWidth="1"/>
+    <col min="1" max="1" width="41.36328125" customWidth="1"/>
+    <col min="2" max="2" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -1526,14 +1557,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.89453125" customWidth="1"/>
+    <col min="1" max="1" width="40.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>134</v>
       </c>
@@ -1541,7 +1572,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -1549,12 +1580,20 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>138</v>
       </c>
       <c r="B3" t="s">
         <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -1565,9 +1604,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>133</v>
       </c>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71000450-380B-413E-A4F8-E63DD9DE5852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB782F99-9060-458B-AF7A-4719F2687302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="175">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -529,6 +532,33 @@
   </si>
   <si>
     <t>мягкой, но шумовой обстановке</t>
+  </si>
+  <si>
+    <t>происходить в эфире</t>
+  </si>
+  <si>
+    <t>происходить во время съёмки</t>
+  </si>
+  <si>
+    <t>вежливо поинтересовавшись</t>
+  </si>
+  <si>
+    <t>вежливо спросили</t>
+  </si>
+  <si>
+    <t>больше, поинтересовавшись</t>
+  </si>
+  <si>
+    <t>больше, спросив</t>
+  </si>
+  <si>
+    <t>у меня интересуются</t>
+  </si>
+  <si>
+    <t>у меня спрашивают</t>
+  </si>
+  <si>
+    <t>товсь</t>
   </si>
 </sst>
 </file>
@@ -860,13 +890,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.15625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -874,7 +904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -882,7 +912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -890,7 +920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -898,7 +928,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -906,7 +936,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
@@ -914,7 +944,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -922,7 +952,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -930,7 +960,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>152</v>
       </c>
@@ -938,7 +968,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -946,7 +976,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
@@ -954,7 +984,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>158</v>
       </c>
@@ -962,7 +992,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>162</v>
       </c>
@@ -970,12 +1000,28 @@
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -985,14 +1031,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="26.08984375" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" customWidth="1"/>
+    <col min="1" max="1" width="26.1015625" customWidth="1"/>
+    <col min="2" max="2" width="27.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1000,7 +1046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1008,7 +1054,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -1016,7 +1062,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -1024,7 +1070,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -1032,12 +1078,28 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>148</v>
       </c>
       <c r="B8" t="s">
         <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -1048,9 +1110,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1066,13 +1128,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="62.6328125" customWidth="1"/>
+    <col min="1" max="1" width="62.62890625" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1080,7 +1142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1088,7 +1150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1096,7 +1158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1104,7 +1166,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1112,7 +1174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1120,7 +1182,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1128,7 +1190,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1136,7 +1198,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1144,7 +1206,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1152,7 +1214,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1160,7 +1222,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1168,7 +1230,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1176,7 +1238,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1184,7 +1246,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1192,7 +1254,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -1200,7 +1262,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1208,7 +1270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1216,7 +1278,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1224,7 +1286,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1232,7 +1294,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1240,7 +1302,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1248,7 +1310,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1256,7 +1318,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1264,7 +1326,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1272,7 +1334,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1280,7 +1342,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1288,7 +1350,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1296,7 +1358,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1304,7 +1366,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
         <v>72</v>
       </c>
@@ -1312,7 +1374,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1320,7 +1382,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1328,7 +1390,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -1336,7 +1398,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -1344,7 +1406,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -1352,7 +1414,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -1360,7 +1422,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -1368,7 +1430,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>90</v>
       </c>
@@ -1376,7 +1438,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -1384,7 +1446,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -1392,7 +1454,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -1400,7 +1462,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -1408,7 +1470,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>100</v>
       </c>
@@ -1416,7 +1478,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>102</v>
       </c>
@@ -1424,7 +1486,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>104</v>
       </c>
@@ -1432,7 +1494,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -1440,7 +1502,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>108</v>
       </c>
@@ -1448,7 +1510,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3" t="s">
         <v>110</v>
       </c>
@@ -1456,7 +1518,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>112</v>
       </c>
@@ -1464,7 +1526,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -1472,7 +1534,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>116</v>
       </c>
@@ -1480,7 +1542,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>118</v>
       </c>
@@ -1488,7 +1550,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>119</v>
       </c>
@@ -1496,7 +1558,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>121</v>
       </c>
@@ -1504,7 +1566,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>123</v>
       </c>
@@ -1512,7 +1574,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>125</v>
       </c>
@@ -1520,7 +1582,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>127</v>
       </c>
@@ -1536,13 +1598,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="41.36328125" customWidth="1"/>
-    <col min="2" max="2" width="48.81640625" customWidth="1"/>
+    <col min="1" max="1" width="41.3671875" customWidth="1"/>
+    <col min="2" max="2" width="48.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -1558,13 +1620,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="40.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.90625" customWidth="1"/>
+    <col min="1" max="1" width="40.734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>134</v>
       </c>
@@ -1572,7 +1634,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -1580,7 +1642,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -1588,7 +1650,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>160</v>
       </c>
@@ -1603,12 +1665,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="32.41796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB782F99-9060-458B-AF7A-4719F2687302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB9AE43-C633-415C-A98F-9628187BBD39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="222">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -559,6 +559,147 @@
   </si>
   <si>
     <t>товсь</t>
+  </si>
+  <si>
+    <t>нашей «бригады»</t>
+  </si>
+  <si>
+    <t>нашего «отряда»</t>
+  </si>
+  <si>
+    <t>Лёша-Солдат</t>
+  </si>
+  <si>
+    <t>Лёша-Воин</t>
+  </si>
+  <si>
+    <t>«Медведковской» бригады</t>
+  </si>
+  <si>
+    <t>«Медведковского» отряда</t>
+  </si>
+  <si>
+    <t>стоящего и тоже «Медведковского» отряда, по слухам, чувствующего себя гораздо лучше нашего</t>
+  </si>
+  <si>
+    <t>стоящей и тоже «Медведковской» бригады, по слухам, чувствующей себя гораздо лучше нашей</t>
+  </si>
+  <si>
+    <t>одного из корпусов гостиничного</t>
+  </si>
+  <si>
+    <t>одного из зданий гостинничного</t>
+  </si>
+  <si>
+    <t>из указателя здания</t>
+  </si>
+  <si>
+    <t>из номеров корпуса</t>
+  </si>
+  <si>
+    <t>Дмитрий взял на обдумывании</t>
+  </si>
+  <si>
+    <t>планах компании (возглавляемой</t>
+  </si>
+  <si>
+    <t>планах предприятия (возглавляемого</t>
+  </si>
+  <si>
+    <t>это бригаду</t>
+  </si>
+  <si>
+    <t>с тёмным салоном</t>
+  </si>
+  <si>
+    <t>с тёмной торговой точкой</t>
+  </si>
+  <si>
+    <t>решал патрон в цельной оболочке, но вот его-то</t>
+  </si>
+  <si>
+    <t>решала пуля в цельной оболочке, но вот её-то</t>
+  </si>
+  <si>
+    <t>«революция» к тому времени закончилась</t>
+  </si>
+  <si>
+    <t>«мятеж» к тому времени закончился</t>
+  </si>
+  <si>
+    <t>из «бригады»</t>
+  </si>
+  <si>
+    <t>из «отряда»</t>
+  </si>
+  <si>
+    <t>выработка схемы покушения была отложена до момента определения графика появления</t>
+  </si>
+  <si>
+    <t>выработка замысла покушения был отложен до мгновения определения расписания и появляения</t>
+  </si>
+  <si>
+    <t>этот «пресс»</t>
+  </si>
+  <si>
+    <t>эту «раздачу»</t>
+  </si>
+  <si>
+    <t>полегла какая-нибудь группировка</t>
+  </si>
+  <si>
+    <t>полегло какое-нибудь сообщество</t>
+  </si>
+  <si>
+    <t>в бывшем тогда итальянским рестораном</t>
+  </si>
+  <si>
+    <t>в бывшей тогда итальянской харчёвне для дворян</t>
+  </si>
+  <si>
+    <t>новому крёстному отцу,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ремонт был окончен, и меня </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отделка была окончена, и меня </t>
+  </si>
+  <si>
+    <t>мы затеяли ремонт, утеплили</t>
+  </si>
+  <si>
+    <t>мы затеяли отделку, утеплили</t>
+  </si>
+  <si>
+    <t>который делал ремонт в новой квартире</t>
+  </si>
+  <si>
+    <t>который производил отделку в новой квартире</t>
+  </si>
+  <si>
+    <t>вёлся ремонт</t>
+  </si>
+  <si>
+    <t>велась отделка</t>
+  </si>
+  <si>
+    <t>в «курганской» группировке</t>
+  </si>
+  <si>
+    <t>в «курганском» сообществе</t>
+  </si>
+  <si>
+    <t>островов Канарского архипелага</t>
+  </si>
+  <si>
+    <t>островов Канарского материка</t>
+  </si>
+  <si>
+    <t>автомобиль, его на сервис</t>
+  </si>
+  <si>
+    <t>автомобиль, его в службу по починке</t>
   </si>
 </sst>
 </file>
@@ -890,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="48.15625" style="1" customWidth="1"/>
@@ -1024,6 +1165,54 @@
         <v>173</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1031,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="26.1015625" customWidth="1"/>
@@ -1100,6 +1289,14 @@
       </c>
       <c r="B10" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -1127,7 +1324,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="62.62890625" customWidth="1"/>
@@ -1590,6 +1787,38 @@
         <v>128</v>
       </c>
     </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>177</v>
+      </c>
+      <c r="B59" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>197</v>
+      </c>
+      <c r="B61" t="s">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1597,7 +1826,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="41.3671875" customWidth="1"/>
@@ -1612,6 +1841,30 @@
         <v>132</v>
       </c>
     </row>
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" t="s">
+        <v>196</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1619,43 +1872,107 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="40.734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.89453125" customWidth="1"/>
+    <col min="1" max="1" width="40.734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -1665,7 +1982,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="32.41796875" customWidth="1"/>
@@ -1681,6 +1998,21 @@
         <v>174</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>207</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB9AE43-C633-415C-A98F-9628187BBD39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D51A62-BD93-4A5D-A5D2-C92570B1989A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1032,12 +1029,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="48.15625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1045,7 +1042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1053,7 +1050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1061,7 +1058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1069,7 +1066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1077,7 +1074,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
@@ -1085,7 +1082,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -1093,7 +1090,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -1101,7 +1098,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>152</v>
       </c>
@@ -1109,7 +1106,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -1117,7 +1114,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
@@ -1125,7 +1122,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>158</v>
       </c>
@@ -1133,7 +1130,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>162</v>
       </c>
@@ -1141,7 +1138,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
@@ -1149,7 +1146,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>166</v>
       </c>
@@ -1157,7 +1154,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>172</v>
       </c>
@@ -1165,7 +1162,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>183</v>
       </c>
@@ -1173,7 +1170,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>186</v>
       </c>
@@ -1181,7 +1178,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>188</v>
       </c>
@@ -1189,7 +1186,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>191</v>
       </c>
@@ -1197,7 +1194,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>203</v>
       </c>
@@ -1205,7 +1202,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>218</v>
       </c>
@@ -1221,13 +1218,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.1015625" customWidth="1"/>
-    <col min="2" max="2" width="27.62890625" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1235,7 +1232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1243,7 +1240,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -1251,7 +1248,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -1259,7 +1256,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -1267,7 +1264,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -1275,7 +1272,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>168</v>
       </c>
@@ -1283,7 +1280,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>170</v>
       </c>
@@ -1291,7 +1288,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>214</v>
       </c>
@@ -1307,9 +1304,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1325,13 +1322,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
   <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="62.62890625" customWidth="1"/>
+    <col min="1" max="1" width="62.6328125" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1339,7 +1336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1347,7 +1344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1355,7 +1352,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1363,7 +1360,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1371,7 +1368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1379,7 +1376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1387,7 +1384,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1395,7 +1392,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1403,7 +1400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1411,7 +1408,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1419,7 +1416,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1427,7 +1424,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1435,7 +1432,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1443,7 +1440,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1451,7 +1448,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -1459,7 +1456,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1467,7 +1464,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1475,7 +1472,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1483,7 +1480,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1491,7 +1488,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1499,7 +1496,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1507,7 +1504,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1515,7 +1512,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1523,7 +1520,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1531,7 +1528,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1539,7 +1536,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1547,7 +1544,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1555,7 +1552,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1563,7 +1560,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>72</v>
       </c>
@@ -1571,7 +1568,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1579,7 +1576,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1587,7 +1584,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -1595,7 +1592,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -1603,7 +1600,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -1611,7 +1608,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -1619,7 +1616,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -1627,7 +1624,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>90</v>
       </c>
@@ -1635,7 +1632,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -1643,7 +1640,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -1651,7 +1648,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -1659,7 +1656,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -1667,7 +1664,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>100</v>
       </c>
@@ -1675,7 +1672,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>102</v>
       </c>
@@ -1683,7 +1680,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>104</v>
       </c>
@@ -1691,7 +1688,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -1699,7 +1696,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>108</v>
       </c>
@@ -1707,7 +1704,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>110</v>
       </c>
@@ -1715,7 +1712,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>112</v>
       </c>
@@ -1723,7 +1720,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -1731,7 +1728,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>116</v>
       </c>
@@ -1739,7 +1736,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>118</v>
       </c>
@@ -1747,7 +1744,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>119</v>
       </c>
@@ -1755,7 +1752,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>121</v>
       </c>
@@ -1763,7 +1760,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>123</v>
       </c>
@@ -1771,7 +1768,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>125</v>
       </c>
@@ -1779,7 +1776,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>127</v>
       </c>
@@ -1787,7 +1784,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>175</v>
       </c>
@@ -1795,7 +1792,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>177</v>
       </c>
@@ -1803,7 +1800,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>179</v>
       </c>
@@ -1811,7 +1808,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>197</v>
       </c>
@@ -1827,13 +1824,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.3671875" customWidth="1"/>
-    <col min="2" max="2" width="48.7890625" customWidth="1"/>
+    <col min="1" max="1" width="41.36328125" customWidth="1"/>
+    <col min="2" max="2" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -1841,7 +1838,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>182</v>
       </c>
@@ -1849,7 +1846,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>193</v>
       </c>
@@ -1857,7 +1854,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>195</v>
       </c>
@@ -1873,13 +1870,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -1887,7 +1884,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
@@ -1895,7 +1892,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
@@ -1903,7 +1900,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>160</v>
       </c>
@@ -1911,7 +1908,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>199</v>
       </c>
@@ -1919,7 +1916,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>201</v>
       </c>
@@ -1927,7 +1924,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>205</v>
       </c>
@@ -1935,7 +1932,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>208</v>
       </c>
@@ -1943,7 +1940,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>210</v>
       </c>
@@ -1951,7 +1948,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>212</v>
       </c>
@@ -1959,7 +1956,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>216</v>
       </c>
@@ -1967,7 +1964,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>220</v>
       </c>
@@ -1983,32 +1980,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.41796875" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>207</v>
       </c>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D51A62-BD93-4A5D-A5D2-C92570B1989A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E168FEE-3FFF-4A86-89FA-A250C1362FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,16 @@
     <sheet name="неизменные_короткие" sheetId="7" r:id="rId6"/>
     <sheet name="ошибки" sheetId="6" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные_важные!$A$1:$B$22</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1029,12 +1035,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.15625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1042,7 +1048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1050,7 +1056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1058,7 +1064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1066,7 +1072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1074,7 +1080,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
@@ -1082,7 +1088,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -1090,7 +1096,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -1098,7 +1104,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>152</v>
       </c>
@@ -1106,7 +1112,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -1114,7 +1120,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
@@ -1122,7 +1128,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>158</v>
       </c>
@@ -1130,7 +1136,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>162</v>
       </c>
@@ -1138,7 +1144,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
@@ -1146,7 +1152,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>166</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>172</v>
       </c>
@@ -1162,7 +1168,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>183</v>
       </c>
@@ -1170,7 +1176,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>186</v>
       </c>
@@ -1178,7 +1184,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>188</v>
       </c>
@@ -1186,7 +1192,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>191</v>
       </c>
@@ -1194,7 +1200,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>203</v>
       </c>
@@ -1202,7 +1208,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>218</v>
       </c>
@@ -1211,6 +1217,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B22" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1218,13 +1225,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="26.08984375" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" customWidth="1"/>
+    <col min="1" max="1" width="26.1015625" customWidth="1"/>
+    <col min="2" max="2" width="27.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1240,7 +1247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -1248,7 +1255,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -1256,7 +1263,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -1264,7 +1271,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -1272,7 +1279,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>168</v>
       </c>
@@ -1280,7 +1287,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>170</v>
       </c>
@@ -1288,7 +1295,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>214</v>
       </c>
@@ -1304,9 +1311,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1322,13 +1329,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
   <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="62.6328125" customWidth="1"/>
+    <col min="1" max="1" width="62.62890625" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1336,7 +1343,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1344,7 +1351,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1352,7 +1359,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1360,7 +1367,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1368,7 +1375,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1376,7 +1383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1384,7 +1391,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1392,7 +1399,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1400,7 +1407,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1408,7 +1415,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1416,7 +1423,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1424,7 +1431,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1432,7 +1439,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1440,7 +1447,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1448,7 +1455,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -1456,7 +1463,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1464,7 +1471,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1472,7 +1479,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1480,7 +1487,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1488,7 +1495,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1496,7 +1503,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1504,7 +1511,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1512,7 +1519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1520,7 +1527,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1528,7 +1535,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1536,7 +1543,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1544,7 +1551,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1552,7 +1559,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1560,7 +1567,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3" t="s">
         <v>72</v>
       </c>
@@ -1568,7 +1575,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1576,7 +1583,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1584,7 +1591,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -1592,7 +1599,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -1600,7 +1607,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -1608,7 +1615,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -1616,7 +1623,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -1624,7 +1631,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>90</v>
       </c>
@@ -1632,7 +1639,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -1640,7 +1647,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -1648,7 +1655,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -1656,7 +1663,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -1664,7 +1671,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>100</v>
       </c>
@@ -1672,7 +1679,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>102</v>
       </c>
@@ -1680,7 +1687,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>104</v>
       </c>
@@ -1688,7 +1695,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -1696,7 +1703,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>108</v>
       </c>
@@ -1704,7 +1711,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="3" t="s">
         <v>110</v>
       </c>
@@ -1712,7 +1719,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>112</v>
       </c>
@@ -1720,7 +1727,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -1728,7 +1735,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>116</v>
       </c>
@@ -1736,7 +1743,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>118</v>
       </c>
@@ -1744,7 +1751,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>119</v>
       </c>
@@ -1752,7 +1759,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>121</v>
       </c>
@@ -1760,7 +1767,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>123</v>
       </c>
@@ -1768,7 +1775,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>125</v>
       </c>
@@ -1776,7 +1783,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>127</v>
       </c>
@@ -1784,7 +1791,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>175</v>
       </c>
@@ -1792,7 +1799,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>177</v>
       </c>
@@ -1800,7 +1807,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>179</v>
       </c>
@@ -1808,7 +1815,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>197</v>
       </c>
@@ -1824,13 +1831,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="41.36328125" customWidth="1"/>
-    <col min="2" max="2" width="48.81640625" customWidth="1"/>
+    <col min="1" max="1" width="41.3671875" customWidth="1"/>
+    <col min="2" max="2" width="48.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -1838,7 +1845,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>182</v>
       </c>
@@ -1846,7 +1853,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>193</v>
       </c>
@@ -1854,7 +1861,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>195</v>
       </c>
@@ -1870,13 +1877,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="40.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.90625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -1884,7 +1891,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
@@ -1892,7 +1899,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
@@ -1900,7 +1907,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>160</v>
       </c>
@@ -1908,7 +1915,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>199</v>
       </c>
@@ -1916,7 +1923,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>201</v>
       </c>
@@ -1924,7 +1931,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>205</v>
       </c>
@@ -1932,7 +1939,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>208</v>
       </c>
@@ -1940,7 +1947,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>210</v>
       </c>
@@ -1948,7 +1955,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>212</v>
       </c>
@@ -1956,7 +1963,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>216</v>
       </c>
@@ -1964,7 +1971,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>220</v>
       </c>
@@ -1980,32 +1987,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="32.453125" customWidth="1"/>
+    <col min="1" max="1" width="32.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>207</v>
       </c>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E168FEE-3FFF-4A86-89FA-A250C1362FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A25E38D-22C9-4E3C-A00D-3A75FCFE84E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="255">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -561,9 +561,6 @@
     <t>у меня спрашивают</t>
   </si>
   <si>
-    <t>товсь</t>
-  </si>
-  <si>
     <t>нашей «бригады»</t>
   </si>
   <si>
@@ -703,6 +700,108 @@
   </si>
   <si>
     <t>автомобиль, его в службу по починке</t>
+  </si>
+  <si>
+    <t>он оперировал супругу</t>
+  </si>
+  <si>
+    <t>он самолично проводил врачебные вмешательства ножом супруге</t>
+  </si>
+  <si>
+    <t>обеих «корпорациях»</t>
+  </si>
+  <si>
+    <t>обоих «предприятиях»</t>
+  </si>
+  <si>
+    <t>интересов, заинтересованность</t>
+  </si>
+  <si>
+    <t>увлечений, одержимость</t>
+  </si>
+  <si>
+    <t>в этой «корпорации»</t>
+  </si>
+  <si>
+    <t>в этом «предприятии»</t>
+  </si>
+  <si>
+    <t>этой «корпорации»</t>
+  </si>
+  <si>
+    <t>этого «предприятия»</t>
+  </si>
+  <si>
+    <t>этой «корпорации», слишком многих из неё</t>
+  </si>
+  <si>
+    <t>этого «предприятия», слишком многих из него</t>
+  </si>
+  <si>
+    <t>массе предложил</t>
+  </si>
+  <si>
+    <t>множеству предложил</t>
+  </si>
+  <si>
+    <t>увлекающаяся натура</t>
+  </si>
+  <si>
+    <t>увлекающийся по природе</t>
+  </si>
+  <si>
+    <t>отдельная тема, вряд ли нужная</t>
+  </si>
+  <si>
+    <t>отдельный вопрос, вряд ли нужный</t>
+  </si>
+  <si>
+    <t>оказался строящийся концертный зал</t>
+  </si>
+  <si>
+    <t>оказались строящиеся хоромы для выступлений</t>
+  </si>
+  <si>
+    <t>с новой «фигурой»</t>
+  </si>
+  <si>
+    <t>с новым «человеком»</t>
+  </si>
+  <si>
+    <t>новый зал, осматривая его</t>
+  </si>
+  <si>
+    <t>новые хоромы, осматривая их</t>
+  </si>
+  <si>
+    <t>о процентах которого я знал чётко одно – их</t>
+  </si>
+  <si>
+    <t>о лихве которого я знал чётко одно – её</t>
+  </si>
+  <si>
+    <t>помогать из процентов, которые даёт эта сумма</t>
+  </si>
+  <si>
+    <t>помогать их лихвы, которую дают этот денежный общак</t>
+  </si>
+  <si>
+    <t xml:space="preserve">трогать эту сумму </t>
+  </si>
+  <si>
+    <t>трогать эти денежные средства</t>
+  </si>
+  <si>
+    <t>Комитетовский банк</t>
+  </si>
+  <si>
+    <t>денежное хранилище Совета</t>
+  </si>
+  <si>
+    <t>готовсь</t>
+  </si>
+  <si>
+    <t>в стойке положения «товсь»</t>
   </si>
 </sst>
 </file>
@@ -1170,50 +1269,50 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -1224,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="26.1015625" customWidth="1"/>
@@ -1297,10 +1396,18 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" t="s">
         <v>214</v>
       </c>
-      <c r="B11" t="s">
-        <v>215</v>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B12" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -1328,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="62.62890625" customWidth="1"/>
@@ -1793,34 +1900,146 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" t="s">
         <v>175</v>
-      </c>
-      <c r="B58" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" t="s">
         <v>177</v>
-      </c>
-      <c r="B59" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" t="s">
         <v>179</v>
-      </c>
-      <c r="B60" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
+        <v>196</v>
+      </c>
+      <c r="B61" t="s">
         <v>197</v>
       </c>
-      <c r="B61" t="s">
-        <v>198</v>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>221</v>
+      </c>
+      <c r="B62" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>223</v>
+      </c>
+      <c r="B63" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>225</v>
+      </c>
+      <c r="B64" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>227</v>
+      </c>
+      <c r="B65" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
+        <v>233</v>
+      </c>
+      <c r="B66" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>235</v>
+      </c>
+      <c r="B67" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" t="s">
+        <v>237</v>
+      </c>
+      <c r="B68" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" t="s">
+        <v>239</v>
+      </c>
+      <c r="B69" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" t="s">
+        <v>241</v>
+      </c>
+      <c r="B70" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" t="s">
+        <v>243</v>
+      </c>
+      <c r="B71" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" t="s">
+        <v>245</v>
+      </c>
+      <c r="B72" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" t="s">
+        <v>247</v>
+      </c>
+      <c r="B73" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" t="s">
+        <v>249</v>
+      </c>
+      <c r="B74" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" t="s">
+        <v>251</v>
+      </c>
+      <c r="B75" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -1847,26 +2066,26 @@
     </row>
     <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" t="s">
         <v>193</v>
-      </c>
-      <c r="B3" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" t="s">
         <v>195</v>
-      </c>
-      <c r="B4" t="s">
-        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -1876,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="40.734375" style="1" bestFit="1" customWidth="1"/>
@@ -1917,66 +2136,74 @@
     </row>
     <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>221</v>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -1986,35 +2213,38 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="32.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+        <v>254</v>
+      </c>
+      <c r="B2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A25E38D-22C9-4E3C-A00D-3A75FCFE84E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594595DE-A744-4503-A64F-435438F7660F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="271">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -802,6 +799,54 @@
   </si>
   <si>
     <t>в стойке положения «товсь»</t>
+  </si>
+  <si>
+    <t>маломощным патроном</t>
+  </si>
+  <si>
+    <t>маломощной пулей</t>
+  </si>
+  <si>
+    <t>низшим структурам</t>
+  </si>
+  <si>
+    <t>низшим учреждениям</t>
+  </si>
+  <si>
+    <t>просто организация была не</t>
+  </si>
+  <si>
+    <t>просто подготовка была не</t>
+  </si>
+  <si>
+    <t>Свое белой</t>
+  </si>
+  <si>
+    <t>Своей белой</t>
+  </si>
+  <si>
+    <t>«оброс» спецификой</t>
+  </si>
+  <si>
+    <t>«оброс» опытом исполнения особых поручений</t>
+  </si>
+  <si>
+    <t>той репрессивной дисциплины, которая властвовала</t>
+  </si>
+  <si>
+    <t>тех угнетающих правил, которые властвовали</t>
+  </si>
+  <si>
+    <t>С ним самими</t>
+  </si>
+  <si>
+    <t>С ним самим</t>
+  </si>
+  <si>
+    <t>дошедшая до них информация</t>
+  </si>
+  <si>
+    <t>дошедшие до них сведения</t>
   </si>
 </sst>
 </file>
@@ -1134,12 +1179,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="48.15625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1147,7 +1192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1155,7 +1200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1163,7 +1208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1171,7 +1216,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1179,7 +1224,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
@@ -1187,7 +1232,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -1195,7 +1240,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -1203,7 +1248,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>152</v>
       </c>
@@ -1211,7 +1256,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -1219,7 +1264,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
@@ -1227,7 +1272,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>158</v>
       </c>
@@ -1235,7 +1280,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>162</v>
       </c>
@@ -1243,7 +1288,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
@@ -1251,7 +1296,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>166</v>
       </c>
@@ -1259,7 +1304,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>172</v>
       </c>
@@ -1267,7 +1312,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>182</v>
       </c>
@@ -1275,7 +1320,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>185</v>
       </c>
@@ -1283,7 +1328,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>187</v>
       </c>
@@ -1291,7 +1336,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>190</v>
       </c>
@@ -1299,7 +1344,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>202</v>
       </c>
@@ -1307,7 +1352,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>217</v>
       </c>
@@ -1323,14 +1368,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.1015625" customWidth="1"/>
-    <col min="2" max="2" width="27.62890625" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1338,7 +1383,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1346,7 +1391,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -1354,7 +1399,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -1362,7 +1407,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -1370,7 +1415,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -1378,7 +1423,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>168</v>
       </c>
@@ -1386,7 +1431,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>170</v>
       </c>
@@ -1394,7 +1439,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>213</v>
       </c>
@@ -1402,12 +1447,28 @@
         <v>214</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>229</v>
       </c>
       <c r="B12" t="s">
         <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>255</v>
+      </c>
+      <c r="B13" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -1418,9 +1479,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1435,14 +1496,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
-  <dimension ref="A1:B75"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B81"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="62.62890625" customWidth="1"/>
+    <col min="1" max="1" width="62.6328125" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1450,7 +1511,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1458,7 +1519,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1466,7 +1527,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1474,7 +1535,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1482,7 +1543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1490,7 +1551,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1498,7 +1559,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1506,7 +1567,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1514,7 +1575,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1522,7 +1583,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1530,7 +1591,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1538,7 +1599,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1546,7 +1607,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1554,7 +1615,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1562,7 +1623,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -1570,7 +1631,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1578,7 +1639,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1586,7 +1647,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1594,7 +1655,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1602,7 +1663,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1610,7 +1671,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1618,7 +1679,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1626,7 +1687,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1634,7 +1695,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1642,7 +1703,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1650,7 +1711,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1658,7 +1719,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1666,7 +1727,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1674,7 +1735,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>72</v>
       </c>
@@ -1682,7 +1743,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1690,7 +1751,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1698,7 +1759,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -1706,7 +1767,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -1714,7 +1775,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -1722,7 +1783,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -1730,7 +1791,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -1738,7 +1799,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>90</v>
       </c>
@@ -1746,7 +1807,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -1754,7 +1815,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -1762,7 +1823,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -1770,7 +1831,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -1778,7 +1839,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>100</v>
       </c>
@@ -1786,7 +1847,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>102</v>
       </c>
@@ -1794,7 +1855,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>104</v>
       </c>
@@ -1802,7 +1863,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -1810,7 +1871,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>108</v>
       </c>
@@ -1818,7 +1879,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>110</v>
       </c>
@@ -1826,7 +1887,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>112</v>
       </c>
@@ -1834,7 +1895,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -1842,7 +1903,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>116</v>
       </c>
@@ -1850,7 +1911,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>118</v>
       </c>
@@ -1858,7 +1919,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>119</v>
       </c>
@@ -1866,7 +1927,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>121</v>
       </c>
@@ -1874,7 +1935,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>123</v>
       </c>
@@ -1882,7 +1943,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>125</v>
       </c>
@@ -1890,7 +1951,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>127</v>
       </c>
@@ -1898,7 +1959,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>174</v>
       </c>
@@ -1906,7 +1967,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>176</v>
       </c>
@@ -1914,7 +1975,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>178</v>
       </c>
@@ -1922,7 +1983,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>196</v>
       </c>
@@ -1930,7 +1991,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>221</v>
       </c>
@@ -1938,7 +1999,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>223</v>
       </c>
@@ -1946,7 +2007,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>225</v>
       </c>
@@ -1954,7 +2015,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>227</v>
       </c>
@@ -1962,7 +2023,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>233</v>
       </c>
@@ -1970,7 +2031,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>235</v>
       </c>
@@ -1978,7 +2039,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>237</v>
       </c>
@@ -1986,7 +2047,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>239</v>
       </c>
@@ -1994,7 +2055,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>241</v>
       </c>
@@ -2002,7 +2063,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>243</v>
       </c>
@@ -2010,7 +2071,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>245</v>
       </c>
@@ -2018,7 +2079,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>247</v>
       </c>
@@ -2026,7 +2087,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>249</v>
       </c>
@@ -2034,12 +2095,60 @@
         <v>250</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>251</v>
       </c>
       <c r="B75" t="s">
         <v>252</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>259</v>
+      </c>
+      <c r="B76" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>116</v>
+      </c>
+      <c r="B77" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>263</v>
+      </c>
+      <c r="B78" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>265</v>
+      </c>
+      <c r="B79" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>196</v>
+      </c>
+      <c r="B80" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>269</v>
+      </c>
+      <c r="B81" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -2050,13 +2159,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.3671875" customWidth="1"/>
-    <col min="2" max="2" width="48.7890625" customWidth="1"/>
+    <col min="1" max="1" width="41.36328125" customWidth="1"/>
+    <col min="2" max="2" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -2064,7 +2173,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>181</v>
       </c>
@@ -2072,7 +2181,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>192</v>
       </c>
@@ -2080,7 +2189,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>194</v>
       </c>
@@ -2096,13 +2205,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -2110,7 +2219,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
@@ -2118,7 +2227,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
@@ -2126,7 +2235,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>160</v>
       </c>
@@ -2134,7 +2243,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>198</v>
       </c>
@@ -2142,7 +2251,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>200</v>
       </c>
@@ -2150,7 +2259,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>204</v>
       </c>
@@ -2158,7 +2267,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>207</v>
       </c>
@@ -2166,7 +2275,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>209</v>
       </c>
@@ -2174,7 +2283,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>211</v>
       </c>
@@ -2182,7 +2291,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>215</v>
       </c>
@@ -2190,7 +2299,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>219</v>
       </c>
@@ -2198,7 +2307,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>231</v>
       </c>
@@ -2213,18 +2322,18 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.47265625" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>254</v>
       </c>
@@ -2232,19 +2341,35 @@
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594595DE-A744-4503-A64F-435438F7660F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5310BDE0-6C79-4878-A78A-BDCE3C3A2970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="271">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -516,9 +519,6 @@
     <t>невозможных общностей, в</t>
   </si>
   <si>
-    <t>Один из денежных хранилищ его знакомых дал согласие</t>
-  </si>
-  <si>
     <t>Одно из денежных хранилищ его знакомых дало согласие</t>
   </si>
   <si>
@@ -847,6 +847,9 @@
   </si>
   <si>
     <t>дошедшие до них сведения</t>
+  </si>
+  <si>
+    <t>Один из банков его знакомых дал согласие</t>
   </si>
 </sst>
 </file>
@@ -1179,12 +1182,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.15625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1200,7 +1203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1208,7 +1211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1216,7 +1219,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1224,7 +1227,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -1248,7 +1251,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>152</v>
       </c>
@@ -1256,7 +1259,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -1264,7 +1267,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
@@ -1272,7 +1275,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>158</v>
       </c>
@@ -1280,84 +1283,84 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -1369,13 +1372,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="26.08984375" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" customWidth="1"/>
+    <col min="1" max="1" width="26.1015625" customWidth="1"/>
+    <col min="2" max="2" width="27.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1383,7 +1386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1391,7 +1394,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -1399,7 +1402,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -1407,7 +1410,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -1415,7 +1418,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -1423,52 +1426,52 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" t="s">
         <v>168</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>170</v>
       </c>
-      <c r="B10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" t="s">
         <v>213</v>
       </c>
-      <c r="B11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" t="s">
         <v>229</v>
       </c>
-      <c r="B12" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" t="s">
         <v>255</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>257</v>
-      </c>
-      <c r="B14" t="s">
-        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -1479,9 +1482,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1497,661 +1500,648 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
   <dimension ref="A1:B81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="62.6328125" customWidth="1"/>
+    <col min="1" max="1" width="62.62890625" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>224</v>
+      </c>
+      <c r="B24" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B30" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B34" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>232</v>
+      </c>
+      <c r="B35" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>173</v>
+      </c>
+      <c r="B37" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>242</v>
+      </c>
+      <c r="B40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>244</v>
+      </c>
+      <c r="B42" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>222</v>
+      </c>
+      <c r="B43" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>238</v>
+      </c>
+      <c r="B45" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>220</v>
+      </c>
+      <c r="B46" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>236</v>
+      </c>
+      <c r="B48" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B52" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>246</v>
+      </c>
+      <c r="B59" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>108</v>
+      </c>
+      <c r="B60" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>258</v>
+      </c>
+      <c r="B62" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>106</v>
+      </c>
+      <c r="B63" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>240</v>
+      </c>
+      <c r="B65" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
         <v>42</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B66" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" t="s">
         <v>50</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B68" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" t="s">
+        <v>54</v>
+      </c>
+      <c r="B69" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" t="s">
         <v>52</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B70" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B71" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" t="s">
+        <v>264</v>
+      </c>
+      <c r="B72" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" t="s">
+        <v>248</v>
+      </c>
+      <c r="B75" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" t="s">
+        <v>234</v>
+      </c>
+      <c r="B76" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" t="s">
+        <v>98</v>
+      </c>
+      <c r="B77" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" t="s">
+        <v>74</v>
+      </c>
+      <c r="B79" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" t="s">
         <v>60</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B81" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>80</v>
-      </c>
-      <c r="B34" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>88</v>
-      </c>
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>90</v>
-      </c>
-      <c r="B38" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>92</v>
-      </c>
-      <c r="B39" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>94</v>
-      </c>
-      <c r="B40" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>98</v>
-      </c>
-      <c r="B42" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>100</v>
-      </c>
-      <c r="B43" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>106</v>
-      </c>
-      <c r="B46" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>116</v>
-      </c>
-      <c r="B51" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>118</v>
-      </c>
-      <c r="B52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>119</v>
-      </c>
-      <c r="B53" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>121</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>123</v>
-      </c>
-      <c r="B55" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>127</v>
-      </c>
-      <c r="B57" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>174</v>
-      </c>
-      <c r="B58" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>176</v>
-      </c>
-      <c r="B59" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>178</v>
-      </c>
-      <c r="B60" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>196</v>
-      </c>
-      <c r="B61" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>221</v>
-      </c>
-      <c r="B62" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>223</v>
-      </c>
-      <c r="B63" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>225</v>
-      </c>
-      <c r="B64" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>227</v>
-      </c>
-      <c r="B65" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>233</v>
-      </c>
-      <c r="B66" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>235</v>
-      </c>
-      <c r="B67" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>237</v>
-      </c>
-      <c r="B68" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>239</v>
-      </c>
-      <c r="B69" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>241</v>
-      </c>
-      <c r="B70" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>243</v>
-      </c>
-      <c r="B71" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>245</v>
-      </c>
-      <c r="B72" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>247</v>
-      </c>
-      <c r="B73" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>249</v>
-      </c>
-      <c r="B74" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>251</v>
-      </c>
-      <c r="B75" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>259</v>
-      </c>
-      <c r="B76" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>116</v>
-      </c>
-      <c r="B77" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>263</v>
-      </c>
-      <c r="B78" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>265</v>
-      </c>
-      <c r="B79" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>196</v>
-      </c>
-      <c r="B80" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>269</v>
-      </c>
-      <c r="B81" t="s">
-        <v>270</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B81">
+    <sortCondition ref="A1:A81"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2159,13 +2149,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="41.36328125" customWidth="1"/>
-    <col min="2" max="2" width="48.81640625" customWidth="1"/>
+    <col min="1" max="1" width="41.3671875" customWidth="1"/>
+    <col min="2" max="2" width="48.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -2173,28 +2163,28 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" t="s">
         <v>192</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>194</v>
-      </c>
-      <c r="B4" t="s">
-        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2205,13 +2195,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="40.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.90625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -2219,7 +2209,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
@@ -2227,7 +2217,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
@@ -2235,84 +2225,84 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2323,53 +2313,53 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="32.453125" customWidth="1"/>
+    <col min="1" max="1" width="32.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B6" t="s">
         <v>261</v>
       </c>
-      <c r="B6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" t="s">
         <v>267</v>
-      </c>
-      <c r="B7" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5310BDE0-6C79-4878-A78A-BDCE3C3A2970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AB9087-7F3D-45CF-9E7C-9F0B8045A46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -1483,6 +1483,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="44.7890625" customWidth="1"/>
+    <col min="2" max="2" width="23.20703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AB9087-7F3D-45CF-9E7C-9F0B8045A46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15393675-1755-4F97-A6A5-CAF623DF3EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-46188" yWindow="-108" windowWidth="46296" windowHeight="25416" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="295">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -850,6 +847,78 @@
   </si>
   <si>
     <t>Один из банков его знакомых дал согласие</t>
+  </si>
+  <si>
+    <t>в забытый кем-то пакет</t>
+  </si>
+  <si>
+    <t>в забытую кем-то посылку</t>
+  </si>
+  <si>
+    <t>в своём личном зале</t>
+  </si>
+  <si>
+    <t>в своих личных хоромах</t>
+  </si>
+  <si>
+    <t>один из известных офисов</t>
+  </si>
+  <si>
+    <t>одно из известных рабочих помещений</t>
+  </si>
+  <si>
+    <t>хорошую и надежную команду</t>
+  </si>
+  <si>
+    <t>хороший и надёжный отряд</t>
+  </si>
+  <si>
+    <t>какой-то спирали, восходящей или нисходящий</t>
+  </si>
+  <si>
+    <t>какого-то завитка, восходящего или нисходящего</t>
+  </si>
+  <si>
+    <t>в философствования, фантазию</t>
+  </si>
+  <si>
+    <t>в обсуждение мировоззрения, воображение</t>
+  </si>
+  <si>
+    <t>в одну из крупнейших на тот период фирм</t>
+  </si>
+  <si>
+    <t>в одно из крупнейших на тот временной промежуток предприятий</t>
+  </si>
+  <si>
+    <t>о небольшом семейном бедствии</t>
+  </si>
+  <si>
+    <t>о небольшой семейной трагедии</t>
+  </si>
+  <si>
+    <t>весь магазин разрядили</t>
+  </si>
+  <si>
+    <t>всю обойму разрядили</t>
+  </si>
+  <si>
+    <t>от своей «бригады»</t>
+  </si>
+  <si>
+    <t>от своего «отряда»</t>
+  </si>
+  <si>
+    <t>мой авторитет в этом плане оказался непререкаемым</t>
+  </si>
+  <si>
+    <t>моя значимость в этом замысле оказалась непререкаемой</t>
+  </si>
+  <si>
+    <t>печатный текст говорил</t>
+  </si>
+  <si>
+    <t>печатная письменность говорила</t>
   </si>
 </sst>
 </file>
@@ -1182,12 +1251,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="48.15625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1195,7 +1264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1203,7 +1272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1211,7 +1280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1219,7 +1288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1227,7 +1296,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
@@ -1235,7 +1304,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -1243,7 +1312,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -1251,7 +1320,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>152</v>
       </c>
@@ -1259,7 +1328,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -1267,7 +1336,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
@@ -1275,7 +1344,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>158</v>
       </c>
@@ -1283,7 +1352,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>161</v>
       </c>
@@ -1291,7 +1360,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>163</v>
       </c>
@@ -1299,7 +1368,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>165</v>
       </c>
@@ -1307,7 +1376,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>171</v>
       </c>
@@ -1315,7 +1384,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>181</v>
       </c>
@@ -1323,7 +1392,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>184</v>
       </c>
@@ -1331,7 +1400,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>186</v>
       </c>
@@ -1339,7 +1408,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>189</v>
       </c>
@@ -1347,7 +1416,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>201</v>
       </c>
@@ -1355,7 +1424,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>216</v>
       </c>
@@ -1372,13 +1441,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.1015625" customWidth="1"/>
-    <col min="2" max="2" width="27.62890625" customWidth="1"/>
+    <col min="1" max="1" width="26.109375" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1386,7 +1455,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1394,7 +1463,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -1402,7 +1471,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -1410,7 +1479,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -1418,7 +1487,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -1426,7 +1495,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>167</v>
       </c>
@@ -1434,7 +1503,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>169</v>
       </c>
@@ -1442,7 +1511,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>212</v>
       </c>
@@ -1450,7 +1519,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>228</v>
       </c>
@@ -1458,7 +1527,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>254</v>
       </c>
@@ -1466,7 +1535,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>256</v>
       </c>
@@ -1482,13 +1551,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.7890625" customWidth="1"/>
-    <col min="2" max="2" width="23.20703125" customWidth="1"/>
+    <col min="1" max="1" width="44.77734375" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1503,14 +1572,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
-  <dimension ref="A1:B81"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B92"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="62.62890625" customWidth="1"/>
+    <col min="1" max="1" width="62.6640625" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>84</v>
       </c>
@@ -1518,7 +1587,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>177</v>
       </c>
@@ -1526,7 +1595,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>262</v>
       </c>
@@ -1534,7 +1603,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1542,7 +1611,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>80</v>
       </c>
@@ -1550,7 +1619,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1558,7 +1627,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -1566,7 +1635,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>226</v>
       </c>
@@ -1574,7 +1643,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1582,7 +1651,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1590,7 +1659,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>64</v>
       </c>
@@ -1598,7 +1667,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1606,7 +1675,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1614,7 +1683,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>268</v>
       </c>
@@ -1622,7 +1691,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -1630,7 +1699,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -1638,7 +1707,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -1646,7 +1715,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>195</v>
       </c>
@@ -1654,7 +1723,15 @@
         <v>196</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>271</v>
+      </c>
+      <c r="B19" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -1662,7 +1739,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -1670,7 +1747,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -1678,7 +1755,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1686,7 +1763,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>224</v>
       </c>
@@ -1694,7 +1771,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -1702,7 +1779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -1710,7 +1787,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>96</v>
       </c>
@@ -1718,7 +1795,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -1726,7 +1803,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1734,7 +1811,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>250</v>
       </c>
@@ -1742,7 +1819,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -1750,7 +1827,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -1758,7 +1835,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>175</v>
       </c>
@@ -1766,7 +1843,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1774,7 +1851,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>232</v>
       </c>
@@ -1782,7 +1859,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -1790,7 +1867,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>173</v>
       </c>
@@ -1798,7 +1875,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,7 +1883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -1814,7 +1891,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>242</v>
       </c>
@@ -1822,7 +1899,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>104</v>
       </c>
@@ -1830,7 +1907,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>244</v>
       </c>
@@ -1838,7 +1915,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>222</v>
       </c>
@@ -1846,7 +1923,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -1854,7 +1931,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>238</v>
       </c>
@@ -1862,7 +1939,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>220</v>
       </c>
@@ -1870,7 +1947,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1878,7 +1955,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>236</v>
       </c>
@@ -1886,7 +1963,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -1894,7 +1971,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>72</v>
       </c>
@@ -1902,7 +1979,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>82</v>
       </c>
@@ -1910,7 +1987,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>30</v>
       </c>
@@ -1918,7 +1995,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>116</v>
       </c>
@@ -1926,7 +2003,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>273</v>
+      </c>
+      <c r="B54" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>119</v>
       </c>
@@ -1934,7 +2019,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>110</v>
       </c>
@@ -1942,7 +2027,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -1950,7 +2035,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -1958,7 +2043,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>246</v>
       </c>
@@ -1966,7 +2051,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>108</v>
       </c>
@@ -1974,7 +2059,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>46</v>
       </c>
@@ -1982,7 +2067,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>258</v>
       </c>
@@ -1990,7 +2075,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>106</v>
       </c>
@@ -1998,7 +2083,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>90</v>
       </c>
@@ -2006,7 +2091,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>240</v>
       </c>
@@ -2014,7 +2099,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>42</v>
       </c>
@@ -2022,7 +2107,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>92</v>
       </c>
@@ -2030,7 +2115,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>50</v>
       </c>
@@ -2038,7 +2123,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>54</v>
       </c>
@@ -2046,7 +2131,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>52</v>
       </c>
@@ -2054,7 +2139,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>123</v>
       </c>
@@ -2062,7 +2147,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>264</v>
       </c>
@@ -2070,7 +2155,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>62</v>
       </c>
@@ -2078,7 +2163,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -2086,7 +2171,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>248</v>
       </c>
@@ -2094,7 +2179,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>234</v>
       </c>
@@ -2102,7 +2187,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>98</v>
       </c>
@@ -2110,7 +2195,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -2118,7 +2203,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>74</v>
       </c>
@@ -2126,7 +2211,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -2134,12 +2219,100 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>60</v>
       </c>
       <c r="B81" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>119</v>
+      </c>
+      <c r="B82" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>275</v>
+      </c>
+      <c r="B83" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>277</v>
+      </c>
+      <c r="B84" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>279</v>
+      </c>
+      <c r="B85" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>281</v>
+      </c>
+      <c r="B86" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>283</v>
+      </c>
+      <c r="B87" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>286</v>
+      </c>
+      <c r="B88" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>287</v>
+      </c>
+      <c r="B89" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>289</v>
+      </c>
+      <c r="B90" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>291</v>
+      </c>
+      <c r="B91" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>293</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -2153,13 +2326,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.3671875" customWidth="1"/>
-    <col min="2" max="2" width="48.7890625" customWidth="1"/>
+    <col min="1" max="1" width="41.33203125" customWidth="1"/>
+    <col min="2" max="2" width="48.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -2167,7 +2340,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>180</v>
       </c>
@@ -2175,7 +2348,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>191</v>
       </c>
@@ -2183,7 +2356,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>193</v>
       </c>
@@ -2199,13 +2372,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -2213,7 +2386,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
@@ -2221,7 +2394,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
@@ -2229,7 +2402,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>270</v>
       </c>
@@ -2237,7 +2410,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>197</v>
       </c>
@@ -2245,7 +2418,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>199</v>
       </c>
@@ -2253,7 +2426,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>203</v>
       </c>
@@ -2261,7 +2434,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>206</v>
       </c>
@@ -2269,7 +2442,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>208</v>
       </c>
@@ -2277,7 +2450,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>210</v>
       </c>
@@ -2285,7 +2458,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>214</v>
       </c>
@@ -2293,7 +2466,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>218</v>
       </c>
@@ -2301,7 +2474,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>230</v>
       </c>
@@ -2317,17 +2490,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.47265625" customWidth="1"/>
+    <col min="1" max="1" width="32.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>253</v>
       </c>
@@ -2335,22 +2508,22 @@
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>260</v>
       </c>
@@ -2358,7 +2531,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>266</v>
       </c>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15393675-1755-4F97-A6A5-CAF623DF3EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67785C5A-8244-4128-AE37-D8C51A1BA3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-46188" yWindow="-108" windowWidth="46296" windowHeight="25416" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="323">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -919,6 +922,90 @@
   </si>
   <si>
     <t>печатная письменность говорила</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Челны </t>
+  </si>
+  <si>
+    <t>члены</t>
+  </si>
+  <si>
+    <t>всю установленную аппаратуру</t>
+  </si>
+  <si>
+    <t>все установленные приборы</t>
+  </si>
+  <si>
+    <t>Что это была за схема</t>
+  </si>
+  <si>
+    <t>Что это был за чертёж</t>
+  </si>
+  <si>
+    <t>Материал чемодана</t>
+  </si>
+  <si>
+    <t>Сырьё чемодана</t>
+  </si>
+  <si>
+    <t>разрядили свои «магазины»</t>
+  </si>
+  <si>
+    <t>разрядили свои «обоймы»</t>
+  </si>
+  <si>
+    <t>«уважающей себя» «группировке»</t>
+  </si>
+  <si>
+    <t>«уважающего себя» «сообщества»</t>
+  </si>
+  <si>
+    <t>от величины фигуры</t>
+  </si>
+  <si>
+    <t>от величины личности</t>
+  </si>
+  <si>
+    <t>в нашей структуре</t>
+  </si>
+  <si>
+    <t>в нашем отряде</t>
+  </si>
+  <si>
+    <t>линия монолога встала</t>
+  </si>
+  <si>
+    <t>направление размышления встало</t>
+  </si>
+  <si>
+    <t>номеров первым,</t>
+  </si>
+  <si>
+    <t>номером первым,</t>
+  </si>
+  <si>
+    <t>в их компании или приглашая в свою</t>
+  </si>
+  <si>
+    <t>в их кругу или приглашая в свой</t>
+  </si>
+  <si>
+    <t>Информация набиралась сама собой</t>
+  </si>
+  <si>
+    <t>Сведения набирались сами собой</t>
+  </si>
+  <si>
+    <t>есть версия, что</t>
+  </si>
+  <si>
+    <t>есть предположение, что</t>
+  </si>
+  <si>
+    <t>в другую «бригаду»</t>
+  </si>
+  <si>
+    <t>в другой «отряд»</t>
   </si>
 </sst>
 </file>
@@ -1250,13 +1337,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="48.109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1015625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1264,7 +1351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1272,7 +1359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1280,7 +1367,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1288,7 +1375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1296,7 +1383,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
@@ -1304,7 +1391,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -1312,7 +1399,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -1320,7 +1407,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>152</v>
       </c>
@@ -1328,7 +1415,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -1336,7 +1423,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
@@ -1344,7 +1431,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>158</v>
       </c>
@@ -1352,7 +1439,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>161</v>
       </c>
@@ -1360,7 +1447,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>163</v>
       </c>
@@ -1368,7 +1455,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>165</v>
       </c>
@@ -1376,7 +1463,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>171</v>
       </c>
@@ -1384,7 +1471,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>181</v>
       </c>
@@ -1392,7 +1479,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>184</v>
       </c>
@@ -1400,7 +1487,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>186</v>
       </c>
@@ -1408,7 +1495,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>189</v>
       </c>
@@ -1416,7 +1503,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>201</v>
       </c>
@@ -1424,12 +1511,20 @@
         <v>202</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>216</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -1441,13 +1536,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="26.109375" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" customWidth="1"/>
+    <col min="1" max="1" width="26.1015625" customWidth="1"/>
+    <col min="2" max="2" width="27.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1455,7 +1550,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1463,7 +1558,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -1471,7 +1566,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -1479,7 +1574,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -1487,7 +1582,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -1495,7 +1590,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>167</v>
       </c>
@@ -1503,7 +1598,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>169</v>
       </c>
@@ -1511,7 +1606,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>212</v>
       </c>
@@ -1519,7 +1614,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>228</v>
       </c>
@@ -1527,7 +1622,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>254</v>
       </c>
@@ -1535,7 +1630,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>256</v>
       </c>
@@ -1551,13 +1646,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="44.77734375" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" customWidth="1"/>
+    <col min="1" max="1" width="44.7890625" customWidth="1"/>
+    <col min="2" max="2" width="23.20703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1572,14 +1667,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
-  <dimension ref="A1:B92"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B96"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="62.6640625" customWidth="1"/>
-    <col min="2" max="2" width="71" customWidth="1"/>
+    <col min="1" max="1" width="48.7890625" customWidth="1"/>
+    <col min="2" max="2" width="55.9453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>84</v>
       </c>
@@ -1587,7 +1682,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>177</v>
       </c>
@@ -1595,7 +1690,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>262</v>
       </c>
@@ -1603,7 +1698,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1611,7 +1706,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>80</v>
       </c>
@@ -1619,7 +1714,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1627,7 +1722,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -1635,7 +1730,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>226</v>
       </c>
@@ -1643,7 +1738,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1651,7 +1746,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1659,7 +1754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>64</v>
       </c>
@@ -1667,7 +1762,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1675,7 +1770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1683,7 +1778,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>268</v>
       </c>
@@ -1691,7 +1786,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -1699,7 +1794,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -1707,7 +1802,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -1715,7 +1810,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>195</v>
       </c>
@@ -1723,7 +1818,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>271</v>
       </c>
@@ -1731,7 +1826,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -1739,7 +1834,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -1747,7 +1842,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -1755,7 +1850,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1763,7 +1858,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>224</v>
       </c>
@@ -1771,7 +1866,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -1779,7 +1874,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -1787,7 +1882,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>96</v>
       </c>
@@ -1795,7 +1890,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -1803,7 +1898,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1811,7 +1906,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>250</v>
       </c>
@@ -1819,7 +1914,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -1827,7 +1922,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -1835,7 +1930,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>175</v>
       </c>
@@ -1843,7 +1938,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1851,7 +1946,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>232</v>
       </c>
@@ -1859,7 +1954,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -1867,7 +1962,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>173</v>
       </c>
@@ -1875,7 +1970,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>24</v>
       </c>
@@ -1883,7 +1978,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -1891,7 +1986,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>242</v>
       </c>
@@ -1899,7 +1994,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>104</v>
       </c>
@@ -1907,7 +2002,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>244</v>
       </c>
@@ -1915,7 +2010,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>222</v>
       </c>
@@ -1923,7 +2018,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -1931,7 +2026,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>238</v>
       </c>
@@ -1939,7 +2034,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>220</v>
       </c>
@@ -1947,7 +2042,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1955,7 +2050,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>236</v>
       </c>
@@ -1963,7 +2058,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -1971,7 +2066,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="3" t="s">
         <v>72</v>
       </c>
@@ -1979,7 +2074,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>82</v>
       </c>
@@ -1987,7 +2082,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>30</v>
       </c>
@@ -1995,7 +2090,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>116</v>
       </c>
@@ -2003,7 +2098,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>273</v>
       </c>
@@ -2011,7 +2106,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>119</v>
       </c>
@@ -2019,7 +2114,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3" t="s">
         <v>110</v>
       </c>
@@ -2027,7 +2122,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -2035,7 +2130,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -2043,7 +2138,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>246</v>
       </c>
@@ -2051,7 +2146,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>108</v>
       </c>
@@ -2059,7 +2154,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>46</v>
       </c>
@@ -2067,7 +2162,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>258</v>
       </c>
@@ -2075,7 +2170,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>106</v>
       </c>
@@ -2083,7 +2178,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>90</v>
       </c>
@@ -2091,7 +2186,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>240</v>
       </c>
@@ -2099,7 +2194,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>42</v>
       </c>
@@ -2107,7 +2202,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>92</v>
       </c>
@@ -2115,7 +2210,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>50</v>
       </c>
@@ -2123,7 +2218,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>54</v>
       </c>
@@ -2131,7 +2226,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>52</v>
       </c>
@@ -2139,7 +2234,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>123</v>
       </c>
@@ -2147,7 +2242,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>264</v>
       </c>
@@ -2155,7 +2250,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>62</v>
       </c>
@@ -2163,7 +2258,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -2171,7 +2266,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>248</v>
       </c>
@@ -2179,7 +2274,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>234</v>
       </c>
@@ -2187,7 +2282,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>98</v>
       </c>
@@ -2195,7 +2290,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -2203,7 +2298,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>74</v>
       </c>
@@ -2211,7 +2306,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -2219,7 +2314,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>60</v>
       </c>
@@ -2227,7 +2322,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>119</v>
       </c>
@@ -2235,7 +2330,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>275</v>
       </c>
@@ -2243,7 +2338,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>277</v>
       </c>
@@ -2251,7 +2346,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>279</v>
       </c>
@@ -2259,7 +2354,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>281</v>
       </c>
@@ -2267,7 +2362,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>283</v>
       </c>
@@ -2275,7 +2370,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>286</v>
       </c>
@@ -2283,7 +2378,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>287</v>
       </c>
@@ -2291,7 +2386,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>289</v>
       </c>
@@ -2299,7 +2394,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>291</v>
       </c>
@@ -2307,12 +2402,44 @@
         <v>292</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>293</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>294</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" t="s">
+        <v>299</v>
+      </c>
+      <c r="B93" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" t="s">
+        <v>301</v>
+      </c>
+      <c r="B94" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" t="s">
+        <v>311</v>
+      </c>
+      <c r="B95" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
+        <v>319</v>
+      </c>
+      <c r="B96" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -2325,14 +2452,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="41.33203125" customWidth="1"/>
-    <col min="2" max="2" width="48.77734375" customWidth="1"/>
+    <col min="1" max="1" width="41.3125" customWidth="1"/>
+    <col min="2" max="2" width="48.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -2340,7 +2467,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>180</v>
       </c>
@@ -2348,7 +2475,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>191</v>
       </c>
@@ -2356,12 +2483,20 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>193</v>
       </c>
       <c r="B4" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B5" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -2371,14 +2506,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="40.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.7890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -2386,7 +2521,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
@@ -2394,7 +2529,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
@@ -2402,7 +2537,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>270</v>
       </c>
@@ -2410,7 +2545,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>197</v>
       </c>
@@ -2418,7 +2553,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>199</v>
       </c>
@@ -2426,7 +2561,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>203</v>
       </c>
@@ -2434,7 +2569,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>206</v>
       </c>
@@ -2442,7 +2577,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>208</v>
       </c>
@@ -2450,7 +2585,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>210</v>
       </c>
@@ -2458,7 +2593,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>214</v>
       </c>
@@ -2466,7 +2601,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>218</v>
       </c>
@@ -2474,12 +2609,60 @@
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -2489,18 +2672,18 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="32.44140625" customWidth="1"/>
+    <col min="1" max="1" width="32.41796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>253</v>
       </c>
@@ -2508,22 +2691,22 @@
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>260</v>
       </c>
@@ -2531,12 +2714,28 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>266</v>
       </c>
       <c r="B7" t="s">
         <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B9" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67785C5A-8244-4128-AE37-D8C51A1BA3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8A127D-8587-4E94-A0C6-E79CBB423673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="365">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1006,6 +1006,132 @@
   </si>
   <si>
     <t>в другой «отряд»</t>
+  </si>
+  <si>
+    <t>жёстко придерживающихся определённой дисциплины</t>
+  </si>
+  <si>
+    <t>жёстко придерживающихся определённых правил</t>
+  </si>
+  <si>
+    <t>такой, постоянно подстёгиваемой дисциплины</t>
+  </si>
+  <si>
+    <t>таких, постоянно подстёгиваемых правил</t>
+  </si>
+  <si>
+    <t>Хороший, знаете ли, бизнес</t>
+  </si>
+  <si>
+    <t>Хорошее, знаете ли, предпринимательство</t>
+  </si>
+  <si>
+    <t>какую-то «нашу» фирму</t>
+  </si>
+  <si>
+    <t>какое-то «наше» предприятие</t>
+  </si>
+  <si>
+    <t>жизнедеятельность «бригады»</t>
+  </si>
+  <si>
+    <t>жизнедеятельность «отряда»</t>
+  </si>
+  <si>
+    <t>плюс «на</t>
+  </si>
+  <si>
+    <t>дополнительно «на</t>
+  </si>
+  <si>
+    <t>любая другая структура,</t>
+  </si>
+  <si>
+    <t>любое другое сообщество,</t>
+  </si>
+  <si>
+    <t>Случай с Фишером не единичный и не исключительный</t>
+  </si>
+  <si>
+    <t>История с Фишером не единичная и не исключительная</t>
+  </si>
+  <si>
+    <t>Того же типа была история с танзанитами, о которой я узнал после её идиотского окончания и о которой</t>
+  </si>
+  <si>
+    <t>Того же вида был случай с танзанитами, о котором я узнал после его идиотского окончания и о котором</t>
+  </si>
+  <si>
+    <t>«аудиторскую» проверку</t>
+  </si>
+  <si>
+    <t>«полную» проверку</t>
+  </si>
+  <si>
+    <t>позволю ситуации развиться до критической и смогу вовремя ее остановить</t>
+  </si>
+  <si>
+    <t>позволю случаю развиться до чрезвычайного и смогу вовремя его остановить</t>
+  </si>
+  <si>
+    <t>железная и даже репрессивная дисциплина</t>
+  </si>
+  <si>
+    <t>железные и даже угнетающие правила</t>
+  </si>
+  <si>
+    <t>сэкономить на их долях</t>
+  </si>
+  <si>
+    <t>уменьшить их доли</t>
+  </si>
+  <si>
+    <t>ему в пику</t>
+  </si>
+  <si>
+    <t>ему в острие</t>
+  </si>
+  <si>
+    <t>повторил всю процедуру</t>
+  </si>
+  <si>
+    <t>повторил всё действие</t>
+  </si>
+  <si>
+    <t>этот фактор и должен был</t>
+  </si>
+  <si>
+    <t>это обстоятельство и должно было</t>
+  </si>
+  <si>
+    <t>Спецназ перевалился</t>
+  </si>
+  <si>
+    <t>особое подразделение перевалилось</t>
+  </si>
+  <si>
+    <t>Вологодский конвой</t>
+  </si>
+  <si>
+    <t>Вологодское сопровождение под стражей</t>
+  </si>
+  <si>
+    <t>процедуру не представлялось</t>
+  </si>
+  <si>
+    <t>действие не представлялось</t>
+  </si>
+  <si>
+    <t>наша, вовремя созданная контора</t>
+  </si>
+  <si>
+    <t>наше, вовремя созданное учреждение</t>
+  </si>
+  <si>
+    <t>была готова любая сумма</t>
+  </si>
+  <si>
+    <t>было готово любое количество денег</t>
   </si>
 </sst>
 </file>
@@ -1338,12 +1464,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="48.1015625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.08984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1351,7 +1477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1359,7 +1485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1367,7 +1493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1375,7 +1501,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1383,7 +1509,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
@@ -1391,7 +1517,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -1399,7 +1525,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -1407,7 +1533,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>152</v>
       </c>
@@ -1415,7 +1541,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -1423,7 +1549,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>156</v>
       </c>
@@ -1431,7 +1557,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>158</v>
       </c>
@@ -1439,7 +1565,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>161</v>
       </c>
@@ -1447,7 +1573,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>163</v>
       </c>
@@ -1455,7 +1581,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>165</v>
       </c>
@@ -1463,7 +1589,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>171</v>
       </c>
@@ -1471,7 +1597,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>181</v>
       </c>
@@ -1479,7 +1605,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>184</v>
       </c>
@@ -1487,7 +1613,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>186</v>
       </c>
@@ -1495,7 +1621,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>189</v>
       </c>
@@ -1503,7 +1629,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>201</v>
       </c>
@@ -1511,7 +1637,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>216</v>
       </c>
@@ -1519,7 +1645,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>297</v>
       </c>
@@ -1536,13 +1662,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F87438-90D7-474C-93D6-C8C288F022C9}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.1015625" customWidth="1"/>
-    <col min="2" max="2" width="27.68359375" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1550,7 +1676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1558,7 +1684,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -1566,7 +1692,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -1574,7 +1700,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -1582,7 +1708,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -1590,7 +1716,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>167</v>
       </c>
@@ -1598,7 +1724,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>169</v>
       </c>
@@ -1606,7 +1732,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>212</v>
       </c>
@@ -1614,7 +1740,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>228</v>
       </c>
@@ -1622,7 +1748,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>254</v>
       </c>
@@ -1630,7 +1756,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>256</v>
       </c>
@@ -1646,13 +1772,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E77608-116C-4BB2-AE5D-93226A6BBFA4}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="44.7890625" customWidth="1"/>
-    <col min="2" max="2" width="23.20703125" customWidth="1"/>
+    <col min="1" max="1" width="44.81640625" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>44</v>
       </c>
@@ -1667,14 +1793,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
-  <dimension ref="A1:B96"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B108"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.7890625" customWidth="1"/>
-    <col min="2" max="2" width="55.9453125" customWidth="1"/>
+    <col min="1" max="1" width="48.81640625" customWidth="1"/>
+    <col min="2" max="2" width="55.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>84</v>
       </c>
@@ -1682,7 +1808,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>177</v>
       </c>
@@ -1690,7 +1816,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>262</v>
       </c>
@@ -1698,7 +1824,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1706,7 +1832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>80</v>
       </c>
@@ -1714,7 +1840,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -1722,7 +1848,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -1730,7 +1856,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>226</v>
       </c>
@@ -1738,7 +1864,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1746,7 +1872,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1754,7 +1880,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>64</v>
       </c>
@@ -1762,7 +1888,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1770,7 +1896,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1778,7 +1904,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>268</v>
       </c>
@@ -1786,7 +1912,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -1794,7 +1920,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -1802,7 +1928,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -1810,7 +1936,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>195</v>
       </c>
@@ -1818,7 +1944,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>271</v>
       </c>
@@ -1826,7 +1952,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -1834,7 +1960,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -1842,7 +1968,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -1850,7 +1976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1858,7 +1984,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>224</v>
       </c>
@@ -1866,7 +1992,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -1874,7 +2000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -1882,7 +2008,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>96</v>
       </c>
@@ -1890,7 +2016,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -1898,7 +2024,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1906,7 +2032,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>250</v>
       </c>
@@ -1914,7 +2040,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -1922,7 +2048,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -1930,7 +2056,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>175</v>
       </c>
@@ -1938,7 +2064,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1946,7 +2072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>232</v>
       </c>
@@ -1954,7 +2080,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -1962,7 +2088,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>173</v>
       </c>
@@ -1970,7 +2096,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>24</v>
       </c>
@@ -1978,7 +2104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -1986,7 +2112,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>242</v>
       </c>
@@ -1994,7 +2120,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>104</v>
       </c>
@@ -2002,7 +2128,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>244</v>
       </c>
@@ -2010,7 +2136,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>222</v>
       </c>
@@ -2018,7 +2144,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -2026,7 +2152,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>238</v>
       </c>
@@ -2034,7 +2160,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>220</v>
       </c>
@@ -2042,7 +2168,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -2050,7 +2176,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>236</v>
       </c>
@@ -2058,7 +2184,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -2066,7 +2192,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>72</v>
       </c>
@@ -2074,7 +2200,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>82</v>
       </c>
@@ -2082,7 +2208,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>30</v>
       </c>
@@ -2090,7 +2216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>116</v>
       </c>
@@ -2098,7 +2224,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>273</v>
       </c>
@@ -2106,7 +2232,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>119</v>
       </c>
@@ -2114,7 +2240,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>110</v>
       </c>
@@ -2122,7 +2248,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -2130,7 +2256,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -2138,7 +2264,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>246</v>
       </c>
@@ -2146,7 +2272,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>108</v>
       </c>
@@ -2154,7 +2280,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>46</v>
       </c>
@@ -2162,7 +2288,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>258</v>
       </c>
@@ -2170,7 +2296,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>106</v>
       </c>
@@ -2178,7 +2304,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>90</v>
       </c>
@@ -2186,7 +2312,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>240</v>
       </c>
@@ -2194,7 +2320,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>42</v>
       </c>
@@ -2202,7 +2328,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>92</v>
       </c>
@@ -2210,7 +2336,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>50</v>
       </c>
@@ -2218,7 +2344,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>54</v>
       </c>
@@ -2226,7 +2352,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>52</v>
       </c>
@@ -2234,7 +2360,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>123</v>
       </c>
@@ -2242,7 +2368,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>264</v>
       </c>
@@ -2250,7 +2376,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>62</v>
       </c>
@@ -2258,7 +2384,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -2266,7 +2392,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>248</v>
       </c>
@@ -2274,7 +2400,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>234</v>
       </c>
@@ -2282,7 +2408,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>98</v>
       </c>
@@ -2290,7 +2416,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -2298,7 +2424,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>74</v>
       </c>
@@ -2306,7 +2432,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -2314,7 +2440,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>60</v>
       </c>
@@ -2322,15 +2448,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" t="s">
-        <v>119</v>
-      </c>
-      <c r="B82" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>275</v>
       </c>
@@ -2338,7 +2456,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>277</v>
       </c>
@@ -2346,7 +2464,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>279</v>
       </c>
@@ -2354,7 +2472,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>281</v>
       </c>
@@ -2362,7 +2480,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>283</v>
       </c>
@@ -2370,7 +2488,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>286</v>
       </c>
@@ -2378,7 +2496,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>287</v>
       </c>
@@ -2386,7 +2504,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>289</v>
       </c>
@@ -2394,7 +2512,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>291</v>
       </c>
@@ -2402,7 +2520,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>293</v>
       </c>
@@ -2410,7 +2528,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>299</v>
       </c>
@@ -2418,7 +2536,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>301</v>
       </c>
@@ -2426,7 +2544,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>311</v>
       </c>
@@ -2434,12 +2552,108 @@
         <v>312</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>319</v>
       </c>
       <c r="B96" t="s">
         <v>320</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>331</v>
+      </c>
+      <c r="B97" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>333</v>
+      </c>
+      <c r="B98" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>335</v>
+      </c>
+      <c r="B99" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>341</v>
+      </c>
+      <c r="B100" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>347</v>
+      </c>
+      <c r="B101" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>349</v>
+      </c>
+      <c r="B102" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>351</v>
+      </c>
+      <c r="B103" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>353</v>
+      </c>
+      <c r="B104" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>355</v>
+      </c>
+      <c r="B105" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>357</v>
+      </c>
+      <c r="B106" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>361</v>
+      </c>
+      <c r="B108" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -2452,14 +2666,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41358612-3EA0-4A89-95C5-BCB8AC62B7D5}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.3125" customWidth="1"/>
-    <col min="2" max="2" width="48.7890625" customWidth="1"/>
+    <col min="1" max="1" width="52.36328125" customWidth="1"/>
+    <col min="2" max="2" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -2467,7 +2681,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>180</v>
       </c>
@@ -2475,7 +2689,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>191</v>
       </c>
@@ -2483,7 +2697,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>193</v>
       </c>
@@ -2491,12 +2705,28 @@
         <v>194</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>315</v>
       </c>
       <c r="B5" t="s">
         <v>316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B7" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -2506,14 +2736,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.7890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="71.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
@@ -2521,7 +2751,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
@@ -2529,7 +2759,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
@@ -2537,7 +2767,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>270</v>
       </c>
@@ -2545,7 +2775,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>197</v>
       </c>
@@ -2553,7 +2783,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>199</v>
       </c>
@@ -2561,7 +2791,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>203</v>
       </c>
@@ -2569,7 +2799,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>206</v>
       </c>
@@ -2577,7 +2807,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>208</v>
       </c>
@@ -2585,7 +2815,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>210</v>
       </c>
@@ -2593,7 +2823,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>214</v>
       </c>
@@ -2601,7 +2831,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>218</v>
       </c>
@@ -2609,7 +2839,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>230</v>
       </c>
@@ -2617,7 +2847,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>303</v>
       </c>
@@ -2625,7 +2855,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>305</v>
       </c>
@@ -2633,7 +2863,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>307</v>
       </c>
@@ -2641,7 +2871,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>309</v>
       </c>
@@ -2649,7 +2879,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>317</v>
       </c>
@@ -2657,12 +2887,68 @@
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>321</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>322</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>338</v>
+      </c>
+      <c r="B24" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>345</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -2673,17 +2959,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6C6BFA-193E-467E-8515-B98D288F205E}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.41796875" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>253</v>
       </c>
@@ -2691,22 +2977,22 @@
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>260</v>
       </c>
@@ -2714,7 +3000,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>266</v>
       </c>
@@ -2722,7 +3008,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>295</v>
       </c>
@@ -2730,7 +3016,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>313</v>
       </c>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8A127D-8587-4E94-A0C6-E79CBB423673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0352580F-EA1E-4B1B-B8AC-69D25C054B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="367">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1132,6 +1132,13 @@
   </si>
   <si>
     <t>было готово любое количество денег</t>
+  </si>
+  <si>
+    <t>каждая бригада и
+дружественная ей</t>
+  </si>
+  <si>
+    <t>каждый отряд и дружественный ему</t>
   </si>
 </sst>
 </file>
@@ -2736,7 +2743,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="71.453125" style="1" customWidth="1"/>
@@ -2949,6 +2956,14 @@
       </c>
       <c r="B26" s="1" t="s">
         <v>364</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B27" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0352580F-EA1E-4B1B-B8AC-69D25C054B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94570761-F2F7-40DA-8D08-E20057EA67B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="377">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1139,6 +1139,36 @@
   </si>
   <si>
     <t>каждый отряд и дружественный ему</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ремонт которого шёл полным ходом и требовал </t>
+  </si>
+  <si>
+    <t>починка которого шла полным ходом и требовала</t>
+  </si>
+  <si>
+    <t>информацией (она была уже устаревшей</t>
+  </si>
+  <si>
+    <t>сведениями (они были уже устаревшими</t>
+  </si>
+  <si>
+    <t>Материала накопилась масса</t>
+  </si>
+  <si>
+    <t>сведений накопилось множество</t>
+  </si>
+  <si>
+    <t>накопилась в избытке информация</t>
+  </si>
+  <si>
+    <t>накопилмсь в избытке сведения</t>
+  </si>
+  <si>
+    <t>сыграло значение и потребильское обстоятельство</t>
+  </si>
+  <si>
+    <t>сыграл роль и меркантильный фактор</t>
   </si>
 </sst>
 </file>
@@ -1470,7 +1500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="48.08984375" style="1" customWidth="1"/>
@@ -1658,6 +1688,14 @@
       </c>
       <c r="B23" s="1" t="s">
         <v>298</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -1800,7 +1838,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.81640625" customWidth="1"/>
@@ -2661,6 +2699,14 @@
       </c>
       <c r="B108" t="s">
         <v>362</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>373</v>
+      </c>
+      <c r="B109" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -2743,7 +2789,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7221AE72-6516-46D3-AD64-A2A61F3BB4E0}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="71.453125" style="1" customWidth="1"/>
@@ -2964,6 +3010,30 @@
       </c>
       <c r="B27" t="s">
         <v>366</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94570761-F2F7-40DA-8D08-E20057EA67B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9AF6E0-2282-41CA-AEF8-1EDDE957015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="381">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1169,6 +1169,18 @@
   </si>
   <si>
     <t>сыграл роль и меркантильный фактор</t>
+  </si>
+  <si>
+    <t>упала дисциплина</t>
+  </si>
+  <si>
+    <t>соблюдение правил упало</t>
+  </si>
+  <si>
+    <t>поддерживать эту самую дисциплину</t>
+  </si>
+  <si>
+    <t>поддерживать это самое соблюдение правил</t>
   </si>
 </sst>
 </file>
@@ -1838,7 +1850,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBA6DC-890F-42B4-9EA1-03D77E0C5D6C}">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.81640625" customWidth="1"/>
@@ -2707,6 +2719,22 @@
       </c>
       <c r="B109" t="s">
         <v>374</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B110" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>379</v>
+      </c>
+      <c r="B111" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="6"/>
+  <fileVersion appName="Calc" lowestEdited="7"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="490">
   <si>
     <t xml:space="preserve">обрабатываемой информации, по просторам которой</t>
   </si>
@@ -925,7 +925,7 @@
     <t xml:space="preserve">накопилась в избытке информация</t>
   </si>
   <si>
-    <t xml:space="preserve">накопилмсь в избытке сведения</t>
+    <t xml:space="preserve">накопились в избытке сведения</t>
   </si>
   <si>
     <t xml:space="preserve">упала дисциплина</t>
@@ -1116,6 +1116,114 @@
     <t xml:space="preserve">используют тот же разговорник</t>
   </si>
   <si>
+    <t xml:space="preserve">увидел впервые бизнес-леди</t>
+  </si>
+  <si>
+    <t xml:space="preserve">увидел впервые женщину-предпринимателя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">спас президента компании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">спас главу предприятия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">красной активной марки </t>
+  </si>
+  <si>
+    <t xml:space="preserve">красной метки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">соблюдаемой схеме сопровождения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">соблюдаемом укладе сопровождения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">с самой «конторой» </t>
+  </si>
+  <si>
+    <t xml:space="preserve">с самой «службой безопасности государства» </t>
+  </si>
+  <si>
+    <t xml:space="preserve">отель я попросил</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гостинницу я попросил</t>
+  </si>
+  <si>
+    <t xml:space="preserve">не менять внутри инфраструктуры </t>
+  </si>
+  <si>
+    <t xml:space="preserve">не менять внутри выстроенных порядков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">следственную группу, ведущую </t>
+  </si>
+  <si>
+    <t xml:space="preserve">следственное подразделение, ведущее</t>
+  </si>
+  <si>
+    <t xml:space="preserve">с помпой и сиренами</t>
+  </si>
+  <si>
+    <t xml:space="preserve">с тревожными оповещением</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кучу материала, собранного </t>
+  </si>
+  <si>
+    <t xml:space="preserve">кучу сведений, собранных</t>
+  </si>
+  <si>
+    <t xml:space="preserve">проанализированная и с конкретными выводами, привело к тому, что ею </t>
+  </si>
+  <si>
+    <t xml:space="preserve">рассмотренные и с определёнными выводами, привело к тому, что ими </t>
+  </si>
+  <si>
+    <t xml:space="preserve">гастрономическая тема во Франции неповторима </t>
+  </si>
+  <si>
+    <t xml:space="preserve">вопрос чревоугодия во Франции неповторим</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оставшийся внутри салона</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оставшийся внутри средства передвижения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Процент, который он предложил </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доход, который он предложил </t>
+  </si>
+  <si>
+    <t xml:space="preserve">накопленная небольшая сумма позволяла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">накопленное небольшое количество денег позволяло</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сумма, кстати</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стоимость, кстати</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сумма оплаты не увеличивалась </t>
+  </si>
+  <si>
+    <t xml:space="preserve">размер оплаты не увеличивался</t>
+  </si>
+  <si>
+    <t xml:space="preserve">копилась, либо передавалась </t>
+  </si>
+  <si>
+    <t xml:space="preserve">копился, либо передавался</t>
+  </si>
+  <si>
     <t xml:space="preserve">обговоренная фраза из уст Олега, которая</t>
   </si>
   <si>
@@ -1345,6 +1453,12 @@
     <t xml:space="preserve">значение основное и подавляющее, а не сдерживающее</t>
   </si>
   <si>
+    <t xml:space="preserve">отеля «Мариотт» на Тверской улице, в фойе которого </t>
+  </si>
+  <si>
+    <t xml:space="preserve">гостинницы «Мариотт» на Тверской улице, в прихожей которой</t>
+  </si>
+  <si>
     <t xml:space="preserve">экономическое конгломераты</t>
   </si>
   <si>
@@ -1394,6 +1508,18 @@
   </si>
   <si>
     <t xml:space="preserve">подходящее оправдание </t>
+  </si>
+  <si>
+    <t xml:space="preserve">замусоренному полу подвала </t>
+  </si>
+  <si>
+    <t xml:space="preserve">замусоренному полу подвалу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">с точки зрения профессиональной, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">с точки зрения профессиональности</t>
   </si>
 </sst>
 </file>
@@ -1493,37 +1619,45 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1737,9 +1871,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.2734375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="48.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="48.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1993,105 +2127,105 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.2734375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="26.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="27.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="5" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2112,17 +2246,17 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.2734375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="44.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="23.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="5" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2142,178 +2276,178 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B137"/>
-  <sheetFormatPr defaultColWidth="8.2734375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B155"/>
+  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="48.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="55.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="5" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="5" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="5" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="5" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="5" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="5" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="5" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="5" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="5" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="5" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="5" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="5" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2326,18 +2460,18 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="5" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="5" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2350,98 +2484,98 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="5" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="5" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="5" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="5" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="5" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="5" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="5" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="5" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="5" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="5" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="5" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2454,562 +2588,562 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="5" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="5" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="5" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="5" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="5" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="5" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="5" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="5" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="6" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="5" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="5" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="5" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="5" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="5" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="5" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="5" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="5" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="5" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="5" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="5" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="5" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="5" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="5" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="5" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="5" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="5" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="5" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="5" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="5" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="5" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="5" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="5" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="5" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="5" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="5" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="5" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="5" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="5" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="5" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="5" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="5" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="5" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="5" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="5" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="5" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="5" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="6" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="5" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="5" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="5" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="5" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" s="5" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" s="5" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="5" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="5" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="5" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" s="5" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" s="5" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" s="5" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" s="5" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="A106" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" s="5" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="5" t="s">
+      <c r="A107" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="6" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="A108" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" s="5" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="A109" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" s="5" t="s">
         <v>298</v>
       </c>
     </row>
@@ -3017,224 +3151,368 @@
       <c r="A110" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="B110" s="5" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="A111" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" s="5" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B112" s="6" t="s">
+      <c r="B112" s="7" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B113" s="7" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="7" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="B115" s="6" t="s">
+      <c r="B115" s="7" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" s="5" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" s="5" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="B118" s="6" t="s">
+      <c r="B118" s="7" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B119" s="7" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="B120" s="6" t="s">
+      <c r="B120" s="7" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B121" s="6" t="s">
+      <c r="B121" s="7" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B122" s="6" t="s">
+      <c r="B122" s="7" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="B123" s="6" t="s">
+      <c r="B123" s="7" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="B124" s="6" t="s">
+      <c r="B124" s="7" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="B125" s="6" t="s">
+      <c r="B125" s="7" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="6" t="s">
+      <c r="A126" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" s="5" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="B127" s="6" t="s">
+      <c r="B127" s="7" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="B128" s="6" t="s">
+      <c r="B128" s="7" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="6" t="s">
+      <c r="A129" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B129" s="6" t="s">
+      <c r="B129" s="7" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="6" t="s">
+      <c r="A130" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B130" s="6" t="s">
+      <c r="B130" s="7" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="6" t="s">
+      <c r="A131" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B131" s="6" t="s">
+      <c r="B131" s="7" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="6" t="s">
+      <c r="A132" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B132" s="6" t="s">
+      <c r="B132" s="7" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="B133" s="6" t="s">
+      <c r="B133" s="7" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="6" t="s">
+      <c r="A134" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="B134" s="6" t="s">
+      <c r="B134" s="7" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="23.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="6" t="s">
+    <row r="135" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B135" s="7" t="s">
+      <c r="B135" s="8" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="6" t="s">
+      <c r="A136" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="B136" s="6" t="s">
+      <c r="B136" s="7" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="6" t="s">
+      <c r="A137" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="B137" s="7" t="s">
         <v>354</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -3254,66 +3532,66 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.2734375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="48.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="52.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="48.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>355</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>356</v>
+      <c r="A1" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>359</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>360</v>
+      <c r="A3" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>361</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>362</v>
+      <c r="A4" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>364</v>
+      <c r="A5" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>366</v>
+        <v>401</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>368</v>
+        <v>403</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -3332,259 +3610,267 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultColWidth="8.2734375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="71.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="53.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="71.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="53.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>372</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>380</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>382</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>386</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>398</v>
+        <v>434</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>409</v>
+        <v>445</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>414</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>416</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>419</v>
+        <v>455</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>421</v>
+        <v>457</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>422</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>424</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>426</v>
+        <v>462</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>428</v>
+        <v>464</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>430</v>
+        <v>466</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -3603,83 +3889,99 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.2734375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="32.41"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>431</v>
+      <c r="A1" s="5" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>433</v>
+      <c r="A2" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>434</v>
+      <c r="A3" s="5" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>435</v>
+      <c r="A4" s="5" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>436</v>
+      <c r="A5" s="5" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>438</v>
+      <c r="A6" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>439</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>440</v>
+      <c r="A7" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>441</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>442</v>
+      <c r="A8" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>443</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>444</v>
+      <c r="A9" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>445</v>
+      <c r="A10" s="5" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>447</v>
+      <c r="A11" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1619,7 +1619,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1654,10 +1654,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3468,10 +3464,10 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="9" t="s">
+      <c r="A150" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B150" s="9" t="s">
+      <c r="B150" s="7" t="s">
         <v>380</v>
       </c>
     </row>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2D1D95-85F7-4493-9FE1-87D0B78214B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Составные_важные" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Составные" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="простые" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="неизменные" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="неизменные_длинные" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="неизменные_короткие" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="ошибки" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
+    <sheet name="Составные" sheetId="2" r:id="rId2"/>
+    <sheet name="простые" sheetId="3" r:id="rId3"/>
+    <sheet name="неизменные" sheetId="4" r:id="rId4"/>
+    <sheet name="неизменные_длинные" sheetId="5" r:id="rId5"/>
+    <sheet name="неизменные_короткие" sheetId="6" r:id="rId6"/>
+    <sheet name="ошибки" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Составные_важные!$A$1:$B$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные_важные!$A$1:$B$22</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -29,150 +37,150 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="490">
-  <si>
-    <t xml:space="preserve">обрабатываемой информации, по просторам которой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обрабатываемых сведений, по просторам которых</t>
-  </si>
-  <si>
-    <t xml:space="preserve">соответствующей сопроводительной информацией</t>
-  </si>
-  <si>
-    <t xml:space="preserve">соответствующими сопроводительными сведениями</t>
-  </si>
-  <si>
-    <t xml:space="preserve">должной информации, поступившей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">должных сведений, поступивших</t>
-  </si>
-  <si>
-    <t xml:space="preserve">опасности информации, которой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">опасности сведений, которыми</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кстати о комплексе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кстати о учреждении</t>
-  </si>
-  <si>
-    <t xml:space="preserve">выехавший на операцию</t>
-  </si>
-  <si>
-    <t xml:space="preserve">выехавший на захват</t>
-  </si>
-  <si>
-    <t xml:space="preserve">то в редких компаниях</t>
-  </si>
-  <si>
-    <t xml:space="preserve">то в редких общностях</t>
-  </si>
-  <si>
-    <t xml:space="preserve">от теперешней компании</t>
-  </si>
-  <si>
-    <t xml:space="preserve">от теперешнего круга</t>
-  </si>
-  <si>
-    <t xml:space="preserve">присутствие в их компании нужно</t>
-  </si>
-  <si>
-    <t xml:space="preserve">присутствие в их общности нужно</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в компании ещё нескольких</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в кругу ещё нескольких</t>
-  </si>
-  <si>
-    <t xml:space="preserve">приездами разных компаний</t>
-  </si>
-  <si>
-    <t xml:space="preserve">приездами разных общностей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">невозможных компаний, в</t>
-  </si>
-  <si>
-    <t xml:space="preserve">невозможных общностей, в</t>
-  </si>
-  <si>
-    <t xml:space="preserve">суммой фактического кредита</t>
-  </si>
-  <si>
-    <t xml:space="preserve">количеством денежных средств взятого долга в рост</t>
-  </si>
-  <si>
-    <t xml:space="preserve">мягкому, но шумовому фону</t>
-  </si>
-  <si>
-    <t xml:space="preserve">мягкой, но шумовой обстановке</t>
-  </si>
-  <si>
-    <t xml:space="preserve">происходить в эфире</t>
-  </si>
-  <si>
-    <t xml:space="preserve">происходить во время съёмки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">у меня интересуются</t>
-  </si>
-  <si>
-    <t xml:space="preserve">у меня спрашивают</t>
-  </si>
-  <si>
-    <t xml:space="preserve">одного из корпусов гостиничного</t>
-  </si>
-  <si>
-    <t xml:space="preserve">одного из зданий гостинничного</t>
-  </si>
-  <si>
-    <t xml:space="preserve">из номеров корпуса</t>
-  </si>
-  <si>
-    <t xml:space="preserve">из указателя здания</t>
-  </si>
-  <si>
-    <t xml:space="preserve">планах компании (возглавляемой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">планах предприятия (возглавляемого</t>
-  </si>
-  <si>
-    <t xml:space="preserve">с тёмным салоном</t>
-  </si>
-  <si>
-    <t xml:space="preserve">с тёмной торговой точкой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">полегла какая-нибудь группировка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">полегло какое-нибудь сообщество</t>
-  </si>
-  <si>
-    <t xml:space="preserve">островов Канарского архипелага</t>
-  </si>
-  <si>
-    <t xml:space="preserve">островов Канарского материка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">всю установленную аппаратуру</t>
-  </si>
-  <si>
-    <t xml:space="preserve">все установленные приборы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Материала накопилась масса</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сведений накопилось множество</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="513">
+  <si>
+    <t>обрабатываемой информации, по просторам которой</t>
+  </si>
+  <si>
+    <t>обрабатываемых сведений, по просторам которых</t>
+  </si>
+  <si>
+    <t>соответствующей сопроводительной информацией</t>
+  </si>
+  <si>
+    <t>соответствующими сопроводительными сведениями</t>
+  </si>
+  <si>
+    <t>должной информации, поступившей</t>
+  </si>
+  <si>
+    <t>должных сведений, поступивших</t>
+  </si>
+  <si>
+    <t>опасности информации, которой</t>
+  </si>
+  <si>
+    <t>опасности сведений, которыми</t>
+  </si>
+  <si>
+    <t>Кстати о комплексе</t>
+  </si>
+  <si>
+    <t>Кстати о учреждении</t>
+  </si>
+  <si>
+    <t>выехавший на операцию</t>
+  </si>
+  <si>
+    <t>выехавший на захват</t>
+  </si>
+  <si>
+    <t>то в редких компаниях</t>
+  </si>
+  <si>
+    <t>то в редких общностях</t>
+  </si>
+  <si>
+    <t>от теперешней компании</t>
+  </si>
+  <si>
+    <t>от теперешнего круга</t>
+  </si>
+  <si>
+    <t>присутствие в их компании нужно</t>
+  </si>
+  <si>
+    <t>присутствие в их общности нужно</t>
+  </si>
+  <si>
+    <t>в компании ещё нескольких</t>
+  </si>
+  <si>
+    <t>в кругу ещё нескольких</t>
+  </si>
+  <si>
+    <t>приездами разных компаний</t>
+  </si>
+  <si>
+    <t>приездами разных общностей</t>
+  </si>
+  <si>
+    <t>невозможных компаний, в</t>
+  </si>
+  <si>
+    <t>невозможных общностей, в</t>
+  </si>
+  <si>
+    <t>суммой фактического кредита</t>
+  </si>
+  <si>
+    <t>количеством денежных средств взятого долга в рост</t>
+  </si>
+  <si>
+    <t>мягкому, но шумовому фону</t>
+  </si>
+  <si>
+    <t>мягкой, но шумовой обстановке</t>
+  </si>
+  <si>
+    <t>происходить в эфире</t>
+  </si>
+  <si>
+    <t>происходить во время съёмки</t>
+  </si>
+  <si>
+    <t>у меня интересуются</t>
+  </si>
+  <si>
+    <t>у меня спрашивают</t>
+  </si>
+  <si>
+    <t>одного из корпусов гостиничного</t>
+  </si>
+  <si>
+    <t>одного из зданий гостинничного</t>
+  </si>
+  <si>
+    <t>из номеров корпуса</t>
+  </si>
+  <si>
+    <t>из указателя здания</t>
+  </si>
+  <si>
+    <t>планах компании (возглавляемой</t>
+  </si>
+  <si>
+    <t>планах предприятия (возглавляемого</t>
+  </si>
+  <si>
+    <t>с тёмным салоном</t>
+  </si>
+  <si>
+    <t>с тёмной торговой точкой</t>
+  </si>
+  <si>
+    <t>полегла какая-нибудь группировка</t>
+  </si>
+  <si>
+    <t>полегло какое-нибудь сообщество</t>
+  </si>
+  <si>
+    <t>островов Канарского архипелага</t>
+  </si>
+  <si>
+    <t>островов Канарского материка</t>
+  </si>
+  <si>
+    <t>всю установленную аппаратуру</t>
+  </si>
+  <si>
+    <t>все установленные приборы</t>
+  </si>
+  <si>
+    <t>Материала накопилась масса</t>
+  </si>
+  <si>
+    <t>сведений накопилось множество</t>
   </si>
   <si>
     <t xml:space="preserve">при организации покушения </t>
@@ -184,766 +192,766 @@
     <t xml:space="preserve">со структурами, подобными нашей </t>
   </si>
   <si>
-    <t xml:space="preserve">с сообществами, подобными нашему</t>
+    <t>с сообществами, подобными нашему</t>
   </si>
   <si>
     <t xml:space="preserve">планомерную акцию, проводящуюся </t>
   </si>
   <si>
-    <t xml:space="preserve">заранее подготовленное действие, проводящееся</t>
+    <t>заранее подготовленное действие, проводящееся</t>
   </si>
   <si>
     <t xml:space="preserve">пускаясь по серпантинам </t>
   </si>
   <si>
-    <t xml:space="preserve">пускаясь по извилистым дорогам</t>
+    <t>пускаясь по извилистым дорогам</t>
   </si>
   <si>
     <t xml:space="preserve">горного серпантина </t>
   </si>
   <si>
-    <t xml:space="preserve">горных извилистых дорог</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Измайловском комплексе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Измайловском учреждении</t>
-  </si>
-  <si>
-    <t xml:space="preserve">констатируюсь отбросом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">являюсь отбросом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в подобных компаниях</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в подобных общностях</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Компания была тёплая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Общность была тёплая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Грише и компании</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Грише и дружине</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в их компании</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в их кругу</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вежливо поинтересовавшись</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вежливо спросили</t>
-  </si>
-  <si>
-    <t xml:space="preserve">больше, поинтересовавшись</t>
-  </si>
-  <si>
-    <t xml:space="preserve">больше, спросив</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вёлся ремонт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">велась отделка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">этой «корпорации»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">этого «предприятия»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">маломощным патроном</t>
-  </si>
-  <si>
-    <t xml:space="preserve">маломощной пулей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">низшим структурам</t>
-  </si>
-  <si>
-    <t xml:space="preserve">низшим учреждениям</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«бригадами»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«дружинами»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«бригадам» структурами</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«дружинам» преступным сообществам</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Медведковской» бригады</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Медведковского» отряда</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«оброс» спецификой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«оброс» опытом исполнения особых поручений</t>
-  </si>
-  <si>
-    <t xml:space="preserve">а дисциплина из железной перешла в рамки репрессивной</t>
-  </si>
-  <si>
-    <t xml:space="preserve">а железное соблюдение правил перешло в рамки угнетения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">был оформлен паспорт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">был указан паспорт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в командах под руководством</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в отрядах под руководством</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в свою команду я</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в свой отряд я</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в этой «корпорации»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в этом «предприятии»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">главшпаном этой уже организованной структуры</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вожаком этой уже собранной дружины</t>
-  </si>
-  <si>
-    <t xml:space="preserve">грифы, находящихся там документов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">уровни тайн, находящихся там документов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">делили одну команду</t>
-  </si>
-  <si>
-    <t xml:space="preserve">делили одно содружество</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дисциплина!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обязательное соблюдение правил!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">до выстрела последовала команда</t>
-  </si>
-  <si>
-    <t xml:space="preserve">до выстрела последовал приказ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дошедшая до них информация</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дошедшие до них сведения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дружественной бригадой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дружественным отрядом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дружественных «команд»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дружественных «отрядов»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">жаркому пару</t>
-  </si>
-  <si>
-    <t xml:space="preserve">из «бригады»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">из «отряда»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в забытый кем-то пакет</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в забытую кем-то посылку</t>
-  </si>
-  <si>
-    <t xml:space="preserve">из номера в коридор</t>
-  </si>
-  <si>
-    <t xml:space="preserve">из палаты в коридор</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Из номера приходилось</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Из палаты приходилось</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Имеющаяся техника либо не подходила, либо была в недостаточном количестве, либо её просто было</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Имеющиеся средства либо не подходили, либо были в недостаточном количестве, либо их просто было</t>
-  </si>
-  <si>
-    <t xml:space="preserve">имея такую команду и все</t>
-  </si>
-  <si>
-    <t xml:space="preserve">имея такой отряд и все</t>
-  </si>
-  <si>
-    <t xml:space="preserve">интересов, заинтересованность</t>
-  </si>
-  <si>
-    <t xml:space="preserve">увлечений, одержимость</t>
-  </si>
-  <si>
-    <t xml:space="preserve">информацией, хоть и небольшой, в частности, обо мне, пусть даже и составленной</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сведениями, хоть и небольшими, в частности, обо мне, пусть даже и составленных</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Картина на удивление мерзка,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Зрелище на удивление мерзко,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">кем-то оплаченные номера</t>
-  </si>
-  <si>
-    <t xml:space="preserve">кем-то оплаченные палаты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">команда у него была неслабая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">отряд у него был неслабый</t>
-  </si>
-  <si>
-    <t xml:space="preserve">команду надзора меняют</t>
-  </si>
-  <si>
-    <t xml:space="preserve">отряд надзора меняют</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Комитетовский банк</t>
-  </si>
-  <si>
-    <t xml:space="preserve">денежное хранилище Совета</t>
-  </si>
-  <si>
-    <t xml:space="preserve">кучей номеров и</t>
-  </si>
-  <si>
-    <t xml:space="preserve">кучей палат и</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лелеемую еврейскими банкирами тему</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лелеемый еврейскими банкирами вопрос</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Лёша-Солдат</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Лёша-Воин</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лучшая импровизация именно та, которую</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лучшее произвведение искусства именно то, которое</t>
-  </si>
-  <si>
-    <t xml:space="preserve">массе предложил</t>
-  </si>
-  <si>
-    <t xml:space="preserve">множеству предложил</t>
-  </si>
-  <si>
-    <t xml:space="preserve">меня без формы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">меня без военного одеяния</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нашей «бригады»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нашего «отряда»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ни одна хорошо разработанная схема, как бы жестко ее ни приводили в жизнь, как бы скрупулёзно ее</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разработанный чертёж, как бы жёстко его ни приводили в жизнь, как бы тщательно за ним не следили</t>
-  </si>
-  <si>
-    <t xml:space="preserve">новой субкультуры, отголоски которой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нового общественного течения, отголоски которого</t>
-  </si>
-  <si>
-    <t xml:space="preserve">новый зал, осматривая его</t>
-  </si>
-  <si>
-    <t xml:space="preserve">новые хоромы, осматривая их</t>
-  </si>
-  <si>
-    <t xml:space="preserve">номер, снимаемый</t>
-  </si>
-  <si>
-    <t xml:space="preserve">палату, снимаемую</t>
-  </si>
-  <si>
-    <t xml:space="preserve">о процентах которого я знал чётко одно – их</t>
-  </si>
-  <si>
-    <t xml:space="preserve">о лихве которого я знал чётко одно – её</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обеих «корпорациях»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обоих «предприятиях»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">одной из его команд</t>
-  </si>
-  <si>
-    <t xml:space="preserve">одним из его отрядов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">оказался строящийся концертный зал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">оказались строящиеся хоромы для выступлений</t>
-  </si>
-  <si>
-    <t xml:space="preserve">он оперировал супругу</t>
-  </si>
-  <si>
-    <t xml:space="preserve">он самолично проводил врачебные вмешательства ножом супруге</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ответ его команда без</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ответ его приказа без</t>
-  </si>
-  <si>
-    <t xml:space="preserve">отдельная тема, вряд ли нужная</t>
-  </si>
-  <si>
-    <t xml:space="preserve">отдельный вопрос, вряд ли нужный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">отработанная легенда заурчала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">отработанный рассказ с целью внедрения заурчал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">официальной версии</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обнародованной вести</t>
-  </si>
-  <si>
-    <t xml:space="preserve">оформленной всевозможными документами</t>
-  </si>
-  <si>
-    <t xml:space="preserve">узаконенной всевозможными письменными свидетельствами</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ошарашенные ждали команды</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ошарашенные ждали приказа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">пару «длинных»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">несколько «длинных»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в своём личном зале</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в своих личных хоромах</t>
-  </si>
-  <si>
-    <t xml:space="preserve">пару «точек»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">несколько «точек»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">пару каких-то</t>
-  </si>
-  <si>
-    <t xml:space="preserve">несколько каких-то</t>
-  </si>
-  <si>
-    <t xml:space="preserve">пару магнитофонов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">несколько магнитофонов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">пару представляли</t>
-  </si>
-  <si>
-    <t xml:space="preserve">семью представляли</t>
-  </si>
-  <si>
-    <t xml:space="preserve">помогать из процентов, которые даёт эта сумма</t>
-  </si>
-  <si>
-    <t xml:space="preserve">помогать их лихвы, которую дают этот денежный общак</t>
-  </si>
-  <si>
-    <t xml:space="preserve">приносили положительные моменты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">приносили положительные чувства</t>
-  </si>
-  <si>
-    <t xml:space="preserve">причитающуюся моей команде</t>
-  </si>
-  <si>
-    <t xml:space="preserve">причитающуюся моему отряду</t>
-  </si>
-  <si>
-    <t xml:space="preserve">просто организация была не</t>
-  </si>
-  <si>
-    <t xml:space="preserve">просто подготовка была не</t>
-  </si>
-  <si>
-    <t xml:space="preserve">психики – она архинормальна, архистабильна, хотя и вся расшатана</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разум – она крайне обычен, крайне безотказен, хотя и весь расшатан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">пять номеров,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">пять палат,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">с новой «фигурой»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">с новым «человеком»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">с разными «командами»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">с разными «отрядами»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сидя в номере</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сидя в палате</t>
-  </si>
-  <si>
-    <t xml:space="preserve">собрали свои команды</t>
-  </si>
-  <si>
-    <t xml:space="preserve">собрали свои отряды</t>
-  </si>
-  <si>
-    <t xml:space="preserve">спортивная команда</t>
-  </si>
-  <si>
-    <t xml:space="preserve">спортивное содружество</t>
-  </si>
-  <si>
-    <t xml:space="preserve">спортивных команд</t>
-  </si>
-  <si>
-    <t xml:space="preserve">спортивных содружеств</t>
-  </si>
-  <si>
-    <t xml:space="preserve">счастливо выглядевшей пары</t>
-  </si>
-  <si>
-    <t xml:space="preserve">счастливо выглядевшей семьи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">той репрессивной дисциплины, которая властвовала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">тех угнетающих правил, которые властвовали</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Только команды ждёт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Только приказа ждёт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">только оформлялся</t>
-  </si>
-  <si>
-    <t xml:space="preserve">только узаканивался</t>
+    <t>горных извилистых дорог</t>
+  </si>
+  <si>
+    <t>Измайловском комплексе</t>
+  </si>
+  <si>
+    <t>Измайловском учреждении</t>
+  </si>
+  <si>
+    <t>констатируюсь отбросом</t>
+  </si>
+  <si>
+    <t>являюсь отбросом</t>
+  </si>
+  <si>
+    <t>в подобных компаниях</t>
+  </si>
+  <si>
+    <t>в подобных общностях</t>
+  </si>
+  <si>
+    <t>Компания была тёплая</t>
+  </si>
+  <si>
+    <t>Общность была тёплая</t>
+  </si>
+  <si>
+    <t>Грише и компании</t>
+  </si>
+  <si>
+    <t>Грише и дружине</t>
+  </si>
+  <si>
+    <t>в их компании</t>
+  </si>
+  <si>
+    <t>в их кругу</t>
+  </si>
+  <si>
+    <t>вежливо поинтересовавшись</t>
+  </si>
+  <si>
+    <t>вежливо спросили</t>
+  </si>
+  <si>
+    <t>больше, поинтересовавшись</t>
+  </si>
+  <si>
+    <t>больше, спросив</t>
+  </si>
+  <si>
+    <t>вёлся ремонт</t>
+  </si>
+  <si>
+    <t>велась отделка</t>
+  </si>
+  <si>
+    <t>этой «корпорации»</t>
+  </si>
+  <si>
+    <t>этого «предприятия»</t>
+  </si>
+  <si>
+    <t>маломощным патроном</t>
+  </si>
+  <si>
+    <t>маломощной пулей</t>
+  </si>
+  <si>
+    <t>низшим структурам</t>
+  </si>
+  <si>
+    <t>низшим учреждениям</t>
+  </si>
+  <si>
+    <t>«бригадами»</t>
+  </si>
+  <si>
+    <t>«дружинами»</t>
+  </si>
+  <si>
+    <t>«бригадам» структурами</t>
+  </si>
+  <si>
+    <t>«дружинам» преступным сообществам</t>
+  </si>
+  <si>
+    <t>«Медведковской» бригады</t>
+  </si>
+  <si>
+    <t>«Медведковского» отряда</t>
+  </si>
+  <si>
+    <t>«оброс» спецификой</t>
+  </si>
+  <si>
+    <t>«оброс» опытом исполнения особых поручений</t>
+  </si>
+  <si>
+    <t>а дисциплина из железной перешла в рамки репрессивной</t>
+  </si>
+  <si>
+    <t>а железное соблюдение правил перешло в рамки угнетения</t>
+  </si>
+  <si>
+    <t>был оформлен паспорт</t>
+  </si>
+  <si>
+    <t>был указан паспорт</t>
+  </si>
+  <si>
+    <t>в командах под руководством</t>
+  </si>
+  <si>
+    <t>в отрядах под руководством</t>
+  </si>
+  <si>
+    <t>в свою команду я</t>
+  </si>
+  <si>
+    <t>в свой отряд я</t>
+  </si>
+  <si>
+    <t>в этой «корпорации»</t>
+  </si>
+  <si>
+    <t>в этом «предприятии»</t>
+  </si>
+  <si>
+    <t>главшпаном этой уже организованной структуры</t>
+  </si>
+  <si>
+    <t>вожаком этой уже собранной дружины</t>
+  </si>
+  <si>
+    <t>грифы, находящихся там документов</t>
+  </si>
+  <si>
+    <t>уровни тайн, находящихся там документов</t>
+  </si>
+  <si>
+    <t>делили одну команду</t>
+  </si>
+  <si>
+    <t>делили одно содружество</t>
+  </si>
+  <si>
+    <t>дисциплина!</t>
+  </si>
+  <si>
+    <t>обязательное соблюдение правил!</t>
+  </si>
+  <si>
+    <t>до выстрела последовала команда</t>
+  </si>
+  <si>
+    <t>до выстрела последовал приказ</t>
+  </si>
+  <si>
+    <t>дошедшая до них информация</t>
+  </si>
+  <si>
+    <t>дошедшие до них сведения</t>
+  </si>
+  <si>
+    <t>дружественной бригадой</t>
+  </si>
+  <si>
+    <t>дружественным отрядом</t>
+  </si>
+  <si>
+    <t>дружественных «команд»</t>
+  </si>
+  <si>
+    <t>дружественных «отрядов»</t>
+  </si>
+  <si>
+    <t>жаркому пару</t>
+  </si>
+  <si>
+    <t>из «бригады»</t>
+  </si>
+  <si>
+    <t>из «отряда»</t>
+  </si>
+  <si>
+    <t>в забытый кем-то пакет</t>
+  </si>
+  <si>
+    <t>в забытую кем-то посылку</t>
+  </si>
+  <si>
+    <t>из номера в коридор</t>
+  </si>
+  <si>
+    <t>из палаты в коридор</t>
+  </si>
+  <si>
+    <t>Из номера приходилось</t>
+  </si>
+  <si>
+    <t>Из палаты приходилось</t>
+  </si>
+  <si>
+    <t>Имеющаяся техника либо не подходила, либо была в недостаточном количестве, либо её просто было</t>
+  </si>
+  <si>
+    <t>Имеющиеся средства либо не подходили, либо были в недостаточном количестве, либо их просто было</t>
+  </si>
+  <si>
+    <t>имея такую команду и все</t>
+  </si>
+  <si>
+    <t>имея такой отряд и все</t>
+  </si>
+  <si>
+    <t>интересов, заинтересованность</t>
+  </si>
+  <si>
+    <t>увлечений, одержимость</t>
+  </si>
+  <si>
+    <t>информацией, хоть и небольшой, в частности, обо мне, пусть даже и составленной</t>
+  </si>
+  <si>
+    <t>сведениями, хоть и небольшими, в частности, обо мне, пусть даже и составленных</t>
+  </si>
+  <si>
+    <t>Картина на удивление мерзка,</t>
+  </si>
+  <si>
+    <t>Зрелище на удивление мерзко,</t>
+  </si>
+  <si>
+    <t>кем-то оплаченные номера</t>
+  </si>
+  <si>
+    <t>кем-то оплаченные палаты</t>
+  </si>
+  <si>
+    <t>команда у него была неслабая</t>
+  </si>
+  <si>
+    <t>отряд у него был неслабый</t>
+  </si>
+  <si>
+    <t>команду надзора меняют</t>
+  </si>
+  <si>
+    <t>отряд надзора меняют</t>
+  </si>
+  <si>
+    <t>Комитетовский банк</t>
+  </si>
+  <si>
+    <t>денежное хранилище Совета</t>
+  </si>
+  <si>
+    <t>кучей номеров и</t>
+  </si>
+  <si>
+    <t>кучей палат и</t>
+  </si>
+  <si>
+    <t>лелеемую еврейскими банкирами тему</t>
+  </si>
+  <si>
+    <t>лелеемый еврейскими банкирами вопрос</t>
+  </si>
+  <si>
+    <t>Лёша-Солдат</t>
+  </si>
+  <si>
+    <t>Лёша-Воин</t>
+  </si>
+  <si>
+    <t>лучшая импровизация именно та, которую</t>
+  </si>
+  <si>
+    <t>лучшее произвведение искусства именно то, которое</t>
+  </si>
+  <si>
+    <t>массе предложил</t>
+  </si>
+  <si>
+    <t>множеству предложил</t>
+  </si>
+  <si>
+    <t>меня без формы</t>
+  </si>
+  <si>
+    <t>меня без военного одеяния</t>
+  </si>
+  <si>
+    <t>нашей «бригады»</t>
+  </si>
+  <si>
+    <t>нашего «отряда»</t>
+  </si>
+  <si>
+    <t>ни одна хорошо разработанная схема, как бы жестко ее ни приводили в жизнь, как бы скрупулёзно ее</t>
+  </si>
+  <si>
+    <t>разработанный чертёж, как бы жёстко его ни приводили в жизнь, как бы тщательно за ним не следили</t>
+  </si>
+  <si>
+    <t>новой субкультуры, отголоски которой</t>
+  </si>
+  <si>
+    <t>нового общественного течения, отголоски которого</t>
+  </si>
+  <si>
+    <t>новый зал, осматривая его</t>
+  </si>
+  <si>
+    <t>новые хоромы, осматривая их</t>
+  </si>
+  <si>
+    <t>номер, снимаемый</t>
+  </si>
+  <si>
+    <t>палату, снимаемую</t>
+  </si>
+  <si>
+    <t>о процентах которого я знал чётко одно – их</t>
+  </si>
+  <si>
+    <t>о лихве которого я знал чётко одно – её</t>
+  </si>
+  <si>
+    <t>обеих «корпорациях»</t>
+  </si>
+  <si>
+    <t>обоих «предприятиях»</t>
+  </si>
+  <si>
+    <t>одной из его команд</t>
+  </si>
+  <si>
+    <t>одним из его отрядов</t>
+  </si>
+  <si>
+    <t>оказался строящийся концертный зал</t>
+  </si>
+  <si>
+    <t>оказались строящиеся хоромы для выступлений</t>
+  </si>
+  <si>
+    <t>он оперировал супругу</t>
+  </si>
+  <si>
+    <t>он самолично проводил врачебные вмешательства ножом супруге</t>
+  </si>
+  <si>
+    <t>ответ его команда без</t>
+  </si>
+  <si>
+    <t>ответ его приказа без</t>
+  </si>
+  <si>
+    <t>отдельная тема, вряд ли нужная</t>
+  </si>
+  <si>
+    <t>отдельный вопрос, вряд ли нужный</t>
+  </si>
+  <si>
+    <t>отработанная легенда заурчала</t>
+  </si>
+  <si>
+    <t>отработанный рассказ с целью внедрения заурчал</t>
+  </si>
+  <si>
+    <t>официальной версии</t>
+  </si>
+  <si>
+    <t>обнародованной вести</t>
+  </si>
+  <si>
+    <t>оформленной всевозможными документами</t>
+  </si>
+  <si>
+    <t>узаконенной всевозможными письменными свидетельствами</t>
+  </si>
+  <si>
+    <t>ошарашенные ждали команды</t>
+  </si>
+  <si>
+    <t>ошарашенные ждали приказа</t>
+  </si>
+  <si>
+    <t>пару «длинных»</t>
+  </si>
+  <si>
+    <t>несколько «длинных»</t>
+  </si>
+  <si>
+    <t>в своём личном зале</t>
+  </si>
+  <si>
+    <t>в своих личных хоромах</t>
+  </si>
+  <si>
+    <t>пару «точек»</t>
+  </si>
+  <si>
+    <t>несколько «точек»</t>
+  </si>
+  <si>
+    <t>пару каких-то</t>
+  </si>
+  <si>
+    <t>несколько каких-то</t>
+  </si>
+  <si>
+    <t>пару магнитофонов</t>
+  </si>
+  <si>
+    <t>несколько магнитофонов</t>
+  </si>
+  <si>
+    <t>пару представляли</t>
+  </si>
+  <si>
+    <t>семью представляли</t>
+  </si>
+  <si>
+    <t>помогать из процентов, которые даёт эта сумма</t>
+  </si>
+  <si>
+    <t>помогать их лихвы, которую дают этот денежный общак</t>
+  </si>
+  <si>
+    <t>приносили положительные моменты</t>
+  </si>
+  <si>
+    <t>приносили положительные чувства</t>
+  </si>
+  <si>
+    <t>причитающуюся моей команде</t>
+  </si>
+  <si>
+    <t>причитающуюся моему отряду</t>
+  </si>
+  <si>
+    <t>просто организация была не</t>
+  </si>
+  <si>
+    <t>просто подготовка была не</t>
+  </si>
+  <si>
+    <t>психики – она архинормальна, архистабильна, хотя и вся расшатана</t>
+  </si>
+  <si>
+    <t>разум – она крайне обычен, крайне безотказен, хотя и весь расшатан</t>
+  </si>
+  <si>
+    <t>пять номеров,</t>
+  </si>
+  <si>
+    <t>пять палат,</t>
+  </si>
+  <si>
+    <t>с новой «фигурой»</t>
+  </si>
+  <si>
+    <t>с новым «человеком»</t>
+  </si>
+  <si>
+    <t>с разными «командами»</t>
+  </si>
+  <si>
+    <t>с разными «отрядами»</t>
+  </si>
+  <si>
+    <t>сидя в номере</t>
+  </si>
+  <si>
+    <t>сидя в палате</t>
+  </si>
+  <si>
+    <t>собрали свои команды</t>
+  </si>
+  <si>
+    <t>собрали свои отряды</t>
+  </si>
+  <si>
+    <t>спортивная команда</t>
+  </si>
+  <si>
+    <t>спортивное содружество</t>
+  </si>
+  <si>
+    <t>спортивных команд</t>
+  </si>
+  <si>
+    <t>спортивных содружеств</t>
+  </si>
+  <si>
+    <t>счастливо выглядевшей пары</t>
+  </si>
+  <si>
+    <t>счастливо выглядевшей семьи</t>
+  </si>
+  <si>
+    <t>той репрессивной дисциплины, которая властвовала</t>
+  </si>
+  <si>
+    <t>тех угнетающих правил, которые властвовали</t>
+  </si>
+  <si>
+    <t>Только команды ждёт</t>
+  </si>
+  <si>
+    <t>Только приказа ждёт</t>
+  </si>
+  <si>
+    <t>только оформлялся</t>
+  </si>
+  <si>
+    <t>только узаканивался</t>
   </si>
   <si>
     <t xml:space="preserve">трогать эту сумму </t>
   </si>
   <si>
-    <t xml:space="preserve">трогать эти денежные средства</t>
-  </si>
-  <si>
-    <t xml:space="preserve">увлекающаяся натура</t>
-  </si>
-  <si>
-    <t xml:space="preserve">увлекающийся по природе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">уплывали в номера</t>
-  </si>
-  <si>
-    <t xml:space="preserve">уплывали в палаты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Часть бывшей команды</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Часть бывшего содружества</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЧОП оформлялся</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЧОП узаканивался</t>
-  </si>
-  <si>
-    <t xml:space="preserve">что до номера им</t>
-  </si>
-  <si>
-    <t xml:space="preserve">что до палаты им</t>
-  </si>
-  <si>
-    <t xml:space="preserve">что команды от него</t>
-  </si>
-  <si>
-    <t xml:space="preserve">что приказа от него</t>
-  </si>
-  <si>
-    <t xml:space="preserve">один из известных офисов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">одно из известных рабочих помещений</t>
-  </si>
-  <si>
-    <t xml:space="preserve">хорошую и надежную команду</t>
-  </si>
-  <si>
-    <t xml:space="preserve">хороший и надёжный отряд</t>
-  </si>
-  <si>
-    <t xml:space="preserve">какой-то спирали, восходящей или нисходящий</t>
-  </si>
-  <si>
-    <t xml:space="preserve">какого-то завитка, восходящего или нисходящего</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в философствования, фантазию</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в обсуждение мировоззрения, воображение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в одну из крупнейших на тот период фирм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в одно из крупнейших на тот временной промежуток предприятий</t>
-  </si>
-  <si>
-    <t xml:space="preserve">о небольшой семейной трагедии</t>
-  </si>
-  <si>
-    <t xml:space="preserve">о небольшом семейном бедствии</t>
-  </si>
-  <si>
-    <t xml:space="preserve">весь магазин разрядили</t>
-  </si>
-  <si>
-    <t xml:space="preserve">всю обойму разрядили</t>
-  </si>
-  <si>
-    <t xml:space="preserve">от своей «бригады»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">от своего «отряда»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">мой авторитет в этом плане оказался непререкаемым</t>
-  </si>
-  <si>
-    <t xml:space="preserve">моя значимость в этом замысле оказалась непререкаемой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">печатный текст говорил</t>
-  </si>
-  <si>
-    <t xml:space="preserve">печатная письменность говорила</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Что это была за схема</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Что это был за чертёж</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Материал чемодана</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сырьё чемодана</t>
-  </si>
-  <si>
-    <t xml:space="preserve">линия монолога встала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">направление размышления встало</t>
-  </si>
-  <si>
-    <t xml:space="preserve">есть версия, что</t>
-  </si>
-  <si>
-    <t xml:space="preserve">есть предположение, что</t>
-  </si>
-  <si>
-    <t xml:space="preserve">жизнедеятельность «бригады»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">жизнедеятельность «отряда»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">плюс «на</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дополнительно «на</t>
-  </si>
-  <si>
-    <t xml:space="preserve">любая другая структура,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">любое другое сообщество,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«аудиторскую» проверку</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«полную» проверку</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сэкономить на их долях</t>
-  </si>
-  <si>
-    <t xml:space="preserve">уменьшить их доли</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ему в пику</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ему в острие</t>
-  </si>
-  <si>
-    <t xml:space="preserve">повторил всю процедуру</t>
-  </si>
-  <si>
-    <t xml:space="preserve">повторил всё действие</t>
-  </si>
-  <si>
-    <t xml:space="preserve">этот фактор и должен был</t>
-  </si>
-  <si>
-    <t xml:space="preserve">это обстоятельство и должно было</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Спецназ перевалился</t>
-  </si>
-  <si>
-    <t xml:space="preserve">особое подразделение перевалилось</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вологодский конвой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вологодское сопровождение под стражей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">процедуру не представлялось</t>
-  </si>
-  <si>
-    <t xml:space="preserve">действие не представлялось</t>
-  </si>
-  <si>
-    <t xml:space="preserve">наша, вовремя созданная контора</t>
-  </si>
-  <si>
-    <t xml:space="preserve">наше, вовремя созданное учреждение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">накопилась в избытке информация</t>
-  </si>
-  <si>
-    <t xml:space="preserve">накопились в избытке сведения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">упала дисциплина</t>
-  </si>
-  <si>
-    <t xml:space="preserve">соблюдение правил упало</t>
-  </si>
-  <si>
-    <t xml:space="preserve">поддерживать эту самую дисциплину</t>
-  </si>
-  <si>
-    <t xml:space="preserve">поддерживать это самое соблюдение правил</t>
+    <t>трогать эти денежные средства</t>
+  </si>
+  <si>
+    <t>увлекающаяся натура</t>
+  </si>
+  <si>
+    <t>увлекающийся по природе</t>
+  </si>
+  <si>
+    <t>уплывали в номера</t>
+  </si>
+  <si>
+    <t>уплывали в палаты</t>
+  </si>
+  <si>
+    <t>Часть бывшей команды</t>
+  </si>
+  <si>
+    <t>Часть бывшего содружества</t>
+  </si>
+  <si>
+    <t>ЧОП оформлялся</t>
+  </si>
+  <si>
+    <t>ЧОП узаканивался</t>
+  </si>
+  <si>
+    <t>что до номера им</t>
+  </si>
+  <si>
+    <t>что до палаты им</t>
+  </si>
+  <si>
+    <t>что команды от него</t>
+  </si>
+  <si>
+    <t>что приказа от него</t>
+  </si>
+  <si>
+    <t>один из известных офисов</t>
+  </si>
+  <si>
+    <t>одно из известных рабочих помещений</t>
+  </si>
+  <si>
+    <t>хорошую и надежную команду</t>
+  </si>
+  <si>
+    <t>хороший и надёжный отряд</t>
+  </si>
+  <si>
+    <t>какой-то спирали, восходящей или нисходящий</t>
+  </si>
+  <si>
+    <t>какого-то завитка, восходящего или нисходящего</t>
+  </si>
+  <si>
+    <t>в философствования, фантазию</t>
+  </si>
+  <si>
+    <t>в обсуждение мировоззрения, воображение</t>
+  </si>
+  <si>
+    <t>в одну из крупнейших на тот период фирм</t>
+  </si>
+  <si>
+    <t>в одно из крупнейших на тот временной промежуток предприятий</t>
+  </si>
+  <si>
+    <t>о небольшой семейной трагедии</t>
+  </si>
+  <si>
+    <t>о небольшом семейном бедствии</t>
+  </si>
+  <si>
+    <t>весь магазин разрядили</t>
+  </si>
+  <si>
+    <t>всю обойму разрядили</t>
+  </si>
+  <si>
+    <t>от своей «бригады»</t>
+  </si>
+  <si>
+    <t>от своего «отряда»</t>
+  </si>
+  <si>
+    <t>мой авторитет в этом плане оказался непререкаемым</t>
+  </si>
+  <si>
+    <t>моя значимость в этом замысле оказалась непререкаемой</t>
+  </si>
+  <si>
+    <t>печатный текст говорил</t>
+  </si>
+  <si>
+    <t>печатная письменность говорила</t>
+  </si>
+  <si>
+    <t>Что это была за схема</t>
+  </si>
+  <si>
+    <t>Что это был за чертёж</t>
+  </si>
+  <si>
+    <t>Материал чемодана</t>
+  </si>
+  <si>
+    <t>Сырьё чемодана</t>
+  </si>
+  <si>
+    <t>линия монолога встала</t>
+  </si>
+  <si>
+    <t>направление размышления встало</t>
+  </si>
+  <si>
+    <t>есть версия, что</t>
+  </si>
+  <si>
+    <t>есть предположение, что</t>
+  </si>
+  <si>
+    <t>жизнедеятельность «бригады»</t>
+  </si>
+  <si>
+    <t>жизнедеятельность «отряда»</t>
+  </si>
+  <si>
+    <t>плюс «на</t>
+  </si>
+  <si>
+    <t>дополнительно «на</t>
+  </si>
+  <si>
+    <t>любая другая структура,</t>
+  </si>
+  <si>
+    <t>любое другое сообщество,</t>
+  </si>
+  <si>
+    <t>«аудиторскую» проверку</t>
+  </si>
+  <si>
+    <t>«полную» проверку</t>
+  </si>
+  <si>
+    <t>сэкономить на их долях</t>
+  </si>
+  <si>
+    <t>уменьшить их доли</t>
+  </si>
+  <si>
+    <t>ему в пику</t>
+  </si>
+  <si>
+    <t>ему в острие</t>
+  </si>
+  <si>
+    <t>повторил всю процедуру</t>
+  </si>
+  <si>
+    <t>повторил всё действие</t>
+  </si>
+  <si>
+    <t>этот фактор и должен был</t>
+  </si>
+  <si>
+    <t>это обстоятельство и должно было</t>
+  </si>
+  <si>
+    <t>Спецназ перевалился</t>
+  </si>
+  <si>
+    <t>особое подразделение перевалилось</t>
+  </si>
+  <si>
+    <t>Вологодский конвой</t>
+  </si>
+  <si>
+    <t>Вологодское сопровождение под стражей</t>
+  </si>
+  <si>
+    <t>процедуру не представлялось</t>
+  </si>
+  <si>
+    <t>действие не представлялось</t>
+  </si>
+  <si>
+    <t>наша, вовремя созданная контора</t>
+  </si>
+  <si>
+    <t>наше, вовремя созданное учреждение</t>
+  </si>
+  <si>
+    <t>накопилась в избытке информация</t>
+  </si>
+  <si>
+    <t>накопились в избытке сведения</t>
+  </si>
+  <si>
+    <t>упала дисциплина</t>
+  </si>
+  <si>
+    <t>соблюдение правил упало</t>
+  </si>
+  <si>
+    <t>поддерживать эту самую дисциплину</t>
+  </si>
+  <si>
+    <t>поддерживать это самое соблюдение правил</t>
   </si>
   <si>
     <t xml:space="preserve">Команда эта выковала </t>
   </si>
   <si>
-    <t xml:space="preserve">Сообщество это выковало</t>
+    <t>Сообщество это выковало</t>
   </si>
   <si>
     <t xml:space="preserve">своей «карьеры» </t>
@@ -955,25 +963,25 @@
     <t xml:space="preserve">Софистика не выдумана </t>
   </si>
   <si>
-    <t xml:space="preserve">Учение о относительности не выдумано</t>
+    <t>Учение о относительности не выдумано</t>
   </si>
   <si>
     <t xml:space="preserve">стратегию – провальной </t>
   </si>
   <si>
-    <t xml:space="preserve">замысел – провальным</t>
+    <t>замысел – провальным</t>
   </si>
   <si>
     <t xml:space="preserve">критики, </t>
   </si>
   <si>
-    <t xml:space="preserve">оценки,</t>
+    <t>оценки,</t>
   </si>
   <si>
     <t xml:space="preserve">маленький процент всё же </t>
   </si>
   <si>
-    <t xml:space="preserve">небольшое количество всё же</t>
+    <t>небольшое количество всё же</t>
   </si>
   <si>
     <t xml:space="preserve">Вышедшие из комплекса </t>
@@ -991,25 +999,25 @@
     <t xml:space="preserve">гостиничном Измайловском комплексе </t>
   </si>
   <si>
-    <t xml:space="preserve">гостиничном Измайловском объединении</t>
+    <t>гостиничном Измайловском объединении</t>
   </si>
   <si>
     <t xml:space="preserve">о комплексе АБВГДйка </t>
   </si>
   <si>
-    <t xml:space="preserve">о сооружениях АБВГД</t>
+    <t>о сооружениях АБВГД</t>
   </si>
   <si>
     <t xml:space="preserve">присмотренную и подготовленную позицию </t>
   </si>
   <si>
-    <t xml:space="preserve">присмотренное и подготовленное месторасположение</t>
+    <t>присмотренное и подготовленное месторасположение</t>
   </si>
   <si>
     <t xml:space="preserve">удобная спокойная позиция </t>
   </si>
   <si>
-    <t xml:space="preserve">удобное спокойное месторасположение</t>
+    <t>удобное спокойное месторасположение</t>
   </si>
   <si>
     <t xml:space="preserve">возможную позицию стрелка </t>
@@ -1027,49 +1035,49 @@
     <t xml:space="preserve">Вторые номера сегодня </t>
   </si>
   <si>
-    <t xml:space="preserve">Страхующие сегодня</t>
+    <t>Страхующие сегодня</t>
   </si>
   <si>
     <t xml:space="preserve">его реакции, лениво соглашательской </t>
   </si>
   <si>
-    <t xml:space="preserve">его ответу, лениво соглашательскому</t>
+    <t>его ответу, лениво соглашательскому</t>
   </si>
   <si>
     <t xml:space="preserve">фирмах, фирмочках, банках </t>
   </si>
   <si>
-    <t xml:space="preserve">предприятиях больших и малых, денежных хранилищах</t>
+    <t>предприятиях больших и малых, денежных хранилищах</t>
   </si>
   <si>
     <t xml:space="preserve">произведённый фурор от манеры исполнения превзошёл </t>
   </si>
   <si>
-    <t xml:space="preserve">произведённое торжество от привычки исполнения превзошло</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Номер был очень большой, вместивший</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гостинничные хоромы были очень большие, вместившие</t>
+    <t>произведённое торжество от привычки исполнения превзошло</t>
+  </si>
+  <si>
+    <t>Номер был очень большой, вместивший</t>
+  </si>
+  <si>
+    <t>Гостинничные хоромы были очень большие, вместившие</t>
   </si>
   <si>
     <t xml:space="preserve">балконом снятого номера </t>
   </si>
   <si>
-    <t xml:space="preserve">балконом снятых гостинничных хором</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дефолт, который произвёл</t>
-  </si>
-  <si>
-    <t xml:space="preserve">неплатёжеспособность государства, которое произвело</t>
+    <t>балконом снятых гостинничных хором</t>
+  </si>
+  <si>
+    <t>дефолт, который произвёл</t>
+  </si>
+  <si>
+    <t>неплатёжеспособность государства, которое произвело</t>
   </si>
   <si>
     <t xml:space="preserve">в компании, мелькающей </t>
   </si>
   <si>
-    <t xml:space="preserve">в сообществе, мелькающем</t>
+    <t>в сообществе, мелькающем</t>
   </si>
   <si>
     <t xml:space="preserve">В информации, блещущей </t>
@@ -1113,31 +1121,31 @@
     <t xml:space="preserve">оперируют тем же разговорником </t>
   </si>
   <si>
-    <t xml:space="preserve">используют тот же разговорник</t>
-  </si>
-  <si>
-    <t xml:space="preserve">увидел впервые бизнес-леди</t>
-  </si>
-  <si>
-    <t xml:space="preserve">увидел впервые женщину-предпринимателя</t>
-  </si>
-  <si>
-    <t xml:space="preserve">спас президента компании</t>
-  </si>
-  <si>
-    <t xml:space="preserve">спас главу предприятия</t>
+    <t>используют тот же разговорник</t>
+  </si>
+  <si>
+    <t>увидел впервые бизнес-леди</t>
+  </si>
+  <si>
+    <t>увидел впервые женщину-предпринимателя</t>
+  </si>
+  <si>
+    <t>спас президента компании</t>
+  </si>
+  <si>
+    <t>спас главу предприятия</t>
   </si>
   <si>
     <t xml:space="preserve">красной активной марки </t>
   </si>
   <si>
-    <t xml:space="preserve">красной метки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">соблюдаемой схеме сопровождения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">соблюдаемом укладе сопровождения</t>
+    <t>красной метки</t>
+  </si>
+  <si>
+    <t>соблюдаемой схеме сопровождения</t>
+  </si>
+  <si>
+    <t>соблюдаемом укладе сопровождения</t>
   </si>
   <si>
     <t xml:space="preserve">с самой «конторой» </t>
@@ -1146,34 +1154,34 @@
     <t xml:space="preserve">с самой «службой безопасности государства» </t>
   </si>
   <si>
-    <t xml:space="preserve">отель я попросил</t>
-  </si>
-  <si>
-    <t xml:space="preserve">гостинницу я попросил</t>
+    <t>отель я попросил</t>
+  </si>
+  <si>
+    <t>гостинницу я попросил</t>
   </si>
   <si>
     <t xml:space="preserve">не менять внутри инфраструктуры </t>
   </si>
   <si>
-    <t xml:space="preserve">не менять внутри выстроенных порядков</t>
+    <t>не менять внутри выстроенных порядков</t>
   </si>
   <si>
     <t xml:space="preserve">следственную группу, ведущую </t>
   </si>
   <si>
-    <t xml:space="preserve">следственное подразделение, ведущее</t>
-  </si>
-  <si>
-    <t xml:space="preserve">с помпой и сиренами</t>
-  </si>
-  <si>
-    <t xml:space="preserve">с тревожными оповещением</t>
+    <t>следственное подразделение, ведущее</t>
+  </si>
+  <si>
+    <t>с помпой и сиренами</t>
+  </si>
+  <si>
+    <t>с тревожными оповещением</t>
   </si>
   <si>
     <t xml:space="preserve">кучу материала, собранного </t>
   </si>
   <si>
-    <t xml:space="preserve">кучу сведений, собранных</t>
+    <t>кучу сведений, собранных</t>
   </si>
   <si>
     <t xml:space="preserve">проанализированная и с конкретными выводами, привело к тому, что ею </t>
@@ -1185,13 +1193,13 @@
     <t xml:space="preserve">гастрономическая тема во Франции неповторима </t>
   </si>
   <si>
-    <t xml:space="preserve">вопрос чревоугодия во Франции неповторим</t>
-  </si>
-  <si>
-    <t xml:space="preserve">оставшийся внутри салона</t>
-  </si>
-  <si>
-    <t xml:space="preserve">оставшийся внутри средства передвижения</t>
+    <t>вопрос чревоугодия во Франции неповторим</t>
+  </si>
+  <si>
+    <t>оставшийся внутри салона</t>
+  </si>
+  <si>
+    <t>оставшийся внутри средства передвижения</t>
   </si>
   <si>
     <t xml:space="preserve">Процент, который он предложил </t>
@@ -1200,112 +1208,112 @@
     <t xml:space="preserve">Доход, который он предложил </t>
   </si>
   <si>
-    <t xml:space="preserve">накопленная небольшая сумма позволяла</t>
-  </si>
-  <si>
-    <t xml:space="preserve">накопленное небольшое количество денег позволяло</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сумма, кстати</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Стоимость, кстати</t>
+    <t>накопленная небольшая сумма позволяла</t>
+  </si>
+  <si>
+    <t>накопленное небольшое количество денег позволяло</t>
+  </si>
+  <si>
+    <t>Сумма, кстати</t>
+  </si>
+  <si>
+    <t>Стоимость, кстати</t>
   </si>
   <si>
     <t xml:space="preserve">сумма оплаты не увеличивалась </t>
   </si>
   <si>
-    <t xml:space="preserve">размер оплаты не увеличивался</t>
+    <t>размер оплаты не увеличивался</t>
   </si>
   <si>
     <t xml:space="preserve">копилась, либо передавалась </t>
   </si>
   <si>
-    <t xml:space="preserve">копился, либо передавался</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обговоренная фраза из уст Олега, которая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обговоренное выражение из уст Олега, которое</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стоящей и тоже «Медведковской» бригады, по слухам, чувствующей себя гораздо лучше нашей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">стоящего и тоже «Медведковского» отряда, по слухам, чувствующего себя гораздо лучше нашего</t>
-  </si>
-  <si>
-    <t xml:space="preserve">решал патрон в цельной оболочке, но вот его-то</t>
-  </si>
-  <si>
-    <t xml:space="preserve">решала пуля в цельной оболочке, но вот её-то</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«революция» к тому времени закончилась</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«мятеж» к тому времени закончился</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в их компании или приглашая в свою</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в их кругу или приглашая в свой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Того же типа была история с танзанитами, о которой я узнал после её идиотского окончания и о которой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Того же вида был случай с танзанитами, о котором я узнал после его идиотского окончания и о котором</t>
-  </si>
-  <si>
-    <t xml:space="preserve">позволю ситуации развиться до критической и смогу вовремя ее остановить</t>
-  </si>
-  <si>
-    <t xml:space="preserve">позволю случаю развиться до чрезвычайного и смогу вовремя его остановить</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Картина на удивление мерзка, но показательна</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Зрелище на удивление мерзко, но показательно</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«командами» и «бригадами»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«отрядами» и «дружинами»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">перспективный, здоровый генофонд</t>
-  </si>
-  <si>
-    <t xml:space="preserve">многообещающая, здоровая родовая наследственность</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Один из банков его знакомых дал согласие</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Одно из денежных хранилищ его знакомых дало согласие</t>
-  </si>
-  <si>
-    <t xml:space="preserve">выработка схемы покушения была отложена до момента определения графика появления</t>
-  </si>
-  <si>
-    <t xml:space="preserve">выработка замысла покушения был отложен до мгновения определения расписания и появляения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">этот «пресс»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">эту «раздачу»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в бывшем тогда итальянским рестораном</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в бывшей тогда итальянской харчёвне для дворян</t>
+    <t>копился, либо передавался</t>
+  </si>
+  <si>
+    <t>обговоренная фраза из уст Олега, которая</t>
+  </si>
+  <si>
+    <t>обговоренное выражение из уст Олега, которое</t>
+  </si>
+  <si>
+    <t>стоящей и тоже «Медведковской» бригады, по слухам, чувствующей себя гораздо лучше нашей</t>
+  </si>
+  <si>
+    <t>стоящего и тоже «Медведковского» отряда, по слухам, чувствующего себя гораздо лучше нашего</t>
+  </si>
+  <si>
+    <t>решал патрон в цельной оболочке, но вот его-то</t>
+  </si>
+  <si>
+    <t>решала пуля в цельной оболочке, но вот её-то</t>
+  </si>
+  <si>
+    <t>«революция» к тому времени закончилась</t>
+  </si>
+  <si>
+    <t>«мятеж» к тому времени закончился</t>
+  </si>
+  <si>
+    <t>в их компании или приглашая в свою</t>
+  </si>
+  <si>
+    <t>в их кругу или приглашая в свой</t>
+  </si>
+  <si>
+    <t>Того же типа была история с танзанитами, о которой я узнал после её идиотского окончания и о которой</t>
+  </si>
+  <si>
+    <t>Того же вида был случай с танзанитами, о котором я узнал после его идиотского окончания и о котором</t>
+  </si>
+  <si>
+    <t>позволю ситуации развиться до критической и смогу вовремя ее остановить</t>
+  </si>
+  <si>
+    <t>позволю случаю развиться до чрезвычайного и смогу вовремя его остановить</t>
+  </si>
+  <si>
+    <t>Картина на удивление мерзка, но показательна</t>
+  </si>
+  <si>
+    <t>Зрелище на удивление мерзко, но показательно</t>
+  </si>
+  <si>
+    <t>«командами» и «бригадами»</t>
+  </si>
+  <si>
+    <t>«отрядами» и «дружинами»</t>
+  </si>
+  <si>
+    <t>перспективный, здоровый генофонд</t>
+  </si>
+  <si>
+    <t>многообещающая, здоровая родовая наследственность</t>
+  </si>
+  <si>
+    <t>Один из банков его знакомых дал согласие</t>
+  </si>
+  <si>
+    <t>Одно из денежных хранилищ его знакомых дало согласие</t>
+  </si>
+  <si>
+    <t>выработка схемы покушения была отложена до момента определения графика появления</t>
+  </si>
+  <si>
+    <t>выработка замысла покушения был отложен до мгновения определения расписания и появляения</t>
+  </si>
+  <si>
+    <t>этот «пресс»</t>
+  </si>
+  <si>
+    <t>эту «раздачу»</t>
+  </si>
+  <si>
+    <t>в бывшем тогда итальянским рестораном</t>
+  </si>
+  <si>
+    <t>в бывшей тогда итальянской харчёвне для дворян</t>
   </si>
   <si>
     <t xml:space="preserve">Ремонт был окончен, и меня </t>
@@ -1314,194 +1322,194 @@
     <t xml:space="preserve">Отделка была окончена, и меня </t>
   </si>
   <si>
-    <t xml:space="preserve">мы затеяли ремонт, утеплили</t>
-  </si>
-  <si>
-    <t xml:space="preserve">мы затеяли отделку, утеплили</t>
-  </si>
-  <si>
-    <t xml:space="preserve">который делал ремонт в новой квартире</t>
-  </si>
-  <si>
-    <t xml:space="preserve">который производил отделку в новой квартире</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в «курганской» группировке</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в «курганском» сообществе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">автомобиль, его на сервис</t>
-  </si>
-  <si>
-    <t xml:space="preserve">автомобиль, его в службу по починке</t>
-  </si>
-  <si>
-    <t xml:space="preserve">этой «корпорации», слишком многих из неё</t>
-  </si>
-  <si>
-    <t xml:space="preserve">этого «предприятия», слишком многих из него</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разрядили свои «магазины»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разрядили свои «обоймы»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«уважающей себя» «группировке»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«уважающего себя» «сообщества»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">от величины фигуры</t>
-  </si>
-  <si>
-    <t xml:space="preserve">от величины личности</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в нашей структуре</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в нашем отряде</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Информация набиралась сама собой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сведения набирались сами собой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в другую «бригаду»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в другой «отряд»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">жёстко придерживающихся определённой дисциплины</t>
-  </si>
-  <si>
-    <t xml:space="preserve">жёстко придерживающихся определённых правил</t>
-  </si>
-  <si>
-    <t xml:space="preserve">такой, постоянно подстёгиваемой дисциплины</t>
-  </si>
-  <si>
-    <t xml:space="preserve">таких, постоянно подстёгиваемых правил</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Хороший, знаете ли, бизнес</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Хорошее, знаете ли, предпринимательство</t>
-  </si>
-  <si>
-    <t xml:space="preserve">какую-то «нашу» фирму</t>
-  </si>
-  <si>
-    <t xml:space="preserve">какое-то «наше» предприятие</t>
-  </si>
-  <si>
-    <t xml:space="preserve">История с Фишером не единичная и не исключительная</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Случай с Фишером не единичный и не исключительный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">железная и даже репрессивная дисциплина</t>
-  </si>
-  <si>
-    <t xml:space="preserve">железные и даже угнетающие правила</t>
-  </si>
-  <si>
-    <t xml:space="preserve">была готова любая сумма</t>
-  </si>
-  <si>
-    <t xml:space="preserve">было готово любое количество денег</t>
-  </si>
-  <si>
-    <t xml:space="preserve">каждая бригада и
+    <t>мы затеяли ремонт, утеплили</t>
+  </si>
+  <si>
+    <t>мы затеяли отделку, утеплили</t>
+  </si>
+  <si>
+    <t>который делал ремонт в новой квартире</t>
+  </si>
+  <si>
+    <t>который производил отделку в новой квартире</t>
+  </si>
+  <si>
+    <t>в «курганской» группировке</t>
+  </si>
+  <si>
+    <t>в «курганском» сообществе</t>
+  </si>
+  <si>
+    <t>автомобиль, его на сервис</t>
+  </si>
+  <si>
+    <t>автомобиль, его в службу по починке</t>
+  </si>
+  <si>
+    <t>этой «корпорации», слишком многих из неё</t>
+  </si>
+  <si>
+    <t>этого «предприятия», слишком многих из него</t>
+  </si>
+  <si>
+    <t>разрядили свои «магазины»</t>
+  </si>
+  <si>
+    <t>разрядили свои «обоймы»</t>
+  </si>
+  <si>
+    <t>«уважающей себя» «группировке»</t>
+  </si>
+  <si>
+    <t>«уважающего себя» «сообщества»</t>
+  </si>
+  <si>
+    <t>от величины фигуры</t>
+  </si>
+  <si>
+    <t>от величины личности</t>
+  </si>
+  <si>
+    <t>в нашей структуре</t>
+  </si>
+  <si>
+    <t>в нашем отряде</t>
+  </si>
+  <si>
+    <t>Информация набиралась сама собой</t>
+  </si>
+  <si>
+    <t>Сведения набирались сами собой</t>
+  </si>
+  <si>
+    <t>в другую «бригаду»</t>
+  </si>
+  <si>
+    <t>в другой «отряд»</t>
+  </si>
+  <si>
+    <t>жёстко придерживающихся определённой дисциплины</t>
+  </si>
+  <si>
+    <t>жёстко придерживающихся определённых правил</t>
+  </si>
+  <si>
+    <t>такой, постоянно подстёгиваемой дисциплины</t>
+  </si>
+  <si>
+    <t>таких, постоянно подстёгиваемых правил</t>
+  </si>
+  <si>
+    <t>Хороший, знаете ли, бизнес</t>
+  </si>
+  <si>
+    <t>Хорошее, знаете ли, предпринимательство</t>
+  </si>
+  <si>
+    <t>какую-то «нашу» фирму</t>
+  </si>
+  <si>
+    <t>какое-то «наше» предприятие</t>
+  </si>
+  <si>
+    <t>История с Фишером не единичная и не исключительная</t>
+  </si>
+  <si>
+    <t>Случай с Фишером не единичный и не исключительный</t>
+  </si>
+  <si>
+    <t>железная и даже репрессивная дисциплина</t>
+  </si>
+  <si>
+    <t>железные и даже угнетающие правила</t>
+  </si>
+  <si>
+    <t>была готова любая сумма</t>
+  </si>
+  <si>
+    <t>было готово любое количество денег</t>
+  </si>
+  <si>
+    <t>каждая бригада и
 дружественная ей</t>
   </si>
   <si>
-    <t xml:space="preserve">каждый отряд и дружественный ему</t>
+    <t>каждый отряд и дружественный ему</t>
   </si>
   <si>
     <t xml:space="preserve">ремонт которого шёл полным ходом и требовал </t>
   </si>
   <si>
-    <t xml:space="preserve">починка которого шла полным ходом и требовала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">информацией (она была уже устаревшей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сведениями (они были уже устаревшими</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сыграл роль и меркантильный фактор</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сыграло значение и потребильское обстоятельство</t>
+    <t>починка которого шла полным ходом и требовала</t>
+  </si>
+  <si>
+    <t>информацией (она была уже устаревшей</t>
+  </si>
+  <si>
+    <t>сведениями (они были уже устаревшими</t>
+  </si>
+  <si>
+    <t>сыграл роль и меркантильный фактор</t>
+  </si>
+  <si>
+    <t>сыграло значение и потребильское обстоятельство</t>
   </si>
   <si>
     <t xml:space="preserve">роль основную и подавляющую, а не сдерживающую </t>
   </si>
   <si>
-    <t xml:space="preserve">значение основное и подавляющее, а не сдерживающее</t>
+    <t>значение основное и подавляющее, а не сдерживающее</t>
   </si>
   <si>
     <t xml:space="preserve">отеля «Мариотт» на Тверской улице, в фойе которого </t>
   </si>
   <si>
-    <t xml:space="preserve">гостинницы «Мариотт» на Тверской улице, в прихожей которой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">экономическое конгломераты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в стойке положения «товсь»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">готовсь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дмитрий взял на обдумывании</t>
-  </si>
-  <si>
-    <t xml:space="preserve">это бригаду</t>
-  </si>
-  <si>
-    <t xml:space="preserve">новому крёстному отцу,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Свое белой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Своей белой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">С ним самими</t>
-  </si>
-  <si>
-    <t xml:space="preserve">С ним самим</t>
+    <t>гостинницы «Мариотт» на Тверской улице, в прихожей которой</t>
+  </si>
+  <si>
+    <t>экономическое конгломераты</t>
+  </si>
+  <si>
+    <t>в стойке положения «товсь»</t>
+  </si>
+  <si>
+    <t>готовсь</t>
+  </si>
+  <si>
+    <t>Дмитрий взял на обдумывании</t>
+  </si>
+  <si>
+    <t>это бригаду</t>
+  </si>
+  <si>
+    <t>новому крёстному отцу,</t>
+  </si>
+  <si>
+    <t>Свое белой</t>
+  </si>
+  <si>
+    <t>Своей белой</t>
+  </si>
+  <si>
+    <t>С ним самими</t>
+  </si>
+  <si>
+    <t>С ним самим</t>
   </si>
   <si>
     <t xml:space="preserve">Челны </t>
   </si>
   <si>
-    <t xml:space="preserve">члены</t>
-  </si>
-  <si>
-    <t xml:space="preserve">номеров первым,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">номером первым,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Книга 2</t>
+    <t>члены</t>
+  </si>
+  <si>
+    <t>номеров первым,</t>
+  </si>
+  <si>
+    <t>номером первым,</t>
+  </si>
+  <si>
+    <t>Книга 2</t>
   </si>
   <si>
     <t xml:space="preserve">подходящая оправдание </t>
@@ -1513,47 +1521,95 @@
     <t xml:space="preserve">замусоренному полу подвала </t>
   </si>
   <si>
-    <t xml:space="preserve">замусоренному полу подвалу</t>
+    <t>замусоренному полу подвалу</t>
   </si>
   <si>
     <t xml:space="preserve">с точки зрения профессиональной, </t>
   </si>
   <si>
-    <t xml:space="preserve">с точки зрения профессиональности</t>
+    <t>с точки зрения профессиональности</t>
+  </si>
+  <si>
+    <t>во всех отношениях леди</t>
+  </si>
+  <si>
+    <t>во всех отношениях женщину</t>
+  </si>
+  <si>
+    <t>известным канонам «бригады»</t>
+  </si>
+  <si>
+    <t>известным правилам «отряда»</t>
+  </si>
+  <si>
+    <t>плюс неуравновешенная психика</t>
+  </si>
+  <si>
+    <t>в дополнение неуравновешенный разум</t>
+  </si>
+  <si>
+    <t>в Тверской колонии</t>
+  </si>
+  <si>
+    <t>в Тверском узилище</t>
+  </si>
+  <si>
+    <t>«Климовской» бригады, входившей</t>
+  </si>
+  <si>
+    <t>«Климовского» отряда, входившего</t>
+  </si>
+  <si>
+    <t>эта «бригада» пыталась</t>
+  </si>
+  <si>
+    <t>этот «отряд» пытался</t>
+  </si>
+  <si>
+    <t>этот «отряд»</t>
+  </si>
+  <si>
+    <t>группировки употребляю наркотики</t>
+  </si>
+  <si>
+    <t>группировки употребляют наркотики</t>
+  </si>
+  <si>
+    <t>задавать вопросы в организации</t>
+  </si>
+  <si>
+    <t>задавать вопросы в сообществе</t>
+  </si>
+  <si>
+    <t>мой вопрос о сумме</t>
+  </si>
+  <si>
+    <t>мой вопрос о стоимости</t>
+  </si>
+  <si>
+    <t>тем сумасшедшим риском, который когда-то да должен был</t>
+  </si>
+  <si>
+    <t>той сумасшедшей опасностью, которая когда-то да должна была</t>
+  </si>
+  <si>
+    <t>в состав «бригады»</t>
+  </si>
+  <si>
+    <t>в состав «отряда»</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1586,7 +1642,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1594,103 +1650,49 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1732,12 +1734,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1769,7 +1771,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1793,7 +1795,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1853,26 +1855,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="48.1"/>
+    <col min="1" max="2" width="48.1015625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1880,7 +1881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1888,7 +1889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1896,7 +1897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1904,7 +1905,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1912,7 +1913,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1920,7 +1921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1928,7 +1929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1936,7 +1937,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1944,7 +1945,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1952,7 +1953,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -1960,7 +1961,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1968,7 +1969,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -1976,7 +1977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1984,7 +1985,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -1992,7 +1993,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2000,7 +2001,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2008,7 +2009,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2016,7 +2017,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2024,7 +2025,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -2032,7 +2033,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -2040,7 +2041,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -2048,7 +2049,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
@@ -2056,7 +2057,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -2064,7 +2065,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -2072,7 +2073,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -2080,7 +2081,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
@@ -2088,7 +2089,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4" t="s">
         <v>54</v>
       </c>
@@ -2096,7 +2097,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -2105,31 +2106,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B22"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:B22" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="26.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="27.63"/>
+    <col min="1" max="1" width="26.1015625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.62890625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
         <v>58</v>
       </c>
@@ -2137,7 +2129,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -2145,7 +2137,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>62</v>
       </c>
@@ -2153,7 +2145,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
         <v>64</v>
       </c>
@@ -2161,7 +2153,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>66</v>
       </c>
@@ -2169,7 +2161,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>68</v>
       </c>
@@ -2177,7 +2169,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
         <v>70</v>
       </c>
@@ -2185,7 +2177,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
         <v>72</v>
       </c>
@@ -2193,7 +2185,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
         <v>74</v>
       </c>
@@ -2201,7 +2193,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
         <v>76</v>
       </c>
@@ -2209,7 +2201,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
@@ -2217,7 +2209,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
         <v>80</v>
       </c>
@@ -2226,29 +2218,21 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="44.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="23.15"/>
+    <col min="1" max="1" width="44.7890625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.15625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>82</v>
       </c>
@@ -2257,29 +2241,21 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B155"/>
-  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B160"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="48.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="55.89"/>
+    <col min="1" max="1" width="48.7890625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.89453125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>84</v>
       </c>
@@ -2287,7 +2263,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
         <v>86</v>
       </c>
@@ -2295,7 +2271,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
         <v>88</v>
       </c>
@@ -2303,7 +2279,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
         <v>90</v>
       </c>
@@ -2311,7 +2287,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
@@ -2319,7 +2295,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
         <v>94</v>
       </c>
@@ -2327,7 +2303,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>96</v>
       </c>
@@ -2335,7 +2311,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
@@ -2343,7 +2319,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
         <v>100</v>
       </c>
@@ -2351,7 +2327,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
         <v>102</v>
       </c>
@@ -2359,7 +2335,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
         <v>104</v>
       </c>
@@ -2367,7 +2343,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
         <v>106</v>
       </c>
@@ -2375,7 +2351,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
         <v>108</v>
       </c>
@@ -2383,7 +2359,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
         <v>110</v>
       </c>
@@ -2391,7 +2367,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
         <v>112</v>
       </c>
@@ -2399,7 +2375,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
         <v>114</v>
       </c>
@@ -2407,7 +2383,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5" t="s">
         <v>116</v>
       </c>
@@ -2415,7 +2391,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5" t="s">
         <v>117</v>
       </c>
@@ -2423,7 +2399,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="5" t="s">
         <v>119</v>
       </c>
@@ -2431,7 +2407,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5" t="s">
         <v>121</v>
       </c>
@@ -2439,7 +2415,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="5" t="s">
         <v>123</v>
       </c>
@@ -2447,7 +2423,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>125</v>
       </c>
@@ -2455,7 +2431,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="5" t="s">
         <v>127</v>
       </c>
@@ -2463,7 +2439,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="5" t="s">
         <v>129</v>
       </c>
@@ -2471,7 +2447,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>131</v>
       </c>
@@ -2479,7 +2455,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="5" t="s">
         <v>133</v>
       </c>
@@ -2487,7 +2463,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="5" t="s">
         <v>135</v>
       </c>
@@ -2495,7 +2471,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="5" t="s">
         <v>137</v>
       </c>
@@ -2503,7 +2479,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="5" t="s">
         <v>139</v>
       </c>
@@ -2511,7 +2487,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="5" t="s">
         <v>141</v>
       </c>
@@ -2519,7 +2495,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="5" t="s">
         <v>143</v>
       </c>
@@ -2527,7 +2503,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="5" t="s">
         <v>145</v>
       </c>
@@ -2535,7 +2511,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="5" t="s">
         <v>147</v>
       </c>
@@ -2543,7 +2519,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="5" t="s">
         <v>149</v>
       </c>
@@ -2551,7 +2527,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="5" t="s">
         <v>151</v>
       </c>
@@ -2559,7 +2535,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="5" t="s">
         <v>153</v>
       </c>
@@ -2567,7 +2543,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="5" t="s">
         <v>155</v>
       </c>
@@ -2575,7 +2551,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>157</v>
       </c>
@@ -2583,7 +2559,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="5" t="s">
         <v>159</v>
       </c>
@@ -2591,7 +2567,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="5" t="s">
         <v>161</v>
       </c>
@@ -2599,7 +2575,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="5" t="s">
         <v>163</v>
       </c>
@@ -2607,7 +2583,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="5" t="s">
         <v>165</v>
       </c>
@@ -2615,7 +2591,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="5" t="s">
         <v>167</v>
       </c>
@@ -2623,7 +2599,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="5" t="s">
         <v>169</v>
       </c>
@@ -2631,7 +2607,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="5" t="s">
         <v>171</v>
       </c>
@@ -2639,7 +2615,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="5" t="s">
         <v>173</v>
       </c>
@@ -2647,7 +2623,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="5" t="s">
         <v>175</v>
       </c>
@@ -2655,7 +2631,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="5" t="s">
         <v>177</v>
       </c>
@@ -2663,7 +2639,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="5" t="s">
         <v>179</v>
       </c>
@@ -2671,7 +2647,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="6" t="s">
         <v>181</v>
       </c>
@@ -2679,7 +2655,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="5" t="s">
         <v>183</v>
       </c>
@@ -2687,7 +2663,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="5" t="s">
         <v>185</v>
       </c>
@@ -2695,7 +2671,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="5" t="s">
         <v>187</v>
       </c>
@@ -2703,7 +2679,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="5" t="s">
         <v>189</v>
       </c>
@@ -2711,7 +2687,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="5" t="s">
         <v>191</v>
       </c>
@@ -2719,7 +2695,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="6" t="s">
         <v>193</v>
       </c>
@@ -2727,7 +2703,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="5" t="s">
         <v>195</v>
       </c>
@@ -2735,7 +2711,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="5" t="s">
         <v>197</v>
       </c>
@@ -2743,7 +2719,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="5" t="s">
         <v>199</v>
       </c>
@@ -2751,7 +2727,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="5" t="s">
         <v>201</v>
       </c>
@@ -2759,7 +2735,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="5" t="s">
         <v>203</v>
       </c>
@@ -2767,7 +2743,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="5" t="s">
         <v>205</v>
       </c>
@@ -2775,7 +2751,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="5" t="s">
         <v>207</v>
       </c>
@@ -2783,7 +2759,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="5" t="s">
         <v>209</v>
       </c>
@@ -2791,7 +2767,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="5" t="s">
         <v>211</v>
       </c>
@@ -2799,7 +2775,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="5" t="s">
         <v>213</v>
       </c>
@@ -2807,7 +2783,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="5" t="s">
         <v>215</v>
       </c>
@@ -2815,7 +2791,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="5" t="s">
         <v>217</v>
       </c>
@@ -2823,7 +2799,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="5" t="s">
         <v>219</v>
       </c>
@@ -2831,7 +2807,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="5" t="s">
         <v>221</v>
       </c>
@@ -2839,7 +2815,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="5" t="s">
         <v>223</v>
       </c>
@@ -2847,7 +2823,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="5" t="s">
         <v>225</v>
       </c>
@@ -2855,7 +2831,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="5" t="s">
         <v>227</v>
       </c>
@@ -2863,7 +2839,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="5" t="s">
         <v>229</v>
       </c>
@@ -2871,7 +2847,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="5" t="s">
         <v>231</v>
       </c>
@@ -2879,7 +2855,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="5" t="s">
         <v>233</v>
       </c>
@@ -2887,7 +2863,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="5" t="s">
         <v>235</v>
       </c>
@@ -2895,7 +2871,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="5" t="s">
         <v>237</v>
       </c>
@@ -2903,7 +2879,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="5" t="s">
         <v>239</v>
       </c>
@@ -2911,7 +2887,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="5" t="s">
         <v>241</v>
       </c>
@@ -2919,7 +2895,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="5" t="s">
         <v>243</v>
       </c>
@@ -2927,7 +2903,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="5" t="s">
         <v>245</v>
       </c>
@@ -2935,7 +2911,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="5" t="s">
         <v>247</v>
       </c>
@@ -2943,7 +2919,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="5" t="s">
         <v>249</v>
       </c>
@@ -2951,7 +2927,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="5" t="s">
         <v>251</v>
       </c>
@@ -2959,7 +2935,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="5" t="s">
         <v>253</v>
       </c>
@@ -2967,7 +2943,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="5" t="s">
         <v>255</v>
       </c>
@@ -2975,7 +2951,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="5" t="s">
         <v>257</v>
       </c>
@@ -2983,7 +2959,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="5" t="s">
         <v>259</v>
       </c>
@@ -2991,7 +2967,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="5" t="s">
         <v>261</v>
       </c>
@@ -2999,7 +2975,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="5" t="s">
         <v>263</v>
       </c>
@@ -3007,7 +2983,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="5" t="s">
         <v>265</v>
       </c>
@@ -3015,7 +2991,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="5" t="s">
         <v>267</v>
       </c>
@@ -3023,7 +2999,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="5" t="s">
         <v>269</v>
       </c>
@@ -3031,7 +3007,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="5" t="s">
         <v>271</v>
       </c>
@@ -3039,7 +3015,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="5" t="s">
         <v>273</v>
       </c>
@@ -3047,7 +3023,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="5" t="s">
         <v>275</v>
       </c>
@@ -3055,7 +3031,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="5" t="s">
         <v>277</v>
       </c>
@@ -3063,7 +3039,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="5" t="s">
         <v>279</v>
       </c>
@@ -3071,7 +3047,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="5" t="s">
         <v>281</v>
       </c>
@@ -3079,7 +3055,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="5" t="s">
         <v>283</v>
       </c>
@@ -3087,7 +3063,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="5" t="s">
         <v>285</v>
       </c>
@@ -3095,7 +3071,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="5" t="s">
         <v>287</v>
       </c>
@@ -3103,7 +3079,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="5" t="s">
         <v>289</v>
       </c>
@@ -3111,7 +3087,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="5" t="s">
         <v>291</v>
       </c>
@@ -3119,7 +3095,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="6" t="s">
         <v>293</v>
       </c>
@@ -3127,7 +3103,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="5" t="s">
         <v>295</v>
       </c>
@@ -3135,7 +3111,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="5" t="s">
         <v>297</v>
       </c>
@@ -3143,7 +3119,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1" t="s">
         <v>299</v>
       </c>
@@ -3151,7 +3127,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="5" t="s">
         <v>301</v>
       </c>
@@ -3159,7 +3135,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="7" t="s">
         <v>303</v>
       </c>
@@ -3167,7 +3143,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="7" t="s">
         <v>305</v>
       </c>
@@ -3175,7 +3151,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="7" t="s">
         <v>307</v>
       </c>
@@ -3183,7 +3159,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="7" t="s">
         <v>309</v>
       </c>
@@ -3191,7 +3167,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="7" t="s">
         <v>311</v>
       </c>
@@ -3199,7 +3175,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="7" t="s">
         <v>313</v>
       </c>
@@ -3207,7 +3183,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="7" t="s">
         <v>315</v>
       </c>
@@ -3215,7 +3191,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="7" t="s">
         <v>317</v>
       </c>
@@ -3223,7 +3199,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="7" t="s">
         <v>319</v>
       </c>
@@ -3231,7 +3207,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="7" t="s">
         <v>321</v>
       </c>
@@ -3239,7 +3215,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="7" t="s">
         <v>323</v>
       </c>
@@ -3247,7 +3223,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="7" t="s">
         <v>325</v>
       </c>
@@ -3255,7 +3231,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="7" t="s">
         <v>327</v>
       </c>
@@ -3263,7 +3239,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="7" t="s">
         <v>329</v>
       </c>
@@ -3271,7 +3247,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="7" t="s">
         <v>331</v>
       </c>
@@ -3279,7 +3255,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="7" t="s">
         <v>333</v>
       </c>
@@ -3287,7 +3263,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="7" t="s">
         <v>335</v>
       </c>
@@ -3295,7 +3271,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="7" t="s">
         <v>337</v>
       </c>
@@ -3303,7 +3279,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="7" t="s">
         <v>339</v>
       </c>
@@ -3311,7 +3287,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="7" t="s">
         <v>341</v>
       </c>
@@ -3319,7 +3295,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="7" t="s">
         <v>343</v>
       </c>
@@ -3327,7 +3303,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="7" t="s">
         <v>345</v>
       </c>
@@ -3335,7 +3311,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="7" t="s">
         <v>347</v>
       </c>
@@ -3343,7 +3319,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" spans="1:2" ht="26.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="7" t="s">
         <v>349</v>
       </c>
@@ -3351,7 +3327,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="7" t="s">
         <v>351</v>
       </c>
@@ -3359,7 +3335,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="7" t="s">
         <v>353</v>
       </c>
@@ -3367,7 +3343,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="7" t="s">
         <v>355</v>
       </c>
@@ -3375,7 +3351,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="7" t="s">
         <v>357</v>
       </c>
@@ -3383,7 +3359,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="7" t="s">
         <v>359</v>
       </c>
@@ -3391,7 +3367,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="7" t="s">
         <v>361</v>
       </c>
@@ -3399,7 +3375,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="7" t="s">
         <v>363</v>
       </c>
@@ -3407,7 +3383,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="7" t="s">
         <v>365</v>
       </c>
@@ -3415,7 +3391,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="7" t="s">
         <v>367</v>
       </c>
@@ -3423,7 +3399,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="7" t="s">
         <v>369</v>
       </c>
@@ -3431,7 +3407,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="7" t="s">
         <v>371</v>
       </c>
@@ -3439,7 +3415,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="7" t="s">
         <v>373</v>
       </c>
@@ -3447,7 +3423,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="7" t="s">
         <v>375</v>
       </c>
@@ -3455,7 +3431,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="7" t="s">
         <v>377</v>
       </c>
@@ -3463,7 +3439,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="7" t="s">
         <v>379</v>
       </c>
@@ -3471,7 +3447,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="7" t="s">
         <v>381</v>
       </c>
@@ -3479,7 +3455,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="7" t="s">
         <v>383</v>
       </c>
@@ -3487,7 +3463,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="7" t="s">
         <v>385</v>
       </c>
@@ -3495,7 +3471,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="7" t="s">
         <v>387</v>
       </c>
@@ -3503,7 +3479,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="7" t="s">
         <v>389</v>
       </c>
@@ -3511,30 +3487,62 @@
         <v>390</v>
       </c>
     </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A156" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A157" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>512</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="52.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="48.79"/>
+    <col min="1" max="1" width="52.3671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="48.7890625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>391</v>
       </c>
@@ -3542,7 +3550,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>393</v>
       </c>
@@ -3550,7 +3558,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
         <v>395</v>
       </c>
@@ -3558,7 +3566,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
         <v>397</v>
       </c>
@@ -3566,7 +3574,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>399</v>
       </c>
@@ -3574,7 +3582,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>401</v>
       </c>
@@ -3582,7 +3590,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>403</v>
       </c>
@@ -3591,29 +3599,21 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="71.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="53.89"/>
+    <col min="1" max="1" width="71.41796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>405</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>407</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>409</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>411</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>413</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>415</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>417</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>419</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>421</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>423</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>425</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>427</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>429</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>431</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>433</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>435</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>437</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>439</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>441</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>443</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>445</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>447</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>449</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>451</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>453</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>455</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>457</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>459</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>461</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>463</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
         <v>465</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4" t="s">
         <v>467</v>
       </c>
@@ -3869,34 +3869,75 @@
         <v>468</v>
       </c>
     </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>510</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="8.265625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="32.41"/>
+    <col min="1" max="1" width="32.41796875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
         <v>470</v>
       </c>
@@ -3904,22 +3945,22 @@
         <v>471</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
         <v>475</v>
       </c>
@@ -3927,7 +3968,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>477</v>
       </c>
@@ -3935,7 +3976,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>479</v>
       </c>
@@ -3943,7 +3984,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
         <v>481</v>
       </c>
@@ -3951,12 +3992,12 @@
         <v>482</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7" t="s">
         <v>484</v>
       </c>
@@ -3964,7 +4005,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7" t="s">
         <v>486</v>
       </c>
@@ -3972,7 +4013,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7" t="s">
         <v>488</v>
       </c>
@@ -3980,13 +4021,16 @@
         <v>489</v>
       </c>
     </row>
+    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2D1D95-85F7-4493-9FE1-87D0B78214B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF920C4-AD4D-4DA7-BE04-961B0413A629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="515">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1597,6 +1597,12 @@
   </si>
   <si>
     <t>в состав «отряда»</t>
+  </si>
+  <si>
+    <t>идеология несколько другая</t>
+  </si>
+  <si>
+    <t>миро-воззрение несколько другое</t>
   </si>
 </sst>
 </file>
@@ -1868,12 +1874,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="48.1015625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.08984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1881,7 +1887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1889,7 +1895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1897,7 +1903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1905,7 +1911,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1913,7 +1919,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1921,7 +1927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1929,7 +1935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1937,7 +1943,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1945,7 +1951,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1953,7 +1959,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -1961,7 +1967,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1969,7 +1975,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -1977,7 +1983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1985,7 +1991,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -1993,7 +1999,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2001,7 +2007,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2009,7 +2015,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2017,7 +2023,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2025,7 +2031,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -2033,7 +2039,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -2041,7 +2047,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -2049,7 +2055,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
@@ -2057,7 +2063,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -2065,7 +2071,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -2073,7 +2079,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -2081,7 +2087,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
@@ -2089,7 +2095,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>54</v>
       </c>
@@ -2097,7 +2103,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -2115,13 +2121,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.1015625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.62890625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>58</v>
       </c>
@@ -2129,7 +2135,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -2137,7 +2143,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>62</v>
       </c>
@@ -2145,7 +2151,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>64</v>
       </c>
@@ -2153,7 +2159,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>66</v>
       </c>
@@ -2161,7 +2167,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>68</v>
       </c>
@@ -2169,7 +2175,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>70</v>
       </c>
@@ -2177,7 +2183,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>72</v>
       </c>
@@ -2185,7 +2191,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>74</v>
       </c>
@@ -2193,7 +2199,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>76</v>
       </c>
@@ -2201,7 +2207,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>78</v>
       </c>
@@ -2209,7 +2215,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>80</v>
       </c>
@@ -2226,13 +2232,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="44.7890625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.15625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.81640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>82</v>
       </c>
@@ -2248,14 +2254,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B160"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B161"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.7890625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.89453125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.81640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.90625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>84</v>
       </c>
@@ -2263,7 +2269,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>86</v>
       </c>
@@ -2271,7 +2277,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>88</v>
       </c>
@@ -2279,7 +2285,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>90</v>
       </c>
@@ -2287,7 +2293,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
@@ -2295,7 +2301,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>94</v>
       </c>
@@ -2303,7 +2309,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>96</v>
       </c>
@@ -2311,7 +2317,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
@@ -2319,7 +2325,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>100</v>
       </c>
@@ -2327,7 +2333,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>102</v>
       </c>
@@ -2335,7 +2341,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>104</v>
       </c>
@@ -2343,7 +2349,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>106</v>
       </c>
@@ -2351,7 +2357,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>108</v>
       </c>
@@ -2359,7 +2365,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>110</v>
       </c>
@@ -2367,7 +2373,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>112</v>
       </c>
@@ -2375,7 +2381,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>114</v>
       </c>
@@ -2383,7 +2389,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>116</v>
       </c>
@@ -2391,7 +2397,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>117</v>
       </c>
@@ -2399,7 +2405,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>119</v>
       </c>
@@ -2407,7 +2413,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>121</v>
       </c>
@@ -2415,7 +2421,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>123</v>
       </c>
@@ -2423,7 +2429,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>125</v>
       </c>
@@ -2431,7 +2437,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>127</v>
       </c>
@@ -2439,7 +2445,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>129</v>
       </c>
@@ -2447,7 +2453,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>131</v>
       </c>
@@ -2455,7 +2461,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>133</v>
       </c>
@@ -2463,7 +2469,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>135</v>
       </c>
@@ -2471,7 +2477,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>137</v>
       </c>
@@ -2479,7 +2485,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>139</v>
       </c>
@@ -2487,7 +2493,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>141</v>
       </c>
@@ -2495,7 +2501,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>143</v>
       </c>
@@ -2503,7 +2509,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>145</v>
       </c>
@@ -2511,7 +2517,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>147</v>
       </c>
@@ -2519,7 +2525,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>149</v>
       </c>
@@ -2527,7 +2533,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>151</v>
       </c>
@@ -2535,7 +2541,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>153</v>
       </c>
@@ -2543,7 +2549,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>155</v>
       </c>
@@ -2551,7 +2557,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>157</v>
       </c>
@@ -2559,7 +2565,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>159</v>
       </c>
@@ -2567,7 +2573,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>161</v>
       </c>
@@ -2575,7 +2581,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>163</v>
       </c>
@@ -2583,7 +2589,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>165</v>
       </c>
@@ -2591,7 +2597,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>167</v>
       </c>
@@ -2599,7 +2605,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>169</v>
       </c>
@@ -2607,7 +2613,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>171</v>
       </c>
@@ -2615,7 +2621,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>173</v>
       </c>
@@ -2623,7 +2629,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>175</v>
       </c>
@@ -2631,7 +2637,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>177</v>
       </c>
@@ -2639,7 +2645,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>179</v>
       </c>
@@ -2647,7 +2653,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>181</v>
       </c>
@@ -2655,7 +2661,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>183</v>
       </c>
@@ -2663,7 +2669,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>185</v>
       </c>
@@ -2671,7 +2677,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>187</v>
       </c>
@@ -2679,7 +2685,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>189</v>
       </c>
@@ -2687,7 +2693,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>191</v>
       </c>
@@ -2695,7 +2701,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>193</v>
       </c>
@@ -2703,7 +2709,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>195</v>
       </c>
@@ -2711,7 +2717,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>197</v>
       </c>
@@ -2719,7 +2725,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>199</v>
       </c>
@@ -2727,7 +2733,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>201</v>
       </c>
@@ -2735,7 +2741,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>203</v>
       </c>
@@ -2743,7 +2749,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>205</v>
       </c>
@@ -2751,7 +2757,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>207</v>
       </c>
@@ -2759,7 +2765,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>209</v>
       </c>
@@ -2767,7 +2773,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>211</v>
       </c>
@@ -2775,7 +2781,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>213</v>
       </c>
@@ -2783,7 +2789,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>215</v>
       </c>
@@ -2791,7 +2797,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>217</v>
       </c>
@@ -2799,7 +2805,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>219</v>
       </c>
@@ -2807,7 +2813,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>221</v>
       </c>
@@ -2815,7 +2821,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>223</v>
       </c>
@@ -2823,7 +2829,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>225</v>
       </c>
@@ -2831,7 +2837,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>227</v>
       </c>
@@ -2839,7 +2845,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>229</v>
       </c>
@@ -2847,7 +2853,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>231</v>
       </c>
@@ -2855,7 +2861,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>233</v>
       </c>
@@ -2863,7 +2869,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>235</v>
       </c>
@@ -2871,7 +2877,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>237</v>
       </c>
@@ -2879,7 +2885,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>239</v>
       </c>
@@ -2887,7 +2893,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>241</v>
       </c>
@@ -2895,7 +2901,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>243</v>
       </c>
@@ -2903,7 +2909,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>245</v>
       </c>
@@ -2911,7 +2917,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>247</v>
       </c>
@@ -2919,7 +2925,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>249</v>
       </c>
@@ -2927,7 +2933,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>251</v>
       </c>
@@ -2935,7 +2941,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>253</v>
       </c>
@@ -2943,7 +2949,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>255</v>
       </c>
@@ -2951,7 +2957,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>257</v>
       </c>
@@ -2959,7 +2965,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>259</v>
       </c>
@@ -2967,7 +2973,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
         <v>261</v>
       </c>
@@ -2975,7 +2981,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>263</v>
       </c>
@@ -2983,7 +2989,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>265</v>
       </c>
@@ -2991,7 +2997,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>267</v>
       </c>
@@ -2999,7 +3005,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>269</v>
       </c>
@@ -3007,7 +3013,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>271</v>
       </c>
@@ -3015,7 +3021,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
         <v>273</v>
       </c>
@@ -3023,7 +3029,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>275</v>
       </c>
@@ -3031,7 +3037,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>277</v>
       </c>
@@ -3039,7 +3045,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>279</v>
       </c>
@@ -3047,7 +3053,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
         <v>281</v>
       </c>
@@ -3055,7 +3061,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
         <v>283</v>
       </c>
@@ -3063,7 +3069,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>285</v>
       </c>
@@ -3071,7 +3077,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>287</v>
       </c>
@@ -3079,7 +3085,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>289</v>
       </c>
@@ -3087,7 +3093,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>291</v>
       </c>
@@ -3095,7 +3101,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="6" t="s">
         <v>293</v>
       </c>
@@ -3103,7 +3109,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>295</v>
       </c>
@@ -3111,7 +3117,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>297</v>
       </c>
@@ -3119,7 +3125,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>299</v>
       </c>
@@ -3127,7 +3133,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
         <v>301</v>
       </c>
@@ -3135,7 +3141,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>303</v>
       </c>
@@ -3143,7 +3149,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>305</v>
       </c>
@@ -3151,7 +3157,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>307</v>
       </c>
@@ -3159,7 +3165,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>309</v>
       </c>
@@ -3167,7 +3173,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>311</v>
       </c>
@@ -3175,7 +3181,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>313</v>
       </c>
@@ -3183,7 +3189,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>315</v>
       </c>
@@ -3191,7 +3197,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>317</v>
       </c>
@@ -3199,7 +3205,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>319</v>
       </c>
@@ -3207,7 +3213,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>321</v>
       </c>
@@ -3215,7 +3221,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>323</v>
       </c>
@@ -3223,7 +3229,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>325</v>
       </c>
@@ -3231,7 +3237,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
         <v>327</v>
       </c>
@@ -3239,7 +3245,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>329</v>
       </c>
@@ -3247,7 +3253,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
         <v>331</v>
       </c>
@@ -3255,7 +3261,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>333</v>
       </c>
@@ -3263,7 +3269,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
         <v>335</v>
       </c>
@@ -3271,7 +3277,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="7" t="s">
         <v>337</v>
       </c>
@@ -3279,7 +3285,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>339</v>
       </c>
@@ -3287,7 +3293,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
         <v>341</v>
       </c>
@@ -3295,7 +3301,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="7" t="s">
         <v>343</v>
       </c>
@@ -3303,7 +3309,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
         <v>345</v>
       </c>
@@ -3311,7 +3317,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="7" t="s">
         <v>347</v>
       </c>
@@ -3319,7 +3325,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="26.1" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
         <v>349</v>
       </c>
@@ -3327,7 +3333,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="7" t="s">
         <v>351</v>
       </c>
@@ -3335,7 +3341,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
         <v>353</v>
       </c>
@@ -3343,7 +3349,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>355</v>
       </c>
@@ -3351,7 +3357,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>357</v>
       </c>
@@ -3359,7 +3365,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>359</v>
       </c>
@@ -3367,7 +3373,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
         <v>361</v>
       </c>
@@ -3375,7 +3381,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
         <v>363</v>
       </c>
@@ -3383,7 +3389,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>365</v>
       </c>
@@ -3391,7 +3397,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="7" t="s">
         <v>367</v>
       </c>
@@ -3399,7 +3405,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>369</v>
       </c>
@@ -3407,7 +3413,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="7" t="s">
         <v>371</v>
       </c>
@@ -3415,7 +3421,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>373</v>
       </c>
@@ -3423,7 +3429,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
         <v>375</v>
       </c>
@@ -3431,7 +3437,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>377</v>
       </c>
@@ -3439,7 +3445,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>379</v>
       </c>
@@ -3447,7 +3453,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
         <v>381</v>
       </c>
@@ -3455,7 +3461,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
         <v>383</v>
       </c>
@@ -3463,7 +3469,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
         <v>385</v>
       </c>
@@ -3471,7 +3477,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
         <v>387</v>
       </c>
@@ -3479,7 +3485,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
         <v>389</v>
       </c>
@@ -3487,7 +3493,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="7" t="s">
         <v>494</v>
       </c>
@@ -3495,7 +3501,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="7" t="s">
         <v>496</v>
       </c>
@@ -3503,7 +3509,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
         <v>498</v>
       </c>
@@ -3511,7 +3517,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>500</v>
       </c>
@@ -3519,12 +3525,20 @@
         <v>502</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
         <v>511</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>512</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -3536,13 +3550,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.3671875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="48.7890625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="52.36328125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="48.81640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>391</v>
       </c>
@@ -3550,7 +3564,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>393</v>
       </c>
@@ -3558,7 +3572,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>395</v>
       </c>
@@ -3566,7 +3580,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>397</v>
       </c>
@@ -3574,7 +3588,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>399</v>
       </c>
@@ -3582,7 +3596,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>401</v>
       </c>
@@ -3590,7 +3604,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>403</v>
       </c>
@@ -3607,13 +3621,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="71.41796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="71.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>405</v>
       </c>
@@ -3621,7 +3635,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>407</v>
       </c>
@@ -3629,7 +3643,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>409</v>
       </c>
@@ -3637,7 +3651,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>411</v>
       </c>
@@ -3645,7 +3659,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>413</v>
       </c>
@@ -3653,7 +3667,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>415</v>
       </c>
@@ -3661,7 +3675,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>417</v>
       </c>
@@ -3669,7 +3683,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>419</v>
       </c>
@@ -3677,7 +3691,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>421</v>
       </c>
@@ -3685,7 +3699,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>423</v>
       </c>
@@ -3693,7 +3707,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>425</v>
       </c>
@@ -3701,7 +3715,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>427</v>
       </c>
@@ -3709,7 +3723,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>429</v>
       </c>
@@ -3717,7 +3731,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>431</v>
       </c>
@@ -3725,7 +3739,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>433</v>
       </c>
@@ -3733,7 +3747,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>435</v>
       </c>
@@ -3741,7 +3755,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>437</v>
       </c>
@@ -3749,7 +3763,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>439</v>
       </c>
@@ -3757,7 +3771,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>441</v>
       </c>
@@ -3765,7 +3779,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>443</v>
       </c>
@@ -3773,7 +3787,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>445</v>
       </c>
@@ -3781,7 +3795,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>447</v>
       </c>
@@ -3789,7 +3803,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>449</v>
       </c>
@@ -3797,7 +3811,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>451</v>
       </c>
@@ -3805,7 +3819,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>453</v>
       </c>
@@ -3813,7 +3827,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>455</v>
       </c>
@@ -3821,7 +3835,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>457</v>
       </c>
@@ -3829,7 +3843,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>459</v>
       </c>
@@ -3837,7 +3851,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>461</v>
       </c>
@@ -3845,7 +3859,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>463</v>
       </c>
@@ -3853,7 +3867,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>465</v>
       </c>
@@ -3861,7 +3875,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>467</v>
       </c>
@@ -3869,7 +3883,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>490</v>
       </c>
@@ -3877,7 +3891,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>492</v>
       </c>
@@ -3885,7 +3899,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>500</v>
       </c>
@@ -3893,7 +3907,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>505</v>
       </c>
@@ -3901,7 +3915,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>507</v>
       </c>
@@ -3909,7 +3923,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>509</v>
       </c>
@@ -3926,18 +3940,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.41796875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.68359375" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>470</v>
       </c>
@@ -3945,22 +3959,22 @@
         <v>471</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>475</v>
       </c>
@@ -3968,7 +3982,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>477</v>
       </c>
@@ -3976,7 +3990,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>479</v>
       </c>
@@ -3984,7 +3998,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>481</v>
       </c>
@@ -3992,12 +4006,12 @@
         <v>482</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>484</v>
       </c>
@@ -4005,7 +4019,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>486</v>
       </c>
@@ -4013,7 +4027,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>488</v>
       </c>
@@ -4021,7 +4035,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>503</v>
       </c>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF920C4-AD4D-4DA7-BE04-961B0413A629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBEA620-4F29-4A73-9A2A-1555AB469F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
-    <sheet name="Составные" sheetId="2" r:id="rId2"/>
-    <sheet name="простые" sheetId="3" r:id="rId3"/>
+    <sheet name="простые" sheetId="3" r:id="rId2"/>
+    <sheet name="Составные" sheetId="2" r:id="rId3"/>
     <sheet name="неизменные" sheetId="4" r:id="rId4"/>
     <sheet name="неизменные_длинные" sheetId="5" r:id="rId5"/>
     <sheet name="неизменные_короткие" sheetId="6" r:id="rId6"/>
@@ -2119,6 +2119,29 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="44.81640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2221,29 +2244,6 @@
       </c>
       <c r="B14" s="5" t="s">
         <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="44.81640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBEA620-4F29-4A73-9A2A-1555AB469F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F40F77-C7AB-4754-80C1-5D13EE5B5871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
-    <sheet name="простые" sheetId="3" r:id="rId2"/>
-    <sheet name="Составные" sheetId="2" r:id="rId3"/>
+    <sheet name="простые" sheetId="2" r:id="rId2"/>
+    <sheet name="Составные" sheetId="3" r:id="rId3"/>
     <sheet name="неизменные" sheetId="4" r:id="rId4"/>
     <sheet name="неизменные_длинные" sheetId="5" r:id="rId5"/>
     <sheet name="неизменные_короткие" sheetId="6" r:id="rId6"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="549">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -213,6 +213,12 @@
     <t>горных извилистых дорог</t>
   </si>
   <si>
+    <t>«бригадами»</t>
+  </si>
+  <si>
+    <t>«дружинами»</t>
+  </si>
+  <si>
     <t>Измайловском комплексе</t>
   </si>
   <si>
@@ -283,12 +289,6 @@
   </si>
   <si>
     <t>низшим учреждениям</t>
-  </si>
-  <si>
-    <t>«бригадами»</t>
-  </si>
-  <si>
-    <t>«дружинами»</t>
   </si>
   <si>
     <t>«бригадам» структурами</t>
@@ -1232,6 +1232,90 @@
     <t>копился, либо передавался</t>
   </si>
   <si>
+    <t>плюс неуравновешенная психика</t>
+  </si>
+  <si>
+    <t>в дополнение неуравновешенный разум</t>
+  </si>
+  <si>
+    <t>в Тверской колонии</t>
+  </si>
+  <si>
+    <t>в Тверском узилище</t>
+  </si>
+  <si>
+    <t>«Климовской» бригады, входившей</t>
+  </si>
+  <si>
+    <t>«Климовского» отряда, входившего</t>
+  </si>
+  <si>
+    <t>эта «бригада» пыталась</t>
+  </si>
+  <si>
+    <t>этот «отряд»</t>
+  </si>
+  <si>
+    <t>в состав «бригады»</t>
+  </si>
+  <si>
+    <t>в состав «отряда»</t>
+  </si>
+  <si>
+    <t>идеология несколько другая</t>
+  </si>
+  <si>
+    <t>миро-воззрение несколько другое</t>
+  </si>
+  <si>
+    <t>после армией, которой</t>
+  </si>
+  <si>
+    <t>после вооружённым силам, которым</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Армия дала мне </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вооружённые силы дали мне </t>
+  </si>
+  <si>
+    <t>любил вспоминать историю</t>
+  </si>
+  <si>
+    <t>любил вспоминать случай</t>
+  </si>
+  <si>
+    <t>в многочисленной компании</t>
+  </si>
+  <si>
+    <t>в многочисленном скоплении людей</t>
+  </si>
+  <si>
+    <t>образование, помогавшая в этом, носила</t>
+  </si>
+  <si>
+    <t>ведомство, помогавшее в этом, носило</t>
+  </si>
+  <si>
+    <t>произошёл казус, повлиявший</t>
+  </si>
+  <si>
+    <t>произошёл недоразумение, повлиявшее</t>
+  </si>
+  <si>
+    <t>техника устарела, а защита от неё</t>
+  </si>
+  <si>
+    <t>средства устарели, а защита от них</t>
+  </si>
+  <si>
+    <t>любой, имеющийся у меня документ</t>
+  </si>
+  <si>
+    <t>любое, имеющееся у меня письменное сведетельство</t>
+  </si>
+  <si>
     <t>обговоренная фраза из уст Олега, которая</t>
   </si>
   <si>
@@ -1272,6 +1356,24 @@
   </si>
   <si>
     <t>позволю случаю развиться до чрезвычайного и смогу вовремя его остановить</t>
+  </si>
+  <si>
+    <t>уголовно-криминальный момент, имевший место быть, прошедший проверку и апробацию королевской полицией, «пальнул»</t>
+  </si>
+  <si>
+    <t>Уголовно-преступная особенность, имевшая место быть, прошедшая проверку и апробацию королевской полицией, «пальнула»</t>
+  </si>
+  <si>
+    <t>Весь его офис, который за время нашего общения поменялся трижды, становясь всё более престижным, был уставлен</t>
+  </si>
+  <si>
+    <t>Всё его рабочее помещение, которое за время нашегообщения поменялось трижды, становясь всё более влиятельным, было уставлено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">один момент своей жизни – не самый лучший и не тот </t>
+  </si>
+  <si>
+    <t>одно мгновение своей жизни – не самое лучшее и не то</t>
   </si>
   <si>
     <t>Картина на удивление мерзка, но показательна</t>
@@ -1467,6 +1569,69 @@
     <t>гостинницы «Мариотт» на Тверской улице, в прихожей которой</t>
   </si>
   <si>
+    <t>во всех отношениях леди</t>
+  </si>
+  <si>
+    <t>во всех отношениях женщину</t>
+  </si>
+  <si>
+    <t>известным канонам «бригады»</t>
+  </si>
+  <si>
+    <t>известным правилам «отряда»</t>
+  </si>
+  <si>
+    <t>этот «отряд» пытался</t>
+  </si>
+  <si>
+    <t>задавать вопросы в организации</t>
+  </si>
+  <si>
+    <t>задавать вопросы в сообществе</t>
+  </si>
+  <si>
+    <t>мой вопрос о сумме</t>
+  </si>
+  <si>
+    <t>мой вопрос о стоимости</t>
+  </si>
+  <si>
+    <t>тем сумасшедшим риском, который когда-то да должен был</t>
+  </si>
+  <si>
+    <t>той сумасшедшей опасностью, которая когда-то да должна была</t>
+  </si>
+  <si>
+    <t xml:space="preserve">с четырьмя магазинами,  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">с четырьмя обоймами,  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">о сумме, всё же переданной </t>
+  </si>
+  <si>
+    <t>о денежных средствах, всё же переданными</t>
+  </si>
+  <si>
+    <t xml:space="preserve">организовать дезинформацию, которая ляжет </t>
+  </si>
+  <si>
+    <t>устроить вброс лже-сведений, которые лягут</t>
+  </si>
+  <si>
+    <t>Грамматика была ужасна</t>
+  </si>
+  <si>
+    <t>Языко-ведение было ужасно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в ресторанчик, на этот раз это был китайский </t>
+  </si>
+  <si>
+    <t>в харчёвню для дворян, на этот раз это была китайская</t>
+  </si>
+  <si>
     <t>экономическое конгломераты</t>
   </si>
   <si>
@@ -1530,79 +1695,16 @@
     <t>с точки зрения профессиональности</t>
   </si>
   <si>
-    <t>во всех отношениях леди</t>
-  </si>
-  <si>
-    <t>во всех отношениях женщину</t>
-  </si>
-  <si>
-    <t>известным канонам «бригады»</t>
-  </si>
-  <si>
-    <t>известным правилам «отряда»</t>
-  </si>
-  <si>
-    <t>плюс неуравновешенная психика</t>
-  </si>
-  <si>
-    <t>в дополнение неуравновешенный разум</t>
-  </si>
-  <si>
-    <t>в Тверской колонии</t>
-  </si>
-  <si>
-    <t>в Тверском узилище</t>
-  </si>
-  <si>
-    <t>«Климовской» бригады, входившей</t>
-  </si>
-  <si>
-    <t>«Климовского» отряда, входившего</t>
-  </si>
-  <si>
-    <t>эта «бригада» пыталась</t>
-  </si>
-  <si>
-    <t>этот «отряд» пытался</t>
-  </si>
-  <si>
-    <t>этот «отряд»</t>
-  </si>
-  <si>
     <t>группировки употребляю наркотики</t>
   </si>
   <si>
     <t>группировки употребляют наркотики</t>
   </si>
   <si>
-    <t>задавать вопросы в организации</t>
-  </si>
-  <si>
-    <t>задавать вопросы в сообществе</t>
-  </si>
-  <si>
-    <t>мой вопрос о сумме</t>
-  </si>
-  <si>
-    <t>мой вопрос о стоимости</t>
-  </si>
-  <si>
-    <t>тем сумасшедшим риском, который когда-то да должен был</t>
-  </si>
-  <si>
-    <t>той сумасшедшей опасностью, которая когда-то да должна была</t>
-  </si>
-  <si>
-    <t>в состав «бригады»</t>
-  </si>
-  <si>
-    <t>в состав «отряда»</t>
-  </si>
-  <si>
-    <t>идеология несколько другая</t>
-  </si>
-  <si>
-    <t>миро-воззрение несколько другое</t>
+    <t xml:space="preserve">который бы хотелось </t>
+  </si>
+  <si>
+    <t xml:space="preserve">которым бы хотелось </t>
   </si>
 </sst>
 </file>
@@ -1679,7 +1781,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1874,12 +1976,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="48.08984375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1015625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1887,7 +1989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1895,7 +1997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1903,7 +2005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1911,7 +2013,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1919,7 +2021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1927,7 +2029,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1935,7 +2037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1943,7 +2045,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1951,7 +2053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1959,7 +2061,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -1967,7 +2069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1975,7 +2077,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -1983,7 +2085,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1991,7 +2093,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -1999,7 +2101,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2007,7 +2109,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2015,7 +2117,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2023,7 +2125,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2031,7 +2133,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -2039,7 +2141,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -2047,7 +2149,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -2055,7 +2157,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
@@ -2063,7 +2165,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -2071,7 +2173,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -2079,7 +2181,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -2087,7 +2189,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
@@ -2095,7 +2197,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4" t="s">
         <v>54</v>
       </c>
@@ -2103,7 +2205,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -2119,20 +2221,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="44.81640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.7890625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.15625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2142,108 +2244,108 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="26.08984375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.1015625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.62890625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2254,14 +2356,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B161"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B168"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="48.81640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.90625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.7890625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.89453125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>84</v>
       </c>
@@ -2269,7 +2371,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
         <v>86</v>
       </c>
@@ -2277,7 +2379,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
         <v>88</v>
       </c>
@@ -2285,7 +2387,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
         <v>90</v>
       </c>
@@ -2293,7 +2395,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
@@ -2301,7 +2403,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
         <v>94</v>
       </c>
@@ -2309,7 +2411,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>96</v>
       </c>
@@ -2317,7 +2419,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
@@ -2325,7 +2427,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
         <v>100</v>
       </c>
@@ -2333,7 +2435,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
         <v>102</v>
       </c>
@@ -2341,7 +2443,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
         <v>104</v>
       </c>
@@ -2349,7 +2451,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
         <v>106</v>
       </c>
@@ -2357,7 +2459,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
         <v>108</v>
       </c>
@@ -2365,7 +2467,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
         <v>110</v>
       </c>
@@ -2373,7 +2475,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
         <v>112</v>
       </c>
@@ -2381,7 +2483,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
         <v>114</v>
       </c>
@@ -2389,7 +2491,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5" t="s">
         <v>116</v>
       </c>
@@ -2397,7 +2499,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5" t="s">
         <v>117</v>
       </c>
@@ -2405,7 +2507,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="5" t="s">
         <v>119</v>
       </c>
@@ -2413,7 +2515,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5" t="s">
         <v>121</v>
       </c>
@@ -2421,7 +2523,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="5" t="s">
         <v>123</v>
       </c>
@@ -2429,7 +2531,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>125</v>
       </c>
@@ -2437,7 +2539,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="5" t="s">
         <v>127</v>
       </c>
@@ -2445,7 +2547,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="5" t="s">
         <v>129</v>
       </c>
@@ -2453,7 +2555,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>131</v>
       </c>
@@ -2461,7 +2563,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="5" t="s">
         <v>133</v>
       </c>
@@ -2469,7 +2571,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="5" t="s">
         <v>135</v>
       </c>
@@ -2477,7 +2579,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="5" t="s">
         <v>137</v>
       </c>
@@ -2485,7 +2587,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="5" t="s">
         <v>139</v>
       </c>
@@ -2493,7 +2595,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="5" t="s">
         <v>141</v>
       </c>
@@ -2501,7 +2603,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="5" t="s">
         <v>143</v>
       </c>
@@ -2509,7 +2611,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="5" t="s">
         <v>145</v>
       </c>
@@ -2517,7 +2619,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="5" t="s">
         <v>147</v>
       </c>
@@ -2525,7 +2627,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="5" t="s">
         <v>149</v>
       </c>
@@ -2533,7 +2635,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="5" t="s">
         <v>151</v>
       </c>
@@ -2541,7 +2643,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="5" t="s">
         <v>153</v>
       </c>
@@ -2549,7 +2651,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="5" t="s">
         <v>155</v>
       </c>
@@ -2557,7 +2659,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>157</v>
       </c>
@@ -2565,7 +2667,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="5" t="s">
         <v>159</v>
       </c>
@@ -2573,7 +2675,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="5" t="s">
         <v>161</v>
       </c>
@@ -2581,7 +2683,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="5" t="s">
         <v>163</v>
       </c>
@@ -2589,7 +2691,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="5" t="s">
         <v>165</v>
       </c>
@@ -2597,7 +2699,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="5" t="s">
         <v>167</v>
       </c>
@@ -2605,7 +2707,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="5" t="s">
         <v>169</v>
       </c>
@@ -2613,7 +2715,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="5" t="s">
         <v>171</v>
       </c>
@@ -2621,7 +2723,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="5" t="s">
         <v>173</v>
       </c>
@@ -2629,7 +2731,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="5" t="s">
         <v>175</v>
       </c>
@@ -2637,7 +2739,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="5" t="s">
         <v>177</v>
       </c>
@@ -2645,7 +2747,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="5" t="s">
         <v>179</v>
       </c>
@@ -2653,7 +2755,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="6" t="s">
         <v>181</v>
       </c>
@@ -2661,7 +2763,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="5" t="s">
         <v>183</v>
       </c>
@@ -2669,7 +2771,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="5" t="s">
         <v>185</v>
       </c>
@@ -2677,7 +2779,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="5" t="s">
         <v>187</v>
       </c>
@@ -2685,7 +2787,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="5" t="s">
         <v>189</v>
       </c>
@@ -2693,7 +2795,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="5" t="s">
         <v>191</v>
       </c>
@@ -2701,7 +2803,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="6" t="s">
         <v>193</v>
       </c>
@@ -2709,7 +2811,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="5" t="s">
         <v>195</v>
       </c>
@@ -2717,7 +2819,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="5" t="s">
         <v>197</v>
       </c>
@@ -2725,7 +2827,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="5" t="s">
         <v>199</v>
       </c>
@@ -2733,7 +2835,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="5" t="s">
         <v>201</v>
       </c>
@@ -2741,7 +2843,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="5" t="s">
         <v>203</v>
       </c>
@@ -2749,7 +2851,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="5" t="s">
         <v>205</v>
       </c>
@@ -2757,7 +2859,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="5" t="s">
         <v>207</v>
       </c>
@@ -2765,7 +2867,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="5" t="s">
         <v>209</v>
       </c>
@@ -2773,7 +2875,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="5" t="s">
         <v>211</v>
       </c>
@@ -2781,7 +2883,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="5" t="s">
         <v>213</v>
       </c>
@@ -2789,7 +2891,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="5" t="s">
         <v>215</v>
       </c>
@@ -2797,7 +2899,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="5" t="s">
         <v>217</v>
       </c>
@@ -2805,7 +2907,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="5" t="s">
         <v>219</v>
       </c>
@@ -2813,7 +2915,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="5" t="s">
         <v>221</v>
       </c>
@@ -2821,7 +2923,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="5" t="s">
         <v>223</v>
       </c>
@@ -2829,7 +2931,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="5" t="s">
         <v>225</v>
       </c>
@@ -2837,7 +2939,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="5" t="s">
         <v>227</v>
       </c>
@@ -2845,7 +2947,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="5" t="s">
         <v>229</v>
       </c>
@@ -2853,7 +2955,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="5" t="s">
         <v>231</v>
       </c>
@@ -2861,7 +2963,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="5" t="s">
         <v>233</v>
       </c>
@@ -2869,7 +2971,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="5" t="s">
         <v>235</v>
       </c>
@@ -2877,7 +2979,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="5" t="s">
         <v>237</v>
       </c>
@@ -2885,7 +2987,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="5" t="s">
         <v>239</v>
       </c>
@@ -2893,7 +2995,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="5" t="s">
         <v>241</v>
       </c>
@@ -2901,7 +3003,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="5" t="s">
         <v>243</v>
       </c>
@@ -2909,636 +3011,700 @@
         <v>244</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+        <v>265</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B106" s="5" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" s="6" t="s">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B106" s="6" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="5" t="s">
+        <v>301</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B111" s="5" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="7" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="7" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="7" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B125" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="26.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
+        <v>349</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="B135" s="8" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+        <v>351</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="7" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="7" t="s">
-        <v>494</v>
+        <v>393</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="7" t="s">
-        <v>496</v>
+        <v>395</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A158" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A159" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="7" t="s">
-        <v>511</v>
+        <v>401</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>514</v>
+        <v>403</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A162" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A163" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A165" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A166" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A167" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A168" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -3549,67 +3715,91 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="52.36328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="48.81640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="52.3671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.7890625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>429</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>404</v>
+        <v>431</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="38.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="38.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -3620,315 +3810,355 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="71.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.90625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.68359375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>407</v>
+        <v>441</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>429</v>
+        <v>463</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>447</v>
+        <v>481</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>449</v>
+        <v>483</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
-        <v>453</v>
+        <v>487</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="7" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
-        <v>500</v>
+        <v>397</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="29.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>510</v>
+        <v>512</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -3939,108 +4169,116 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.6328125" customWidth="1"/>
+    <col min="1" max="1" width="32.41796875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.62890625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
-        <v>470</v>
+        <v>525</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
-        <v>475</v>
+        <v>530</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
-        <v>477</v>
+        <v>532</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
-        <v>479</v>
+        <v>534</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
-        <v>481</v>
+        <v>536</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7" t="s">
-        <v>484</v>
+        <v>539</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7" t="s">
-        <v>486</v>
+        <v>541</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7" t="s">
-        <v>488</v>
+        <v>543</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>503</v>
+        <v>545</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>504</v>
+        <v>546</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>548</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F40F77-C7AB-4754-80C1-5D13EE5B5871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942CE7E0-5928-47BE-88D3-34112E327949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="551">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1705,6 +1705,12 @@
   </si>
   <si>
     <t xml:space="preserve">которым бы хотелось </t>
+  </si>
+  <si>
+    <t>единовременная итог сложения, пусть и крупная</t>
+  </si>
+  <si>
+    <t>единовременное количество денег, пусть и крупное</t>
   </si>
 </sst>
 </file>
@@ -3810,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="51.68359375" style="1" customWidth="1"/>
@@ -4159,6 +4165,14 @@
       </c>
       <c r="B43" s="9" t="s">
         <v>523</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>550</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942CE7E0-5928-47BE-88D3-34112E327949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEE594D-A397-4418-A6B6-6DD42E530A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные_важные!$A$1:$B$22</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -37,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="581">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1711,6 +1722,96 @@
   </si>
   <si>
     <t>единовременное количество денег, пусть и крупное</t>
+  </si>
+  <si>
+    <t>сумма «благодарности» та же</t>
+  </si>
+  <si>
+    <t>вознаграждение «благодарности» то же</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> была передана на хозяйственные</t>
+  </si>
+  <si>
+    <t>оперативная информация указывала</t>
+  </si>
+  <si>
+    <t>сведения милиции, указывали</t>
+  </si>
+  <si>
+    <t>было передано на хозяйственные</t>
+  </si>
+  <si>
+    <t>полной и доподлинной картины</t>
+  </si>
+  <si>
+    <t>полной и доподлинной обстановки</t>
+  </si>
+  <si>
+    <t>начального базового материала</t>
+  </si>
+  <si>
+    <t>начального достаточного количества</t>
+  </si>
+  <si>
+    <t>была такая узкая и неполная</t>
+  </si>
+  <si>
+    <t>были такие узкие и неполные</t>
+  </si>
+  <si>
+    <t>– её добывание</t>
+  </si>
+  <si>
+    <t>– их добывание</t>
+  </si>
+  <si>
+    <t>Состоял в первой команде</t>
+  </si>
+  <si>
+    <t>Состоял в первом сообществе</t>
+  </si>
+  <si>
+    <t>появилась информация о Шерстобитове, имеющая</t>
+  </si>
+  <si>
+    <t>появились сведения о Шерстобитове, имеющие</t>
+  </si>
+  <si>
+    <t>тяжелейший для нас обоих момент</t>
+  </si>
+  <si>
+    <t>тяжелейшее для нас обоих мгновение</t>
+  </si>
+  <si>
+    <t>на свою «базу</t>
+  </si>
+  <si>
+    <t>на своё «логово»</t>
+  </si>
+  <si>
+    <t>не только бригады</t>
+  </si>
+  <si>
+    <t>не только отряда</t>
+  </si>
+  <si>
+    <t>в казино и окружал</t>
+  </si>
+  <si>
+    <t>в игорном учреждении и окружал</t>
+  </si>
+  <si>
+    <t>семьи, бригады</t>
+  </si>
+  <si>
+    <t>семьи, отряда</t>
+  </si>
+  <si>
+    <t>Размышление, которое я услышал, было</t>
+  </si>
+  <si>
+    <t>Монолог, который я услышал, был</t>
   </si>
 </sst>
 </file>
@@ -2362,7 +2463,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B168"/>
+  <dimension ref="A1:B183"/>
   <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="48.7890625" style="5" customWidth="1"/>
@@ -3711,6 +3812,126 @@
       </c>
       <c r="B168" s="7" t="s">
         <v>418</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A169" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A170" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A171" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A172" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A173" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A174" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A175" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A176" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A177" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A178" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A179" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A180" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A181" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A182" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A183" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>579</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEE594D-A397-4418-A6B6-6DD42E530A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACCC057-2715-480A-B778-31B0948BAC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="583">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1812,6 +1812,12 @@
   </si>
   <si>
     <t>Монолог, который я услышал, был</t>
+  </si>
+  <si>
+    <t>его «бригады»</t>
+  </si>
+  <si>
+    <t>его «отряда»</t>
   </si>
 </sst>
 </file>
@@ -2083,12 +2089,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="48.1015625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.08984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2096,7 +2102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2104,7 +2110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2112,7 +2118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2120,7 +2126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2128,7 +2134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2136,7 +2142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2144,7 +2150,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2152,7 +2158,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2160,7 +2166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2168,7 +2174,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2176,7 +2182,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -2184,7 +2190,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2192,7 +2198,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2200,7 +2206,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -2208,7 +2214,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2216,7 +2222,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2224,7 +2230,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2232,7 +2238,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2240,7 +2246,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -2248,7 +2254,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -2256,7 +2262,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -2264,7 +2270,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
@@ -2272,7 +2278,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -2280,7 +2286,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -2288,7 +2294,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -2296,7 +2302,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
@@ -2304,7 +2310,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>54</v>
       </c>
@@ -2312,7 +2318,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -2330,13 +2336,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="44.7890625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.15625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.81640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>58</v>
       </c>
@@ -2352,14 +2358,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.1015625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.62890625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -2367,7 +2373,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>62</v>
       </c>
@@ -2375,7 +2381,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>64</v>
       </c>
@@ -2383,7 +2389,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>66</v>
       </c>
@@ -2391,7 +2397,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
@@ -2399,7 +2405,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>70</v>
       </c>
@@ -2407,7 +2413,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>72</v>
       </c>
@@ -2415,7 +2421,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>74</v>
       </c>
@@ -2423,7 +2429,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>76</v>
       </c>
@@ -2431,7 +2437,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>78</v>
       </c>
@@ -2439,7 +2445,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>80</v>
       </c>
@@ -2447,12 +2453,20 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -2464,13 +2478,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B183"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.7890625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.89453125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.81640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.90625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>84</v>
       </c>
@@ -2478,7 +2492,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>86</v>
       </c>
@@ -2486,7 +2500,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>88</v>
       </c>
@@ -2494,7 +2508,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>90</v>
       </c>
@@ -2502,7 +2516,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
@@ -2510,7 +2524,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>94</v>
       </c>
@@ -2518,7 +2532,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>96</v>
       </c>
@@ -2526,7 +2540,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
@@ -2534,7 +2548,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>100</v>
       </c>
@@ -2542,7 +2556,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>102</v>
       </c>
@@ -2550,7 +2564,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>104</v>
       </c>
@@ -2558,7 +2572,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>106</v>
       </c>
@@ -2566,7 +2580,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>108</v>
       </c>
@@ -2574,7 +2588,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>110</v>
       </c>
@@ -2582,7 +2596,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>112</v>
       </c>
@@ -2590,7 +2604,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>114</v>
       </c>
@@ -2598,7 +2612,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>116</v>
       </c>
@@ -2606,7 +2620,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>117</v>
       </c>
@@ -2614,7 +2628,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>119</v>
       </c>
@@ -2622,7 +2636,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>121</v>
       </c>
@@ -2630,7 +2644,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>123</v>
       </c>
@@ -2638,7 +2652,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>125</v>
       </c>
@@ -2646,7 +2660,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>127</v>
       </c>
@@ -2654,7 +2668,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>129</v>
       </c>
@@ -2662,7 +2676,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>131</v>
       </c>
@@ -2670,7 +2684,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>133</v>
       </c>
@@ -2678,7 +2692,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>135</v>
       </c>
@@ -2686,7 +2700,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>137</v>
       </c>
@@ -2694,7 +2708,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>139</v>
       </c>
@@ -2702,7 +2716,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>141</v>
       </c>
@@ -2710,7 +2724,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>143</v>
       </c>
@@ -2718,7 +2732,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>145</v>
       </c>
@@ -2726,7 +2740,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>147</v>
       </c>
@@ -2734,7 +2748,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>149</v>
       </c>
@@ -2742,7 +2756,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>151</v>
       </c>
@@ -2750,7 +2764,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>153</v>
       </c>
@@ -2758,7 +2772,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>155</v>
       </c>
@@ -2766,7 +2780,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>157</v>
       </c>
@@ -2774,7 +2788,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>159</v>
       </c>
@@ -2782,7 +2796,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>161</v>
       </c>
@@ -2790,7 +2804,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>163</v>
       </c>
@@ -2798,7 +2812,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>165</v>
       </c>
@@ -2806,7 +2820,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>167</v>
       </c>
@@ -2814,7 +2828,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>169</v>
       </c>
@@ -2822,7 +2836,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>171</v>
       </c>
@@ -2830,7 +2844,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>173</v>
       </c>
@@ -2838,7 +2852,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>175</v>
       </c>
@@ -2846,7 +2860,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>177</v>
       </c>
@@ -2854,7 +2868,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>179</v>
       </c>
@@ -2862,7 +2876,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>181</v>
       </c>
@@ -2870,7 +2884,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>183</v>
       </c>
@@ -2878,7 +2892,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>185</v>
       </c>
@@ -2886,7 +2900,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>187</v>
       </c>
@@ -2894,7 +2908,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>189</v>
       </c>
@@ -2902,7 +2916,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>191</v>
       </c>
@@ -2910,7 +2924,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>193</v>
       </c>
@@ -2918,7 +2932,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>195</v>
       </c>
@@ -2926,7 +2940,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>197</v>
       </c>
@@ -2934,7 +2948,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>199</v>
       </c>
@@ -2942,7 +2956,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>201</v>
       </c>
@@ -2950,7 +2964,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>203</v>
       </c>
@@ -2958,7 +2972,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>205</v>
       </c>
@@ -2966,7 +2980,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>207</v>
       </c>
@@ -2974,7 +2988,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>209</v>
       </c>
@@ -2982,7 +2996,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>211</v>
       </c>
@@ -2990,7 +3004,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>213</v>
       </c>
@@ -2998,7 +3012,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>215</v>
       </c>
@@ -3006,7 +3020,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>217</v>
       </c>
@@ -3014,7 +3028,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>219</v>
       </c>
@@ -3022,7 +3036,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>221</v>
       </c>
@@ -3030,7 +3044,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>223</v>
       </c>
@@ -3038,7 +3052,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>225</v>
       </c>
@@ -3046,7 +3060,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>227</v>
       </c>
@@ -3054,7 +3068,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>229</v>
       </c>
@@ -3062,7 +3076,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>231</v>
       </c>
@@ -3070,7 +3084,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>233</v>
       </c>
@@ -3078,7 +3092,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>235</v>
       </c>
@@ -3086,7 +3100,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>237</v>
       </c>
@@ -3094,7 +3108,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>239</v>
       </c>
@@ -3102,7 +3116,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>241</v>
       </c>
@@ -3110,7 +3124,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>243</v>
       </c>
@@ -3118,7 +3132,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>245</v>
       </c>
@@ -3126,7 +3140,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>247</v>
       </c>
@@ -3134,7 +3148,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>249</v>
       </c>
@@ -3142,7 +3156,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>251</v>
       </c>
@@ -3150,7 +3164,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>253</v>
       </c>
@@ -3158,7 +3172,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>255</v>
       </c>
@@ -3166,7 +3180,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>257</v>
       </c>
@@ -3174,7 +3188,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>259</v>
       </c>
@@ -3182,7 +3196,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>261</v>
       </c>
@@ -3190,7 +3204,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
         <v>263</v>
       </c>
@@ -3198,7 +3212,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>265</v>
       </c>
@@ -3206,7 +3220,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>267</v>
       </c>
@@ -3214,7 +3228,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>269</v>
       </c>
@@ -3222,7 +3236,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>271</v>
       </c>
@@ -3230,7 +3244,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>273</v>
       </c>
@@ -3238,7 +3252,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
         <v>275</v>
       </c>
@@ -3246,7 +3260,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>277</v>
       </c>
@@ -3254,7 +3268,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>279</v>
       </c>
@@ -3262,7 +3276,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>281</v>
       </c>
@@ -3270,7 +3284,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
         <v>283</v>
       </c>
@@ -3278,7 +3292,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
         <v>285</v>
       </c>
@@ -3286,7 +3300,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>287</v>
       </c>
@@ -3294,7 +3308,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>289</v>
       </c>
@@ -3302,7 +3316,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>291</v>
       </c>
@@ -3310,7 +3324,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="6" t="s">
         <v>293</v>
       </c>
@@ -3318,7 +3332,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>295</v>
       </c>
@@ -3326,7 +3340,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>297</v>
       </c>
@@ -3334,7 +3348,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>299</v>
       </c>
@@ -3342,7 +3356,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
         <v>301</v>
       </c>
@@ -3350,7 +3364,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>303</v>
       </c>
@@ -3358,7 +3372,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>305</v>
       </c>
@@ -3366,7 +3380,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>307</v>
       </c>
@@ -3374,7 +3388,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>309</v>
       </c>
@@ -3382,7 +3396,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>311</v>
       </c>
@@ -3390,7 +3404,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>313</v>
       </c>
@@ -3398,7 +3412,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>315</v>
       </c>
@@ -3406,7 +3420,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>317</v>
       </c>
@@ -3414,7 +3428,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>319</v>
       </c>
@@ -3422,7 +3436,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>321</v>
       </c>
@@ -3430,7 +3444,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>323</v>
       </c>
@@ -3438,7 +3452,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>325</v>
       </c>
@@ -3446,7 +3460,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>327</v>
       </c>
@@ -3454,7 +3468,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
         <v>329</v>
       </c>
@@ -3462,7 +3476,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>331</v>
       </c>
@@ -3470,7 +3484,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
         <v>333</v>
       </c>
@@ -3478,7 +3492,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>335</v>
       </c>
@@ -3486,7 +3500,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
         <v>337</v>
       </c>
@@ -3494,7 +3508,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="7" t="s">
         <v>339</v>
       </c>
@@ -3502,7 +3516,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>341</v>
       </c>
@@ -3510,7 +3524,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
         <v>343</v>
       </c>
@@ -3518,7 +3532,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="7" t="s">
         <v>345</v>
       </c>
@@ -3526,7 +3540,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
         <v>347</v>
       </c>
@@ -3534,7 +3548,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="26.1" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A134" s="7" t="s">
         <v>349</v>
       </c>
@@ -3542,7 +3556,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
         <v>351</v>
       </c>
@@ -3550,7 +3564,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="7" t="s">
         <v>353</v>
       </c>
@@ -3558,7 +3572,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
         <v>355</v>
       </c>
@@ -3566,7 +3580,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>357</v>
       </c>
@@ -3574,7 +3588,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>359</v>
       </c>
@@ -3582,7 +3596,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>361</v>
       </c>
@@ -3590,7 +3604,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
         <v>363</v>
       </c>
@@ -3598,7 +3612,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
         <v>365</v>
       </c>
@@ -3606,7 +3620,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>367</v>
       </c>
@@ -3614,7 +3628,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="7" t="s">
         <v>369</v>
       </c>
@@ -3622,7 +3636,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>371</v>
       </c>
@@ -3630,7 +3644,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="7" t="s">
         <v>373</v>
       </c>
@@ -3638,7 +3652,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>375</v>
       </c>
@@ -3646,7 +3660,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
         <v>377</v>
       </c>
@@ -3654,7 +3668,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>379</v>
       </c>
@@ -3662,7 +3676,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>381</v>
       </c>
@@ -3670,7 +3684,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
         <v>383</v>
       </c>
@@ -3678,7 +3692,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
         <v>385</v>
       </c>
@@ -3686,7 +3700,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
         <v>387</v>
       </c>
@@ -3694,7 +3708,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
         <v>389</v>
       </c>
@@ -3702,7 +3716,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
         <v>391</v>
       </c>
@@ -3710,7 +3724,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="7" t="s">
         <v>393</v>
       </c>
@@ -3718,7 +3732,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="7" t="s">
         <v>395</v>
       </c>
@@ -3726,7 +3740,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>397</v>
       </c>
@@ -3734,7 +3748,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
         <v>399</v>
       </c>
@@ -3742,7 +3756,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
         <v>401</v>
       </c>
@@ -3750,7 +3764,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" s="7" t="s">
         <v>403</v>
       </c>
@@ -3758,7 +3772,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
         <v>405</v>
       </c>
@@ -3766,7 +3780,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" s="7" t="s">
         <v>407</v>
       </c>
@@ -3774,7 +3788,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
         <v>409</v>
       </c>
@@ -3782,7 +3796,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="7" t="s">
         <v>411</v>
       </c>
@@ -3790,7 +3804,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="9" t="s">
         <v>413</v>
       </c>
@@ -3798,7 +3812,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="7" t="s">
         <v>415</v>
       </c>
@@ -3806,7 +3820,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="7" t="s">
         <v>417</v>
       </c>
@@ -3814,7 +3828,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
         <v>551</v>
       </c>
@@ -3822,7 +3836,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="7" t="s">
         <v>554</v>
       </c>
@@ -3830,7 +3844,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
         <v>553</v>
       </c>
@@ -3838,7 +3852,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="7" t="s">
         <v>557</v>
       </c>
@@ -3846,7 +3860,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
         <v>559</v>
       </c>
@@ -3854,7 +3868,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
         <v>561</v>
       </c>
@@ -3862,7 +3876,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
         <v>563</v>
       </c>
@@ -3870,7 +3884,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
         <v>565</v>
       </c>
@@ -3878,7 +3892,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" s="7" t="s">
         <v>567</v>
       </c>
@@ -3886,7 +3900,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" s="7" t="s">
         <v>569</v>
       </c>
@@ -3894,7 +3908,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
         <v>571</v>
       </c>
@@ -3902,7 +3916,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="7" t="s">
         <v>573</v>
       </c>
@@ -3910,7 +3924,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>575</v>
       </c>
@@ -3918,7 +3932,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="7" t="s">
         <v>577</v>
       </c>
@@ -3926,7 +3940,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" s="7" t="s">
         <v>580</v>
       </c>
@@ -3943,13 +3957,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.3671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.7890625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="52.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.81640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>419</v>
       </c>
@@ -3957,7 +3971,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>421</v>
       </c>
@@ -3965,7 +3979,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>423</v>
       </c>
@@ -3973,7 +3987,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>425</v>
       </c>
@@ -3981,7 +3995,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>427</v>
       </c>
@@ -3989,7 +4003,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>429</v>
       </c>
@@ -3997,7 +4011,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>431</v>
       </c>
@@ -4005,7 +4019,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="38.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>433</v>
       </c>
@@ -4013,7 +4027,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="38.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>435</v>
       </c>
@@ -4021,7 +4035,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>437</v>
       </c>
@@ -4038,13 +4052,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="51.68359375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>439</v>
       </c>
@@ -4052,7 +4066,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>441</v>
       </c>
@@ -4060,7 +4074,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>443</v>
       </c>
@@ -4068,7 +4082,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>445</v>
       </c>
@@ -4076,7 +4090,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>447</v>
       </c>
@@ -4084,7 +4098,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>449</v>
       </c>
@@ -4092,7 +4106,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>451</v>
       </c>
@@ -4100,7 +4114,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>453</v>
       </c>
@@ -4108,7 +4122,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>455</v>
       </c>
@@ -4116,7 +4130,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>457</v>
       </c>
@@ -4124,7 +4138,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>459</v>
       </c>
@@ -4132,7 +4146,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>461</v>
       </c>
@@ -4140,7 +4154,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>463</v>
       </c>
@@ -4148,7 +4162,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>465</v>
       </c>
@@ -4156,7 +4170,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>467</v>
       </c>
@@ -4164,7 +4178,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>469</v>
       </c>
@@ -4172,7 +4186,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>471</v>
       </c>
@@ -4180,7 +4194,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>473</v>
       </c>
@@ -4188,7 +4202,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>475</v>
       </c>
@@ -4196,7 +4210,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>477</v>
       </c>
@@ -4204,7 +4218,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>479</v>
       </c>
@@ -4212,7 +4226,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>481</v>
       </c>
@@ -4220,7 +4234,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>483</v>
       </c>
@@ -4228,7 +4242,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>485</v>
       </c>
@@ -4236,7 +4250,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>487</v>
       </c>
@@ -4244,7 +4258,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>489</v>
       </c>
@@ -4252,7 +4266,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>491</v>
       </c>
@@ -4260,7 +4274,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>493</v>
       </c>
@@ -4268,7 +4282,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>495</v>
       </c>
@@ -4276,7 +4290,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>497</v>
       </c>
@@ -4284,7 +4298,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>499</v>
       </c>
@@ -4292,7 +4306,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>501</v>
       </c>
@@ -4300,7 +4314,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>503</v>
       </c>
@@ -4308,7 +4322,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>505</v>
       </c>
@@ -4316,7 +4330,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>397</v>
       </c>
@@ -4324,7 +4338,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>508</v>
       </c>
@@ -4332,7 +4346,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>510</v>
       </c>
@@ -4340,7 +4354,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="29.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>512</v>
       </c>
@@ -4348,7 +4362,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>514</v>
       </c>
@@ -4356,7 +4370,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>516</v>
       </c>
@@ -4364,7 +4378,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>518</v>
       </c>
@@ -4372,7 +4386,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>520</v>
       </c>
@@ -4380,7 +4394,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>522</v>
       </c>
@@ -4388,7 +4402,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>549</v>
       </c>
@@ -4405,18 +4419,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.41796875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.62890625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>525</v>
       </c>
@@ -4424,22 +4438,22 @@
         <v>526</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>530</v>
       </c>
@@ -4447,7 +4461,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>532</v>
       </c>
@@ -4455,7 +4469,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>534</v>
       </c>
@@ -4463,7 +4477,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>536</v>
       </c>
@@ -4471,12 +4485,12 @@
         <v>537</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>539</v>
       </c>
@@ -4484,7 +4498,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>541</v>
       </c>
@@ -4492,7 +4506,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>543</v>
       </c>
@@ -4500,7 +4514,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>545</v>
       </c>
@@ -4508,7 +4522,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>547</v>
       </c>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACCC057-2715-480A-B778-31B0948BAC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34191300-8688-4E22-96AF-4B5B6FE285BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="624">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1818,6 +1818,129 @@
   </si>
   <si>
     <t>его «отряда»</t>
+  </si>
+  <si>
+    <t>вышеупомянутый секстет</t>
+  </si>
+  <si>
+    <t>вышеупомянутых шестерых</t>
+  </si>
+  <si>
+    <t>пап и школы, а</t>
+  </si>
+  <si>
+    <t>пап и учебного заведения, а</t>
+  </si>
+  <si>
+    <t>весь комплекс, с</t>
+  </si>
+  <si>
+    <t>всю гостинницу и приложения к ней, с</t>
+  </si>
+  <si>
+    <t>военным и к форме</t>
+  </si>
+  <si>
+    <t>военным и к военному покрову</t>
+  </si>
+  <si>
+    <t>Шанс остаться был, но неприемлемый</t>
+  </si>
+  <si>
+    <t>Возможность остаться была, но неприемлемая</t>
+  </si>
+  <si>
+    <t>убрали из процесса</t>
+  </si>
+  <si>
+    <t>убрали из судебного разбирательства</t>
+  </si>
+  <si>
+    <t>На этом процессе присутствовали</t>
+  </si>
+  <si>
+    <t>На этом судебном разбирательстве присутствовали</t>
+  </si>
+  <si>
+    <t>3 в 1</t>
+  </si>
+  <si>
+    <t>это дилемму</t>
+  </si>
+  <si>
+    <t>эту дилемму</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На это вопрос </t>
+  </si>
+  <si>
+    <t xml:space="preserve">На этот вопрос </t>
+  </si>
+  <si>
+    <t>ничего себе бригады</t>
+  </si>
+  <si>
+    <t>ничего себе отряда</t>
+  </si>
+  <si>
+    <t>сбора «бригады»</t>
+  </si>
+  <si>
+    <t>сбора «отряда»</t>
+  </si>
+  <si>
+    <t>подобная вид трудовой деятельности</t>
+  </si>
+  <si>
+    <t>подобный вид трудовой деятельности</t>
+  </si>
+  <si>
+    <t>Железная, кровавая, и никого, кроме 3–5 избранных не жалеющая</t>
+  </si>
+  <si>
+    <t>Железные, кровавые, и никого, кроме 3–5 избранных не жалеющие</t>
+  </si>
+  <si>
+    <t>Моя же профессия определялась</t>
+  </si>
+  <si>
+    <t>Мой же вид трудовой деятельности определялся</t>
+  </si>
+  <si>
+    <t>из военных команд сотни</t>
+  </si>
+  <si>
+    <t>из военных учреждений сотни</t>
+  </si>
+  <si>
+    <t>грустные карикатуры или кровавые комиксы</t>
+  </si>
+  <si>
+    <t>грустные изображения или кровавые рассказы</t>
+  </si>
+  <si>
+    <t>гильотина уголовных дел</t>
+  </si>
+  <si>
+    <t>казнь уголовных дел</t>
+  </si>
+  <si>
+    <t>общей людской исторической массы</t>
+  </si>
+  <si>
+    <t>общей летописи народа</t>
+  </si>
+  <si>
+    <t>сам факт столкновения так и не был подтверждён</t>
+  </si>
+  <si>
+    <t>само обстоятельство столкновения так и не было подтверждено</t>
+  </si>
+  <si>
+    <t>свое белой</t>
+  </si>
+  <si>
+    <t>своей белой</t>
   </si>
 </sst>
 </file>
@@ -1874,7 +1997,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -1895,6 +2018,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2358,7 +2482,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.08984375" style="5" customWidth="1"/>
@@ -2469,6 +2593,14 @@
         <v>582</v>
       </c>
     </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>584</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2477,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B183"/>
+  <dimension ref="A1:B191"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.81640625" style="5" customWidth="1"/>
@@ -3948,6 +4080,70 @@
         <v>579</v>
       </c>
     </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A184" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A185" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A186" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A187" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A188" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A189" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A190" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A191" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>605</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3956,7 +4152,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="52.36328125" style="1" customWidth="1"/>
@@ -4043,6 +4239,14 @@
         <v>438</v>
       </c>
     </row>
+    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4051,7 +4255,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="51.6328125" style="1" customWidth="1"/>
@@ -4410,6 +4614,54 @@
         <v>550</v>
       </c>
     </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4418,7 +4670,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
@@ -4530,6 +4782,43 @@
         <v>548</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>623</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34191300-8688-4E22-96AF-4B5B6FE285BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FDDDE0-9F74-4013-A8B8-8692351F14EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="628">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1941,6 +1941,18 @@
   </si>
   <si>
     <t>своей белой</t>
+  </si>
+  <si>
+    <t>убрано в полном</t>
+  </si>
+  <si>
+    <t>новом крёстном отце</t>
+  </si>
+  <si>
+    <t>эту бригаду</t>
+  </si>
+  <si>
+    <t>Дмитрий взял на обдумывание</t>
   </si>
 </sst>
 </file>
@@ -2213,12 +2225,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="48.08984375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1015625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2226,7 +2238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2234,7 +2246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2242,7 +2254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2250,7 +2262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2258,7 +2270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2266,7 +2278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2274,7 +2286,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2282,7 +2294,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2290,7 +2302,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2298,7 +2310,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2306,7 +2318,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -2314,7 +2326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2322,7 +2334,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,7 +2342,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -2338,7 +2350,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2346,7 +2358,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2354,7 +2366,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2362,7 +2374,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2370,7 +2382,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -2378,7 +2390,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -2386,7 +2398,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -2394,7 +2406,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
@@ -2402,7 +2414,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,7 +2422,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -2418,7 +2430,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -2426,7 +2438,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
@@ -2434,7 +2446,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4" t="s">
         <v>54</v>
       </c>
@@ -2442,7 +2454,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -2460,13 +2472,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="44.81640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.7890625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.15625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>58</v>
       </c>
@@ -2483,13 +2495,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="26.08984375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.1015625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.62890625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -2497,7 +2509,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
         <v>62</v>
       </c>
@@ -2505,7 +2517,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>64</v>
       </c>
@@ -2513,7 +2525,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
         <v>66</v>
       </c>
@@ -2521,7 +2533,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
@@ -2529,7 +2541,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>70</v>
       </c>
@@ -2537,7 +2549,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
         <v>72</v>
       </c>
@@ -2545,7 +2557,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
         <v>74</v>
       </c>
@@ -2553,7 +2565,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
         <v>76</v>
       </c>
@@ -2561,7 +2573,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
         <v>78</v>
       </c>
@@ -2569,7 +2581,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
         <v>80</v>
       </c>
@@ -2577,7 +2589,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
         <v>82</v>
       </c>
@@ -2585,7 +2597,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
         <v>581</v>
       </c>
@@ -2593,7 +2605,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
         <v>583</v>
       </c>
@@ -2610,13 +2622,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B191"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="48.81640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.90625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.7890625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.89453125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>84</v>
       </c>
@@ -2624,7 +2636,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
         <v>86</v>
       </c>
@@ -2632,7 +2644,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
         <v>88</v>
       </c>
@@ -2640,7 +2652,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
         <v>90</v>
       </c>
@@ -2648,7 +2660,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>92</v>
       </c>
@@ -2656,7 +2668,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
         <v>94</v>
       </c>
@@ -2664,7 +2676,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>96</v>
       </c>
@@ -2672,7 +2684,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
@@ -2680,7 +2692,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
         <v>100</v>
       </c>
@@ -2688,7 +2700,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
         <v>102</v>
       </c>
@@ -2696,7 +2708,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
         <v>104</v>
       </c>
@@ -2704,7 +2716,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
         <v>106</v>
       </c>
@@ -2712,7 +2724,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
         <v>108</v>
       </c>
@@ -2720,7 +2732,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
         <v>110</v>
       </c>
@@ -2728,7 +2740,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
         <v>112</v>
       </c>
@@ -2736,7 +2748,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
         <v>114</v>
       </c>
@@ -2744,7 +2756,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5" t="s">
         <v>116</v>
       </c>
@@ -2752,7 +2764,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5" t="s">
         <v>117</v>
       </c>
@@ -2760,7 +2772,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="5" t="s">
         <v>119</v>
       </c>
@@ -2768,7 +2780,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5" t="s">
         <v>121</v>
       </c>
@@ -2776,7 +2788,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="5" t="s">
         <v>123</v>
       </c>
@@ -2784,7 +2796,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>125</v>
       </c>
@@ -2792,7 +2804,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="5" t="s">
         <v>127</v>
       </c>
@@ -2800,7 +2812,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="5" t="s">
         <v>129</v>
       </c>
@@ -2808,7 +2820,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>131</v>
       </c>
@@ -2816,7 +2828,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="5" t="s">
         <v>133</v>
       </c>
@@ -2824,7 +2836,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="5" t="s">
         <v>135</v>
       </c>
@@ -2832,7 +2844,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="5" t="s">
         <v>137</v>
       </c>
@@ -2840,7 +2852,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="5" t="s">
         <v>139</v>
       </c>
@@ -2848,7 +2860,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="5" t="s">
         <v>141</v>
       </c>
@@ -2856,7 +2868,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="5" t="s">
         <v>143</v>
       </c>
@@ -2864,7 +2876,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="5" t="s">
         <v>145</v>
       </c>
@@ -2872,7 +2884,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="5" t="s">
         <v>147</v>
       </c>
@@ -2880,7 +2892,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="5" t="s">
         <v>149</v>
       </c>
@@ -2888,7 +2900,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="5" t="s">
         <v>151</v>
       </c>
@@ -2896,7 +2908,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="5" t="s">
         <v>153</v>
       </c>
@@ -2904,7 +2916,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="5" t="s">
         <v>155</v>
       </c>
@@ -2912,7 +2924,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>157</v>
       </c>
@@ -2920,7 +2932,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="5" t="s">
         <v>159</v>
       </c>
@@ -2928,7 +2940,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="5" t="s">
         <v>161</v>
       </c>
@@ -2936,7 +2948,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="5" t="s">
         <v>163</v>
       </c>
@@ -2944,7 +2956,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="5" t="s">
         <v>165</v>
       </c>
@@ -2952,7 +2964,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="5" t="s">
         <v>167</v>
       </c>
@@ -2960,7 +2972,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="5" t="s">
         <v>169</v>
       </c>
@@ -2968,7 +2980,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="5" t="s">
         <v>171</v>
       </c>
@@ -2976,7 +2988,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="5" t="s">
         <v>173</v>
       </c>
@@ -2984,7 +2996,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="5" t="s">
         <v>175</v>
       </c>
@@ -2992,7 +3004,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="5" t="s">
         <v>177</v>
       </c>
@@ -3000,7 +3012,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="5" t="s">
         <v>179</v>
       </c>
@@ -3008,7 +3020,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="6" t="s">
         <v>181</v>
       </c>
@@ -3016,7 +3028,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="5" t="s">
         <v>183</v>
       </c>
@@ -3024,7 +3036,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="5" t="s">
         <v>185</v>
       </c>
@@ -3032,7 +3044,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="5" t="s">
         <v>187</v>
       </c>
@@ -3040,7 +3052,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="5" t="s">
         <v>189</v>
       </c>
@@ -3048,7 +3060,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="5" t="s">
         <v>191</v>
       </c>
@@ -3056,7 +3068,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="6" t="s">
         <v>193</v>
       </c>
@@ -3064,7 +3076,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="5" t="s">
         <v>195</v>
       </c>
@@ -3072,7 +3084,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="5" t="s">
         <v>197</v>
       </c>
@@ -3080,7 +3092,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="5" t="s">
         <v>199</v>
       </c>
@@ -3088,7 +3100,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="5" t="s">
         <v>201</v>
       </c>
@@ -3096,7 +3108,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="5" t="s">
         <v>203</v>
       </c>
@@ -3104,7 +3116,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="5" t="s">
         <v>205</v>
       </c>
@@ -3112,7 +3124,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="5" t="s">
         <v>207</v>
       </c>
@@ -3120,7 +3132,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="5" t="s">
         <v>209</v>
       </c>
@@ -3128,7 +3140,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="5" t="s">
         <v>211</v>
       </c>
@@ -3136,7 +3148,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="5" t="s">
         <v>213</v>
       </c>
@@ -3144,7 +3156,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="5" t="s">
         <v>215</v>
       </c>
@@ -3152,7 +3164,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="5" t="s">
         <v>217</v>
       </c>
@@ -3160,7 +3172,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="5" t="s">
         <v>219</v>
       </c>
@@ -3168,7 +3180,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="5" t="s">
         <v>221</v>
       </c>
@@ -3176,7 +3188,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="5" t="s">
         <v>223</v>
       </c>
@@ -3184,7 +3196,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="5" t="s">
         <v>225</v>
       </c>
@@ -3192,7 +3204,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="5" t="s">
         <v>227</v>
       </c>
@@ -3200,7 +3212,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="5" t="s">
         <v>229</v>
       </c>
@@ -3208,7 +3220,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="5" t="s">
         <v>231</v>
       </c>
@@ -3216,7 +3228,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="5" t="s">
         <v>233</v>
       </c>
@@ -3224,7 +3236,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="5" t="s">
         <v>235</v>
       </c>
@@ -3232,7 +3244,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="5" t="s">
         <v>237</v>
       </c>
@@ -3240,7 +3252,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="5" t="s">
         <v>239</v>
       </c>
@@ -3248,7 +3260,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="5" t="s">
         <v>241</v>
       </c>
@@ -3256,7 +3268,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="5" t="s">
         <v>243</v>
       </c>
@@ -3264,7 +3276,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="5" t="s">
         <v>245</v>
       </c>
@@ -3272,7 +3284,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="5" t="s">
         <v>247</v>
       </c>
@@ -3280,7 +3292,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="5" t="s">
         <v>249</v>
       </c>
@@ -3288,7 +3300,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="5" t="s">
         <v>251</v>
       </c>
@@ -3296,7 +3308,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="5" t="s">
         <v>253</v>
       </c>
@@ -3304,7 +3316,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="5" t="s">
         <v>255</v>
       </c>
@@ -3312,7 +3324,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="5" t="s">
         <v>257</v>
       </c>
@@ -3320,7 +3332,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="5" t="s">
         <v>259</v>
       </c>
@@ -3328,7 +3340,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="5" t="s">
         <v>261</v>
       </c>
@@ -3336,7 +3348,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="5" t="s">
         <v>263</v>
       </c>
@@ -3344,7 +3356,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="5" t="s">
         <v>265</v>
       </c>
@@ -3352,7 +3364,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="5" t="s">
         <v>267</v>
       </c>
@@ -3360,7 +3372,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="5" t="s">
         <v>269</v>
       </c>
@@ -3368,7 +3380,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="5" t="s">
         <v>271</v>
       </c>
@@ -3376,7 +3388,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="5" t="s">
         <v>273</v>
       </c>
@@ -3384,7 +3396,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="5" t="s">
         <v>275</v>
       </c>
@@ -3392,7 +3404,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="5" t="s">
         <v>277</v>
       </c>
@@ -3400,7 +3412,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="5" t="s">
         <v>279</v>
       </c>
@@ -3408,7 +3420,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="5" t="s">
         <v>281</v>
       </c>
@@ -3416,7 +3428,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="5" t="s">
         <v>283</v>
       </c>
@@ -3424,7 +3436,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="5" t="s">
         <v>285</v>
       </c>
@@ -3432,7 +3444,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="5" t="s">
         <v>287</v>
       </c>
@@ -3440,7 +3452,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="5" t="s">
         <v>289</v>
       </c>
@@ -3448,7 +3460,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="5" t="s">
         <v>291</v>
       </c>
@@ -3456,7 +3468,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="6" t="s">
         <v>293</v>
       </c>
@@ -3464,7 +3476,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="5" t="s">
         <v>295</v>
       </c>
@@ -3472,7 +3484,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="5" t="s">
         <v>297</v>
       </c>
@@ -3480,7 +3492,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1" t="s">
         <v>299</v>
       </c>
@@ -3488,7 +3500,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="5" t="s">
         <v>301</v>
       </c>
@@ -3496,7 +3508,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="7" t="s">
         <v>303</v>
       </c>
@@ -3504,7 +3516,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="7" t="s">
         <v>305</v>
       </c>
@@ -3512,7 +3524,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="7" t="s">
         <v>307</v>
       </c>
@@ -3520,7 +3532,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="7" t="s">
         <v>309</v>
       </c>
@@ -3528,7 +3540,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="7" t="s">
         <v>311</v>
       </c>
@@ -3536,7 +3548,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="7" t="s">
         <v>313</v>
       </c>
@@ -3544,7 +3556,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="7" t="s">
         <v>315</v>
       </c>
@@ -3552,7 +3564,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="7" t="s">
         <v>317</v>
       </c>
@@ -3560,7 +3572,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="7" t="s">
         <v>319</v>
       </c>
@@ -3568,7 +3580,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="7" t="s">
         <v>321</v>
       </c>
@@ -3576,7 +3588,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="7" t="s">
         <v>323</v>
       </c>
@@ -3584,7 +3596,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="7" t="s">
         <v>325</v>
       </c>
@@ -3592,7 +3604,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="7" t="s">
         <v>327</v>
       </c>
@@ -3600,7 +3612,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="7" t="s">
         <v>329</v>
       </c>
@@ -3608,7 +3620,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="7" t="s">
         <v>331</v>
       </c>
@@ -3616,7 +3628,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="7" t="s">
         <v>333</v>
       </c>
@@ -3624,7 +3636,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="7" t="s">
         <v>335</v>
       </c>
@@ -3632,7 +3644,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="7" t="s">
         <v>337</v>
       </c>
@@ -3640,7 +3652,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="7" t="s">
         <v>339</v>
       </c>
@@ -3648,7 +3660,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="7" t="s">
         <v>341</v>
       </c>
@@ -3656,7 +3668,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="7" t="s">
         <v>343</v>
       </c>
@@ -3664,7 +3676,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="7" t="s">
         <v>345</v>
       </c>
@@ -3672,7 +3684,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="7" t="s">
         <v>347</v>
       </c>
@@ -3680,7 +3692,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" ht="26.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="7" t="s">
         <v>349</v>
       </c>
@@ -3688,7 +3700,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="7" t="s">
         <v>351</v>
       </c>
@@ -3696,7 +3708,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="7" t="s">
         <v>353</v>
       </c>
@@ -3704,7 +3716,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="7" t="s">
         <v>355</v>
       </c>
@@ -3712,7 +3724,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="7" t="s">
         <v>357</v>
       </c>
@@ -3720,7 +3732,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="7" t="s">
         <v>359</v>
       </c>
@@ -3728,7 +3740,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="7" t="s">
         <v>361</v>
       </c>
@@ -3736,7 +3748,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="7" t="s">
         <v>363</v>
       </c>
@@ -3744,7 +3756,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="7" t="s">
         <v>365</v>
       </c>
@@ -3752,7 +3764,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="7" t="s">
         <v>367</v>
       </c>
@@ -3760,7 +3772,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="7" t="s">
         <v>369</v>
       </c>
@@ -3768,7 +3780,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="7" t="s">
         <v>371</v>
       </c>
@@ -3776,7 +3788,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="7" t="s">
         <v>373</v>
       </c>
@@ -3784,7 +3796,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="7" t="s">
         <v>375</v>
       </c>
@@ -3792,7 +3804,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="7" t="s">
         <v>377</v>
       </c>
@@ -3800,7 +3812,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="7" t="s">
         <v>379</v>
       </c>
@@ -3808,7 +3820,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="7" t="s">
         <v>381</v>
       </c>
@@ -3816,7 +3828,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="7" t="s">
         <v>383</v>
       </c>
@@ -3824,7 +3836,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="7" t="s">
         <v>385</v>
       </c>
@@ -3832,7 +3844,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="7" t="s">
         <v>387</v>
       </c>
@@ -3840,7 +3852,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="7" t="s">
         <v>389</v>
       </c>
@@ -3848,7 +3860,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="7" t="s">
         <v>391</v>
       </c>
@@ -3856,7 +3868,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="7" t="s">
         <v>393</v>
       </c>
@@ -3864,7 +3876,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="7" t="s">
         <v>395</v>
       </c>
@@ -3872,7 +3884,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="1" t="s">
         <v>397</v>
       </c>
@@ -3880,7 +3892,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="7" t="s">
         <v>399</v>
       </c>
@@ -3888,7 +3900,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="7" t="s">
         <v>401</v>
       </c>
@@ -3896,7 +3908,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="7" t="s">
         <v>403</v>
       </c>
@@ -3904,7 +3916,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="7" t="s">
         <v>405</v>
       </c>
@@ -3912,7 +3924,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="7" t="s">
         <v>407</v>
       </c>
@@ -3920,7 +3932,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="7" t="s">
         <v>409</v>
       </c>
@@ -3928,7 +3940,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="7" t="s">
         <v>411</v>
       </c>
@@ -3936,7 +3948,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="9" t="s">
         <v>413</v>
       </c>
@@ -3944,7 +3956,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="7" t="s">
         <v>415</v>
       </c>
@@ -3952,7 +3964,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="7" t="s">
         <v>417</v>
       </c>
@@ -3960,7 +3972,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="7" t="s">
         <v>551</v>
       </c>
@@ -3968,7 +3980,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="7" t="s">
         <v>554</v>
       </c>
@@ -3976,7 +3988,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="7" t="s">
         <v>553</v>
       </c>
@@ -3984,7 +3996,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="7" t="s">
         <v>557</v>
       </c>
@@ -3992,7 +4004,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="7" t="s">
         <v>559</v>
       </c>
@@ -4000,7 +4012,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="7" t="s">
         <v>561</v>
       </c>
@@ -4008,7 +4020,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="7" t="s">
         <v>563</v>
       </c>
@@ -4016,7 +4028,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="7" t="s">
         <v>565</v>
       </c>
@@ -4024,7 +4036,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="7" t="s">
         <v>567</v>
       </c>
@@ -4032,7 +4044,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="7" t="s">
         <v>569</v>
       </c>
@@ -4040,7 +4052,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="7" t="s">
         <v>571</v>
       </c>
@@ -4048,7 +4060,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="7" t="s">
         <v>573</v>
       </c>
@@ -4056,7 +4068,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="7" t="s">
         <v>575</v>
       </c>
@@ -4064,7 +4076,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="7" t="s">
         <v>577</v>
       </c>
@@ -4072,7 +4084,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="7" t="s">
         <v>580</v>
       </c>
@@ -4080,7 +4092,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="7" t="s">
         <v>585</v>
       </c>
@@ -4088,7 +4100,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="7" t="s">
         <v>587</v>
       </c>
@@ -4096,7 +4108,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="7" t="s">
         <v>589</v>
       </c>
@@ -4104,7 +4116,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="7" t="s">
         <v>591</v>
       </c>
@@ -4112,7 +4124,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="7" t="s">
         <v>593</v>
       </c>
@@ -4120,7 +4132,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="7" t="s">
         <v>595</v>
       </c>
@@ -4128,7 +4140,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="7" t="s">
         <v>602</v>
       </c>
@@ -4136,7 +4148,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="7" t="s">
         <v>604</v>
       </c>
@@ -4153,13 +4165,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="52.36328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="52.3671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.7890625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>419</v>
       </c>
@@ -4167,7 +4179,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>421</v>
       </c>
@@ -4175,7 +4187,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>423</v>
       </c>
@@ -4183,7 +4195,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>425</v>
       </c>
@@ -4191,7 +4203,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>427</v>
       </c>
@@ -4199,7 +4211,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>429</v>
       </c>
@@ -4207,7 +4219,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>431</v>
       </c>
@@ -4215,7 +4227,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="38.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
         <v>433</v>
       </c>
@@ -4223,7 +4235,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="38.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4" t="s">
         <v>435</v>
       </c>
@@ -4231,7 +4243,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
         <v>437</v>
       </c>
@@ -4239,7 +4251,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>608</v>
       </c>
@@ -4256,13 +4268,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="51.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.90625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.62890625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>439</v>
       </c>
@@ -4270,7 +4282,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>441</v>
       </c>
@@ -4278,7 +4290,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>443</v>
       </c>
@@ -4286,7 +4298,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>445</v>
       </c>
@@ -4294,7 +4306,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>447</v>
       </c>
@@ -4302,7 +4314,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>449</v>
       </c>
@@ -4310,7 +4322,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>451</v>
       </c>
@@ -4318,7 +4330,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>453</v>
       </c>
@@ -4326,7 +4338,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>455</v>
       </c>
@@ -4334,7 +4346,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>457</v>
       </c>
@@ -4342,7 +4354,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>459</v>
       </c>
@@ -4350,7 +4362,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>461</v>
       </c>
@@ -4358,7 +4370,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>463</v>
       </c>
@@ -4366,7 +4378,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>465</v>
       </c>
@@ -4374,7 +4386,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>467</v>
       </c>
@@ -4382,7 +4394,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>469</v>
       </c>
@@ -4390,7 +4402,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>471</v>
       </c>
@@ -4398,7 +4410,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>473</v>
       </c>
@@ -4406,7 +4418,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>475</v>
       </c>
@@ -4414,7 +4426,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>477</v>
       </c>
@@ -4422,7 +4434,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>479</v>
       </c>
@@ -4430,7 +4442,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>481</v>
       </c>
@@ -4438,7 +4450,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>483</v>
       </c>
@@ -4446,7 +4458,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>485</v>
       </c>
@@ -4454,7 +4466,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>487</v>
       </c>
@@ -4462,7 +4474,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>489</v>
       </c>
@@ -4470,7 +4482,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>491</v>
       </c>
@@ -4478,7 +4490,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>493</v>
       </c>
@@ -4486,7 +4498,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>495</v>
       </c>
@@ -4494,7 +4506,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>497</v>
       </c>
@@ -4502,7 +4514,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
         <v>499</v>
       </c>
@@ -4510,7 +4522,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4" t="s">
         <v>501</v>
       </c>
@@ -4518,7 +4530,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="7" t="s">
         <v>503</v>
       </c>
@@ -4526,7 +4538,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
         <v>505</v>
       </c>
@@ -4534,7 +4546,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
         <v>397</v>
       </c>
@@ -4542,7 +4554,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
         <v>508</v>
       </c>
@@ -4550,7 +4562,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
         <v>510</v>
       </c>
@@ -4558,7 +4570,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>512</v>
       </c>
@@ -4566,7 +4578,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="4" t="s">
         <v>514</v>
       </c>
@@ -4574,7 +4586,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="4" t="s">
         <v>516</v>
       </c>
@@ -4582,7 +4594,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="4" t="s">
         <v>518</v>
       </c>
@@ -4590,7 +4602,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4" t="s">
         <v>520</v>
       </c>
@@ -4598,7 +4610,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="9" t="s">
         <v>522</v>
       </c>
@@ -4606,7 +4618,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
         <v>549</v>
       </c>
@@ -4614,7 +4626,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
         <v>610</v>
       </c>
@@ -4622,7 +4634,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
         <v>612</v>
       </c>
@@ -4630,7 +4642,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
         <v>614</v>
       </c>
@@ -4638,7 +4650,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="10" t="s">
         <v>616</v>
       </c>
@@ -4646,7 +4658,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
         <v>618</v>
       </c>
@@ -4654,7 +4666,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
         <v>620</v>
       </c>
@@ -4670,19 +4682,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.6328125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32.47265625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.62890625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
         <v>525</v>
       </c>
@@ -4690,22 +4705,31 @@
         <v>526</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B3" s="5" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="5" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="5" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
         <v>530</v>
       </c>
@@ -4713,7 +4737,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>532</v>
       </c>
@@ -4721,15 +4745,18 @@
         <v>533</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>534</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
         <v>536</v>
       </c>
@@ -4737,12 +4764,12 @@
         <v>537</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7" t="s">
         <v>539</v>
       </c>
@@ -4750,7 +4777,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7" t="s">
         <v>541</v>
       </c>
@@ -4758,7 +4785,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7" t="s">
         <v>543</v>
       </c>
@@ -4766,7 +4793,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>545</v>
       </c>
@@ -4774,7 +4801,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="7" t="s">
         <v>547</v>
       </c>
@@ -4782,12 +4809,12 @@
         <v>548</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="7" t="s">
         <v>598</v>
       </c>
@@ -4795,7 +4822,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7" t="s">
         <v>600</v>
       </c>
@@ -4803,7 +4830,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="7" t="s">
         <v>606</v>
       </c>
@@ -4811,7 +4838,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="7" t="s">
         <v>622</v>
       </c>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FDDDE0-9F74-4013-A8B8-8692351F14EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0851D0E3-EE6E-425D-BA24-C22A0F46AD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="636">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1953,6 +1953,30 @@
   </si>
   <si>
     <t>Дмитрий взял на обдумывание</t>
+  </si>
+  <si>
+    <t>свой «спецназ»</t>
+  </si>
+  <si>
+    <t>своё «особое подразделение»</t>
+  </si>
+  <si>
+    <t>часть «бригады»</t>
+  </si>
+  <si>
+    <t>часть «отряда»</t>
+  </si>
+  <si>
+    <t>охранного предприятия</t>
+  </si>
+  <si>
+    <t>охранной структуры</t>
+  </si>
+  <si>
+    <t>российского бизнеса, который</t>
+  </si>
+  <si>
+    <t>российского предпринимательства, которое</t>
   </si>
 </sst>
 </file>
@@ -2494,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="26.1015625" style="5" customWidth="1"/>
@@ -2613,6 +2637,22 @@
         <v>584</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>632</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2621,7 +2661,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B191"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="48.7890625" style="5" customWidth="1"/>
@@ -4154,6 +4194,14 @@
       </c>
       <c r="B191" s="7" t="s">
         <v>605</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A192" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -4267,7 +4315,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="51.62890625" style="1" customWidth="1"/>
@@ -4672,6 +4720,14 @@
       </c>
       <c r="B50" s="1" t="s">
         <v>621</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>635</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0851D0E3-EE6E-425D-BA24-C22A0F46AD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CEA770-68EE-4B9B-A209-BB07D0624F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" tabRatio="697" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="635">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -161,9 +161,6 @@
     <t>планах компании (возглавляемой</t>
   </si>
   <si>
-    <t>планах предприятия (возглавляемого</t>
-  </si>
-  <si>
     <t>с тёмным салоном</t>
   </si>
   <si>
@@ -329,9 +326,6 @@
     <t>был оформлен паспорт</t>
   </si>
   <si>
-    <t>был указан паспорт</t>
-  </si>
-  <si>
     <t>в командах под руководством</t>
   </si>
   <si>
@@ -359,9 +353,6 @@
     <t>грифы, находящихся там документов</t>
   </si>
   <si>
-    <t>уровни тайн, находящихся там документов</t>
-  </si>
-  <si>
     <t>делили одну команду</t>
   </si>
   <si>
@@ -398,9 +389,6 @@
     <t>дружественных «отрядов»</t>
   </si>
   <si>
-    <t>жаркому пару</t>
-  </si>
-  <si>
     <t>из «бригады»</t>
   </si>
   <si>
@@ -416,9 +404,6 @@
     <t>из номера в коридор</t>
   </si>
   <si>
-    <t>из палаты в коридор</t>
-  </si>
-  <si>
     <t>Из номера приходилось</t>
   </si>
   <si>
@@ -488,9 +473,6 @@
     <t>лелеемую еврейскими банкирами тему</t>
   </si>
   <si>
-    <t>лелеемый еврейскими банкирами вопрос</t>
-  </si>
-  <si>
     <t>Лёша-Солдат</t>
   </si>
   <si>
@@ -1074,9 +1056,6 @@
   </si>
   <si>
     <t xml:space="preserve">балконом снятого номера </t>
-  </si>
-  <si>
-    <t>балконом снятых гостинничных хором</t>
   </si>
   <si>
     <t>дефолт, который произвёл</t>
@@ -1360,9 +1339,6 @@
     <t>Того же типа была история с танзанитами, о которой я узнал после её идиотского окончания и о которой</t>
   </si>
   <si>
-    <t>Того же вида был случай с танзанитами, о котором я узнал после его идиотского окончания и о котором</t>
-  </si>
-  <si>
     <t>позволю ситуации развиться до критической и смогу вовремя ее остановить</t>
   </si>
   <si>
@@ -1372,9 +1348,6 @@
     <t>уголовно-криминальный момент, имевший место быть, прошедший проверку и апробацию королевской полицией, «пальнул»</t>
   </si>
   <si>
-    <t>Уголовно-преступная особенность, имевшая место быть, прошедшая проверку и апробацию королевской полицией, «пальнула»</t>
-  </si>
-  <si>
     <t>Весь его офис, который за время нашего общения поменялся трижды, становясь всё более престижным, был уставлен</t>
   </si>
   <si>
@@ -1442,9 +1415,6 @@
   </si>
   <si>
     <t>который делал ремонт в новой квартире</t>
-  </si>
-  <si>
-    <t>который производил отделку в новой квартире</t>
   </si>
   <si>
     <t>в «курганской» группировке</t>
@@ -1977,6 +1947,33 @@
   </si>
   <si>
     <t>российского предпринимательства, которое</t>
+  </si>
+  <si>
+    <t>из палаты в проход</t>
+  </si>
+  <si>
+    <t>замыслах предприятия (возглавляемого</t>
+  </si>
+  <si>
+    <t>лелеемый еврейскими главными ростовщиками денежных хранилищ вопрос</t>
+  </si>
+  <si>
+    <t>помостом снятых гостинничных хором</t>
+  </si>
+  <si>
+    <t>было указано главное удостоверение личности гражданина страны</t>
+  </si>
+  <si>
+    <t>Уголовно-преступная особенность, имевшая место быть, прошедшая проверку и проверку королевской полицией, «пальнула»</t>
+  </si>
+  <si>
+    <t>который производил отделку в новой хате</t>
+  </si>
+  <si>
+    <t>Того же вида был случай с танзанитами, о котором я узнал после его недоумного окончания и о котором</t>
+  </si>
+  <si>
+    <t>уровни тайн, находящихся там письменных свидетельств</t>
   </si>
 </sst>
 </file>
@@ -2403,87 +2400,87 @@
         <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>627</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2504,13 +2501,16 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>59</v>
-      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B1">
+    <sortCondition ref="A1"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -2518,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="26.1015625" style="5" customWidth="1"/>
@@ -2526,134 +2526,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>61</v>
+      <c r="A1" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
-        <v>66</v>
+        <v>573</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>67</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
-        <v>70</v>
+        <v>571</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>71</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>73</v>
+      <c r="A9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
-        <v>82</v>
+        <v>623</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>83</v>
+        <v>622</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
-        <v>581</v>
+        <v>620</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>582</v>
+        <v>621</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
-        <v>583</v>
+        <v>77</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>632</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B18">
+    <sortCondition ref="A1:A18"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -2661,7 +2664,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B192"/>
+  <dimension ref="A1:B191"/>
   <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="48.7890625" style="5" customWidth="1"/>
@@ -2669,1542 +2672,1537 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>85</v>
+      <c r="A1" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>87</v>
+      <c r="A2" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
-        <v>88</v>
+        <v>273</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>89</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>93</v>
+      <c r="A5" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>101</v>
+      <c r="A9" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>105</v>
+      <c r="A10" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="26.1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>107</v>
+        <v>630</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>109</v>
+      <c r="A13" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>113</v>
+      <c r="A15" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>115</v>
+      <c r="A16" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>118</v>
+      <c r="A18" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>120</v>
+      <c r="A19" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5" t="s">
-        <v>121</v>
+        <v>247</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>122</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>126</v>
+      <c r="A21" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="5" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>132</v>
+      <c r="A24" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="5" t="s">
-        <v>133</v>
+        <v>245</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>134</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="5" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>138</v>
+      <c r="A28" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>140</v>
+      <c r="A29" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="5" t="s">
-        <v>141</v>
+        <v>251</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>142</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>144</v>
+      <c r="A31" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>146</v>
+      <c r="A32" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="5" t="s">
-        <v>147</v>
+        <v>285</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>148</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="5" t="s">
-        <v>149</v>
+      <c r="A34" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>150</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>152</v>
+      <c r="A35" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>154</v>
+      <c r="A36" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="5" t="s">
-        <v>155</v>
+        <v>98</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>158</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="5" t="s">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>160</v>
+        <v>634</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="5" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>164</v>
+      <c r="A41" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="5" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>166</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="5" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>168</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="5" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="5" t="s">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>172</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="5" t="s">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>174</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>176</v>
+      <c r="A47" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="5" t="s">
-        <v>177</v>
+        <v>277</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>178</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>180</v>
+        <v>265</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>182</v>
+      <c r="A50" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>184</v>
+      <c r="A51" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="5" t="s">
-        <v>185</v>
+        <v>113</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>186</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="5" t="s">
-        <v>187</v>
+        <v>117</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>188</v>
+        <v>626</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="5" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>192</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>194</v>
+      <c r="A56" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="5" t="s">
-        <v>195</v>
+        <v>124</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>198</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="5" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="5" t="s">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>202</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="5" t="s">
-        <v>203</v>
+        <v>130</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>204</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="5" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>208</v>
+      <c r="A63" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="5" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="5" t="s">
-        <v>211</v>
+        <v>136</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>214</v>
+      <c r="A66" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>216</v>
+      <c r="A67" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="5" t="s">
-        <v>217</v>
+      <c r="A68" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>218</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="5" t="s">
-        <v>219</v>
+        <v>138</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>220</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>222</v>
+      <c r="A70" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="5" t="s">
-        <v>223</v>
+        <v>140</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>224</v>
+        <v>628</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="5" t="s">
-        <v>225</v>
+        <v>141</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>226</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="5" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="5" t="s">
-        <v>229</v>
+        <v>143</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>230</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="5" t="s">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>232</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>234</v>
+      <c r="A76" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>236</v>
+      <c r="A77" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="5" t="s">
-        <v>237</v>
+      <c r="A78" s="7" t="s">
+        <v>307</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>238</v>
+        <v>308</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="5" t="s">
-        <v>239</v>
+        <v>145</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>240</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="5" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="5" t="s">
-        <v>243</v>
+        <v>147</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>244</v>
+        <v>148</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="5" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>248</v>
+      <c r="A83" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>250</v>
+      <c r="A84" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>252</v>
+      <c r="A85" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="5" t="s">
-        <v>253</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>256</v>
+      <c r="A87" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>258</v>
+      <c r="A88" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="5" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="5" t="s">
-        <v>261</v>
+        <v>149</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>262</v>
+        <v>150</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>264</v>
+      <c r="A91" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>268</v>
+      <c r="A92" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>270</v>
+      <c r="A94" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="5" t="s">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>272</v>
+        <v>154</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="5" t="s">
-        <v>273</v>
+        <v>155</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>274</v>
+        <v>156</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>276</v>
+      <c r="A97" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="5" t="s">
-        <v>277</v>
+        <v>157</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>278</v>
+        <v>158</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>280</v>
+      <c r="A99" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="5" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="5" t="s">
-        <v>283</v>
+        <v>159</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>284</v>
+        <v>160</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="5" t="s">
-        <v>285</v>
+        <v>161</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>286</v>
+        <v>162</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>288</v>
+      <c r="A103" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="5" t="s">
-        <v>289</v>
+        <v>239</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>290</v>
+        <v>240</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="5" t="s">
-        <v>291</v>
+        <v>163</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>292</v>
+        <v>164</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>294</v>
+      <c r="A106" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="5" t="s">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>296</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>298</v>
+      <c r="A108" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>300</v>
+      <c r="A109" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A110" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>302</v>
+      <c r="A110" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>304</v>
+      <c r="A111" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>306</v>
+      <c r="A112" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>308</v>
+      <c r="A113" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="7" t="s">
-        <v>309</v>
+        <v>358</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>310</v>
+        <v>359</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>312</v>
+      <c r="A115" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>314</v>
+      <c r="A116" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>316</v>
+      <c r="A117" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>318</v>
+      <c r="A118" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="7" t="s">
-        <v>319</v>
+        <v>575</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>320</v>
+        <v>576</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A120" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>322</v>
+      <c r="A120" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A121" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>324</v>
+      <c r="A121" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>326</v>
+      <c r="A122" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A123" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>328</v>
+      <c r="A123" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>330</v>
+      <c r="A124" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>332</v>
+      <c r="A125" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>334</v>
+      <c r="A126" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="7" t="s">
-        <v>335</v>
+        <v>384</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>336</v>
+        <v>385</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A128" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>338</v>
+      <c r="A128" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>340</v>
+      <c r="A129" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="7" t="s">
-        <v>341</v>
+        <v>547</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>342</v>
+        <v>548</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A131" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>344</v>
+      <c r="A131" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>346</v>
+        <v>396</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="7" t="s">
-        <v>347</v>
+        <v>557</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" ht="26.1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A134" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>350</v>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="7" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A136" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>354</v>
+      <c r="A136" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="7" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="7" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A139" s="7" t="s">
-        <v>359</v>
+      <c r="A139" s="9" t="s">
+        <v>406</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>360</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A140" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>362</v>
+      <c r="A140" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A141" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>364</v>
+      <c r="A141" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="7" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A143" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="B143" s="7" t="s">
-        <v>368</v>
+      <c r="A143" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A144" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>370</v>
+      <c r="A144" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>372</v>
+      <c r="A145" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="7" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A147" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>376</v>
+      <c r="A147" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="7" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="7" t="s">
-        <v>379</v>
+        <v>594</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>380</v>
+        <v>595</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="7" t="s">
-        <v>381</v>
+        <v>299</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>382</v>
+        <v>300</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="7" t="s">
-        <v>383</v>
+        <v>618</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>384</v>
+        <v>619</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="7" t="s">
-        <v>385</v>
+        <v>567</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>386</v>
+        <v>568</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A153" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>388</v>
+      <c r="A153" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="7" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="7" t="s">
-        <v>391</v>
+        <v>354</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>392</v>
+        <v>355</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A156" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>394</v>
+      <c r="A156" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="7" t="s">
-        <v>395</v>
+        <v>555</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>396</v>
+        <v>556</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A158" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>398</v>
+      <c r="A158" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="7" t="s">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>400</v>
+        <v>351</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A160" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>402</v>
+      <c r="A160" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A161" s="7" t="s">
-        <v>403</v>
+      <c r="A161" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>404</v>
+        <v>214</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A162" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>406</v>
+      <c r="A162" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="7" t="s">
-        <v>407</v>
+        <v>303</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>408</v>
+        <v>304</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="7" t="s">
-        <v>409</v>
+        <v>541</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>410</v>
+        <v>542</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="7" t="s">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A166" s="9" t="s">
-        <v>413</v>
+      <c r="A166" s="7" t="s">
+        <v>378</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>414</v>
+        <v>379</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A167" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>416</v>
+      <c r="A167" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A168" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>418</v>
+      <c r="A168" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="7" t="s">
-        <v>551</v>
+        <v>408</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>552</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A170" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>555</v>
+      <c r="A170" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A171" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="B171" s="7" t="s">
-        <v>556</v>
+      <c r="A171" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A172" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="B172" s="7" t="s">
-        <v>558</v>
+      <c r="A172" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A173" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="B173" s="7" t="s">
-        <v>560</v>
+      <c r="A173" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="7" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="7" t="s">
-        <v>565</v>
+        <v>348</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>566</v>
+        <v>349</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A177" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="B177" s="7" t="s">
-        <v>568</v>
+      <c r="A177" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="7" t="s">
-        <v>569</v>
+        <v>319</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>570</v>
+        <v>320</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A179" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="B179" s="7" t="s">
-        <v>572</v>
+      <c r="A179" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A180" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="B180" s="7" t="s">
-        <v>574</v>
+      <c r="A180" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="7" t="s">
-        <v>575</v>
+        <v>329</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>576</v>
+        <v>330</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A182" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>578</v>
+      <c r="A182" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A183" s="7" t="s">
-        <v>580</v>
-      </c>
-      <c r="B183" s="7" t="s">
-        <v>579</v>
+      <c r="A183" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A184" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>586</v>
+      <c r="A184" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A185" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="B185" s="7" t="s">
-        <v>588</v>
+      <c r="A185" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A186" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>590</v>
+      <c r="A186" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="7" t="s">
-        <v>591</v>
+        <v>323</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>592</v>
+        <v>324</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A188" s="7" t="s">
-        <v>593</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>594</v>
+      <c r="A188" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="7" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A190" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>603</v>
+      <c r="A190" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A191" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="B191" s="7" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A192" s="7" t="s">
-        <v>628</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>629</v>
+      <c r="A191" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B192">
+    <sortCondition ref="A1:A192"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -4221,90 +4219,90 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>430</v>
+        <v>633</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="38.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>434</v>
+        <v>631</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="38.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -4324,410 +4322,410 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>458</v>
+        <v>632</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="7" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="4" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="4" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="4" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="9" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="10" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>
@@ -4747,159 +4745,159 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="C1" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="C8" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="7" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="7" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="7" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="7" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CEA770-68EE-4B9B-A209-BB07D0624F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB5DAE4-7375-4890-B18C-864B58626CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" tabRatio="697" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="27493" windowHeight="13866" tabRatio="697" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="ошибки" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">неизменные_длинные!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные_важные!$A$1:$B$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -2246,12 +2247,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="2" width="48.1015625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1171875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2259,7 +2260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2267,7 +2268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2275,7 +2276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2283,7 +2284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2291,7 +2292,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2299,7 +2300,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2307,7 +2308,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2315,7 +2316,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2323,7 +2324,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2331,7 +2332,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2339,7 +2340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -2347,7 +2348,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2355,7 +2356,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2363,7 +2364,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -2371,7 +2372,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2379,7 +2380,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2387,7 +2388,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2395,7 +2396,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2403,7 +2404,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -2411,7 +2412,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
@@ -2419,7 +2420,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -2427,7 +2428,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -2435,7 +2436,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A24" s="1" t="s">
         <v>45</v>
       </c>
@@ -2443,7 +2444,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A25" s="4" t="s">
         <v>47</v>
       </c>
@@ -2451,7 +2452,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A26" s="4" t="s">
         <v>49</v>
       </c>
@@ -2459,7 +2460,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A27" s="4" t="s">
         <v>51</v>
       </c>
@@ -2467,7 +2468,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A28" s="4" t="s">
         <v>53</v>
       </c>
@@ -2475,7 +2476,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A29" s="4" t="s">
         <v>55</v>
       </c>
@@ -2493,13 +2494,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="44.7890625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.15625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.76171875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.17578125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>57</v>
       </c>
@@ -2519,13 +2520,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="26.1015625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.62890625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.1171875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.64453125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>73</v>
       </c>
@@ -2533,7 +2534,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="5" t="s">
         <v>69</v>
       </c>
@@ -2541,7 +2542,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="5" t="s">
         <v>63</v>
       </c>
@@ -2549,7 +2550,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="5" t="s">
         <v>71</v>
       </c>
@@ -2557,7 +2558,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="5" t="s">
         <v>75</v>
       </c>
@@ -2565,7 +2566,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" s="5" t="s">
         <v>573</v>
       </c>
@@ -2573,7 +2574,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="5" t="s">
         <v>67</v>
       </c>
@@ -2581,7 +2582,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" s="5" t="s">
         <v>571</v>
       </c>
@@ -2589,7 +2590,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" s="6" t="s">
         <v>59</v>
       </c>
@@ -2597,7 +2598,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" s="5" t="s">
         <v>65</v>
       </c>
@@ -2605,7 +2606,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" s="5" t="s">
         <v>61</v>
       </c>
@@ -2613,7 +2614,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" s="5" t="s">
         <v>79</v>
       </c>
@@ -2621,7 +2622,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" s="5" t="s">
         <v>81</v>
       </c>
@@ -2629,7 +2630,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" s="5" t="s">
         <v>623</v>
       </c>
@@ -2637,7 +2638,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="5" t="s">
         <v>620</v>
       </c>
@@ -2645,7 +2646,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="5" t="s">
         <v>77</v>
       </c>
@@ -2665,13 +2666,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B191"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="48.7890625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.89453125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.76171875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.87890625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="7" t="s">
         <v>543</v>
       </c>
@@ -2679,7 +2680,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="7" t="s">
         <v>553</v>
       </c>
@@ -2687,7 +2688,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="5" t="s">
         <v>273</v>
       </c>
@@ -2695,7 +2696,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="5" t="s">
         <v>83</v>
       </c>
@@ -2703,7 +2704,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="7" t="s">
         <v>388</v>
       </c>
@@ -2711,7 +2712,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" s="5" t="s">
         <v>85</v>
       </c>
@@ -2719,7 +2720,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="5" t="s">
         <v>87</v>
       </c>
@@ -2727,7 +2728,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" s="5" t="s">
         <v>89</v>
       </c>
@@ -2735,7 +2736,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" s="7" t="s">
         <v>398</v>
       </c>
@@ -2743,7 +2744,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" s="7" t="s">
         <v>335</v>
       </c>
@@ -2751,7 +2752,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" ht="26.35" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
         <v>342</v>
       </c>
@@ -2759,7 +2760,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" s="5" t="s">
         <v>91</v>
       </c>
@@ -2767,7 +2768,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
         <v>551</v>
       </c>
@@ -2775,7 +2776,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" s="5" t="s">
         <v>115</v>
       </c>
@@ -2783,7 +2784,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="7" t="s">
         <v>340</v>
       </c>
@@ -2791,7 +2792,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="7" t="s">
         <v>565</v>
       </c>
@@ -2799,7 +2800,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" s="5" t="s">
         <v>92</v>
       </c>
@@ -2807,7 +2808,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="7" t="s">
         <v>338</v>
       </c>
@@ -2815,7 +2816,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="7" t="s">
         <v>402</v>
       </c>
@@ -2823,7 +2824,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" s="5" t="s">
         <v>247</v>
       </c>
@@ -2831,7 +2832,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="7" t="s">
         <v>344</v>
       </c>
@@ -2839,7 +2840,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" s="5" t="s">
         <v>183</v>
       </c>
@@ -2847,7 +2848,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A23" s="5" t="s">
         <v>94</v>
       </c>
@@ -2855,7 +2856,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A24" s="7" t="s">
         <v>392</v>
       </c>
@@ -2863,7 +2864,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A25" s="7" t="s">
         <v>386</v>
       </c>
@@ -2871,7 +2872,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A26" s="5" t="s">
         <v>245</v>
       </c>
@@ -2879,7 +2880,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A27" s="5" t="s">
         <v>96</v>
       </c>
@@ -2887,7 +2888,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A28" s="7" t="s">
         <v>311</v>
       </c>
@@ -2895,7 +2896,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A29" s="7" t="s">
         <v>577</v>
       </c>
@@ -2903,7 +2904,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A30" s="5" t="s">
         <v>251</v>
       </c>
@@ -2911,7 +2912,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A31" s="7" t="s">
         <v>579</v>
       </c>
@@ -2919,7 +2920,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A32" s="7" t="s">
         <v>321</v>
       </c>
@@ -2927,7 +2928,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A33" s="5" t="s">
         <v>285</v>
       </c>
@@ -2935,7 +2936,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A34" s="7" t="s">
         <v>325</v>
       </c>
@@ -2943,7 +2944,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A35" s="7" t="s">
         <v>309</v>
       </c>
@@ -2951,7 +2952,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A36" s="7" t="s">
         <v>370</v>
       </c>
@@ -2959,7 +2960,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A37" s="5" t="s">
         <v>98</v>
       </c>
@@ -2967,7 +2968,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A38" s="7" t="s">
         <v>313</v>
       </c>
@@ -2975,7 +2976,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A39" s="5" t="s">
         <v>100</v>
       </c>
@@ -2983,7 +2984,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A40" s="5" t="s">
         <v>101</v>
       </c>
@@ -2991,7 +2992,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A41" s="7" t="s">
         <v>336</v>
       </c>
@@ -2999,7 +3000,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A42" s="5" t="s">
         <v>103</v>
       </c>
@@ -3007,7 +3008,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A43" s="5" t="s">
         <v>105</v>
       </c>
@@ -3015,7 +3016,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A44" s="5" t="s">
         <v>107</v>
       </c>
@@ -3023,7 +3024,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A45" s="5" t="s">
         <v>109</v>
       </c>
@@ -3031,7 +3032,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A46" s="5" t="s">
         <v>111</v>
       </c>
@@ -3039,7 +3040,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A47" s="7" t="s">
         <v>327</v>
       </c>
@@ -3047,7 +3048,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A48" s="5" t="s">
         <v>277</v>
       </c>
@@ -3055,7 +3056,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A49" s="5" t="s">
         <v>265</v>
       </c>
@@ -3063,7 +3064,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A50" s="5" t="s">
         <v>267</v>
       </c>
@@ -3071,7 +3072,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A51" s="7" t="s">
         <v>394</v>
       </c>
@@ -3079,7 +3080,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A52" s="5" t="s">
         <v>113</v>
       </c>
@@ -3087,7 +3088,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A53" s="5" t="s">
         <v>117</v>
       </c>
@@ -3095,7 +3096,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A54" s="5" t="s">
         <v>118</v>
       </c>
@@ -3103,7 +3104,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A55" s="1" t="s">
         <v>120</v>
       </c>
@@ -3111,7 +3112,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A56" s="5" t="s">
         <v>122</v>
       </c>
@@ -3119,7 +3120,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A57" s="5" t="s">
         <v>124</v>
       </c>
@@ -3127,7 +3128,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A58" s="1" t="s">
         <v>126</v>
       </c>
@@ -3135,7 +3136,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A59" s="5" t="s">
         <v>243</v>
       </c>
@@ -3143,7 +3144,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A60" s="5" t="s">
         <v>128</v>
       </c>
@@ -3151,7 +3152,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A61" s="5" t="s">
         <v>130</v>
       </c>
@@ -3159,7 +3160,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A62" s="5" t="s">
         <v>132</v>
       </c>
@@ -3167,7 +3168,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A63" s="7" t="s">
         <v>297</v>
       </c>
@@ -3175,7 +3176,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A64" s="5" t="s">
         <v>134</v>
       </c>
@@ -3183,7 +3184,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A65" s="5" t="s">
         <v>136</v>
       </c>
@@ -3191,7 +3192,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A66" s="7" t="s">
         <v>382</v>
       </c>
@@ -3199,7 +3200,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A67" s="7" t="s">
         <v>352</v>
       </c>
@@ -3207,7 +3208,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A68" s="7" t="s">
         <v>305</v>
       </c>
@@ -3215,7 +3216,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A69" s="5" t="s">
         <v>138</v>
       </c>
@@ -3223,7 +3224,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A70" s="7" t="s">
         <v>366</v>
       </c>
@@ -3231,7 +3232,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A71" s="5" t="s">
         <v>140</v>
       </c>
@@ -3239,7 +3240,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A72" s="5" t="s">
         <v>141</v>
       </c>
@@ -3247,7 +3248,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A73" s="5" t="s">
         <v>263</v>
       </c>
@@ -3255,7 +3256,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A74" s="5" t="s">
         <v>143</v>
       </c>
@@ -3263,7 +3264,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A75" s="5" t="s">
         <v>271</v>
       </c>
@@ -3271,7 +3272,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A76" s="7" t="s">
         <v>400</v>
       </c>
@@ -3279,7 +3280,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A77" s="7" t="s">
         <v>410</v>
       </c>
@@ -3287,7 +3288,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A78" s="7" t="s">
         <v>307</v>
       </c>
@@ -3295,7 +3296,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A79" s="5" t="s">
         <v>145</v>
       </c>
@@ -3303,7 +3304,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A80" s="5" t="s">
         <v>261</v>
       </c>
@@ -3311,7 +3312,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A81" s="5" t="s">
         <v>147</v>
       </c>
@@ -3319,7 +3320,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A82" s="5" t="s">
         <v>255</v>
       </c>
@@ -3327,7 +3328,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A83" s="7" t="s">
         <v>570</v>
       </c>
@@ -3335,7 +3336,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A84" s="7" t="s">
         <v>561</v>
       </c>
@@ -3343,7 +3344,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A85" s="7" t="s">
         <v>585</v>
       </c>
@@ -3351,7 +3352,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A86" s="5" t="s">
         <v>291</v>
       </c>
@@ -3359,7 +3360,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A87" s="7" t="s">
         <v>376</v>
       </c>
@@ -3367,7 +3368,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A88" s="7" t="s">
         <v>549</v>
       </c>
@@ -3375,7 +3376,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A89" s="5" t="s">
         <v>289</v>
       </c>
@@ -3383,7 +3384,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A90" s="5" t="s">
         <v>149</v>
       </c>
@@ -3391,7 +3392,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A91" s="7" t="s">
         <v>360</v>
       </c>
@@ -3399,7 +3400,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A92" s="7" t="s">
         <v>563</v>
       </c>
@@ -3407,7 +3408,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A93" s="1" t="s">
         <v>151</v>
       </c>
@@ -3415,7 +3416,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A94" s="7" t="s">
         <v>592</v>
       </c>
@@ -3423,7 +3424,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A95" s="5" t="s">
         <v>153</v>
       </c>
@@ -3431,7 +3432,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A96" s="5" t="s">
         <v>155</v>
       </c>
@@ -3439,7 +3440,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A97" s="7" t="s">
         <v>333</v>
       </c>
@@ -3447,7 +3448,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A98" s="5" t="s">
         <v>157</v>
       </c>
@@ -3455,7 +3456,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A99" s="7" t="s">
         <v>315</v>
       </c>
@@ -3463,7 +3464,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A100" s="5" t="s">
         <v>249</v>
       </c>
@@ -3471,7 +3472,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A101" s="5" t="s">
         <v>159</v>
       </c>
@@ -3479,7 +3480,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A102" s="5" t="s">
         <v>161</v>
       </c>
@@ -3487,7 +3488,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A103" s="7" t="s">
         <v>404</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A104" s="5" t="s">
         <v>239</v>
       </c>
@@ -3503,7 +3504,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A105" s="5" t="s">
         <v>163</v>
       </c>
@@ -3511,7 +3512,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A106" s="5" t="s">
         <v>165</v>
       </c>
@@ -3519,7 +3520,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A107" s="5" t="s">
         <v>167</v>
       </c>
@@ -3527,7 +3528,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A108" s="7" t="s">
         <v>544</v>
       </c>
@@ -3535,7 +3536,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A109" s="7" t="s">
         <v>346</v>
       </c>
@@ -3543,7 +3544,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A110" s="7" t="s">
         <v>372</v>
       </c>
@@ -3551,7 +3552,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A111" s="5" t="s">
         <v>253</v>
       </c>
@@ -3559,7 +3560,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A112" s="5" t="s">
         <v>169</v>
       </c>
@@ -3567,7 +3568,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A113" s="5" t="s">
         <v>171</v>
       </c>
@@ -3575,7 +3576,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A114" s="7" t="s">
         <v>358</v>
       </c>
@@ -3583,7 +3584,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A115" s="5" t="s">
         <v>173</v>
       </c>
@@ -3591,7 +3592,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A116" s="6" t="s">
         <v>175</v>
       </c>
@@ -3599,7 +3600,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A117" s="5" t="s">
         <v>177</v>
       </c>
@@ -3607,7 +3608,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A118" s="5" t="s">
         <v>179</v>
       </c>
@@ -3615,7 +3616,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A119" s="7" t="s">
         <v>575</v>
       </c>
@@ -3623,7 +3624,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A120" s="5" t="s">
         <v>181</v>
       </c>
@@ -3631,7 +3632,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A121" s="5" t="s">
         <v>185</v>
       </c>
@@ -3639,7 +3640,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A122" s="6" t="s">
         <v>187</v>
       </c>
@@ -3647,7 +3648,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A123" s="5" t="s">
         <v>189</v>
       </c>
@@ -3655,7 +3656,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A124" s="5" t="s">
         <v>191</v>
       </c>
@@ -3663,7 +3664,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A125" s="5" t="s">
         <v>257</v>
       </c>
@@ -3671,7 +3672,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A126" s="5" t="s">
         <v>269</v>
       </c>
@@ -3679,7 +3680,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A127" s="7" t="s">
         <v>384</v>
       </c>
@@ -3687,7 +3688,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A128" s="5" t="s">
         <v>279</v>
       </c>
@@ -3695,7 +3696,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A129" s="5" t="s">
         <v>295</v>
       </c>
@@ -3703,7 +3704,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A130" s="7" t="s">
         <v>547</v>
       </c>
@@ -3711,7 +3712,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A131" s="5" t="s">
         <v>193</v>
       </c>
@@ -3719,7 +3720,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A132" s="7" t="s">
         <v>396</v>
       </c>
@@ -3727,7 +3728,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A133" s="7" t="s">
         <v>557</v>
       </c>
@@ -3735,7 +3736,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A134" s="5" t="s">
         <v>195</v>
       </c>
@@ -3743,7 +3744,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A135" s="7" t="s">
         <v>317</v>
       </c>
@@ -3751,7 +3752,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A136" s="5" t="s">
         <v>197</v>
       </c>
@@ -3759,7 +3760,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A137" s="7" t="s">
         <v>368</v>
       </c>
@@ -3767,7 +3768,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A138" s="7" t="s">
         <v>331</v>
       </c>
@@ -3775,7 +3776,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A139" s="9" t="s">
         <v>406</v>
       </c>
@@ -3783,7 +3784,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A140" s="5" t="s">
         <v>199</v>
       </c>
@@ -3791,7 +3792,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A141" s="6" t="s">
         <v>287</v>
       </c>
@@ -3799,7 +3800,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A142" s="7" t="s">
         <v>374</v>
       </c>
@@ -3807,7 +3808,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A143" s="5" t="s">
         <v>201</v>
       </c>
@@ -3815,7 +3816,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A144" s="5" t="s">
         <v>203</v>
       </c>
@@ -3823,7 +3824,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A145" s="5" t="s">
         <v>205</v>
       </c>
@@ -3831,7 +3832,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A146" s="7" t="s">
         <v>364</v>
       </c>
@@ -3839,7 +3840,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A147" s="5" t="s">
         <v>207</v>
       </c>
@@ -3847,7 +3848,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A148" s="7" t="s">
         <v>356</v>
       </c>
@@ -3855,7 +3856,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A149" s="7" t="s">
         <v>594</v>
       </c>
@@ -3863,7 +3864,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A150" s="7" t="s">
         <v>299</v>
       </c>
@@ -3871,7 +3872,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A151" s="7" t="s">
         <v>618</v>
       </c>
@@ -3879,7 +3880,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A152" s="7" t="s">
         <v>567</v>
       </c>
@@ -3887,7 +3888,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A153" s="5" t="s">
         <v>209</v>
       </c>
@@ -3895,7 +3896,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A154" s="7" t="s">
         <v>362</v>
       </c>
@@ -3903,7 +3904,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A155" s="7" t="s">
         <v>354</v>
       </c>
@@ -3911,7 +3912,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A156" s="5" t="s">
         <v>211</v>
       </c>
@@ -3919,7 +3920,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A157" s="7" t="s">
         <v>555</v>
       </c>
@@ -3927,7 +3928,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A158" s="7" t="s">
         <v>301</v>
       </c>
@@ -3935,7 +3936,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A159" s="7" t="s">
         <v>350</v>
       </c>
@@ -3943,7 +3944,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A160" s="5" t="s">
         <v>283</v>
       </c>
@@ -3951,7 +3952,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A161" s="5" t="s">
         <v>213</v>
       </c>
@@ -3959,7 +3960,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A162" s="5" t="s">
         <v>215</v>
       </c>
@@ -3967,7 +3968,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A163" s="7" t="s">
         <v>303</v>
       </c>
@@ -3975,7 +3976,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A164" s="7" t="s">
         <v>541</v>
       </c>
@@ -3983,7 +3984,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A165" s="7" t="s">
         <v>380</v>
       </c>
@@ -3991,7 +3992,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A166" s="7" t="s">
         <v>378</v>
       </c>
@@ -3999,7 +4000,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A167" s="5" t="s">
         <v>217</v>
       </c>
@@ -4007,7 +4008,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A168" s="5" t="s">
         <v>275</v>
       </c>
@@ -4015,7 +4016,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A169" s="7" t="s">
         <v>408</v>
       </c>
@@ -4023,7 +4024,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A170" s="5" t="s">
         <v>219</v>
       </c>
@@ -4031,7 +4032,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A171" s="5" t="s">
         <v>221</v>
       </c>
@@ -4039,7 +4040,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A172" s="5" t="s">
         <v>223</v>
       </c>
@@ -4047,7 +4048,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A173" s="5" t="s">
         <v>225</v>
       </c>
@@ -4055,7 +4056,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A174" s="7" t="s">
         <v>559</v>
       </c>
@@ -4063,7 +4064,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A175" s="7" t="s">
         <v>583</v>
       </c>
@@ -4071,7 +4072,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A176" s="7" t="s">
         <v>348</v>
       </c>
@@ -4079,7 +4080,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A177" s="5" t="s">
         <v>227</v>
       </c>
@@ -4087,7 +4088,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A178" s="7" t="s">
         <v>319</v>
       </c>
@@ -4095,7 +4096,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A179" s="1" t="s">
         <v>293</v>
       </c>
@@ -4103,7 +4104,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A180" s="5" t="s">
         <v>229</v>
       </c>
@@ -4111,7 +4112,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A181" s="7" t="s">
         <v>329</v>
       </c>
@@ -4119,7 +4120,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A182" s="5" t="s">
         <v>241</v>
       </c>
@@ -4127,7 +4128,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A183" s="5" t="s">
         <v>231</v>
       </c>
@@ -4135,7 +4136,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A184" s="5" t="s">
         <v>233</v>
       </c>
@@ -4143,7 +4144,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A185" s="5" t="s">
         <v>235</v>
       </c>
@@ -4151,7 +4152,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A186" s="5" t="s">
         <v>237</v>
       </c>
@@ -4159,7 +4160,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A187" s="7" t="s">
         <v>323</v>
       </c>
@@ -4167,7 +4168,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A188" s="5" t="s">
         <v>259</v>
       </c>
@@ -4175,7 +4176,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A189" s="7" t="s">
         <v>581</v>
       </c>
@@ -4183,7 +4184,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A190" s="1" t="s">
         <v>390</v>
       </c>
@@ -4191,7 +4192,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A191" s="5" t="s">
         <v>281</v>
       </c>
@@ -4211,13 +4212,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="52.3671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.7890625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="52.3515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.76171875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>412</v>
       </c>
@@ -4225,7 +4226,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>414</v>
       </c>
@@ -4233,7 +4234,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>416</v>
       </c>
@@ -4241,7 +4242,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>418</v>
       </c>
@@ -4249,7 +4250,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>420</v>
       </c>
@@ -4257,7 +4258,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
         <v>422</v>
       </c>
@@ -4265,7 +4266,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
         <v>423</v>
       </c>
@@ -4273,7 +4274,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="38.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" ht="38.700000000000003" x14ac:dyDescent="0.5">
       <c r="A8" s="4" t="s">
         <v>425</v>
       </c>
@@ -4281,7 +4282,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="38.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" ht="38.700000000000003" x14ac:dyDescent="0.5">
       <c r="A9" s="4" t="s">
         <v>426</v>
       </c>
@@ -4289,7 +4290,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" s="4" t="s">
         <v>428</v>
       </c>
@@ -4297,7 +4298,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A11" s="1" t="s">
         <v>598</v>
       </c>
@@ -4306,6 +4307,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B11" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -4314,13 +4316,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B51"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="51.62890625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.89453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.64453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.87890625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>430</v>
       </c>
@@ -4328,7 +4330,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>432</v>
       </c>
@@ -4336,7 +4338,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>434</v>
       </c>
@@ -4344,7 +4346,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>436</v>
       </c>
@@ -4352,7 +4354,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>438</v>
       </c>
@@ -4360,7 +4362,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
         <v>440</v>
       </c>
@@ -4368,7 +4370,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
         <v>442</v>
       </c>
@@ -4376,7 +4378,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" s="1" t="s">
         <v>444</v>
       </c>
@@ -4384,7 +4386,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" s="1" t="s">
         <v>446</v>
       </c>
@@ -4392,7 +4394,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" s="1" t="s">
         <v>448</v>
       </c>
@@ -4400,7 +4402,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" s="1" t="s">
         <v>449</v>
       </c>
@@ -4408,7 +4410,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" s="1" t="s">
         <v>451</v>
       </c>
@@ -4416,7 +4418,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" s="1" t="s">
         <v>453</v>
       </c>
@@ -4424,7 +4426,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>455</v>
       </c>
@@ -4432,7 +4434,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A15" s="1" t="s">
         <v>457</v>
       </c>
@@ -4440,7 +4442,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A16" s="1" t="s">
         <v>459</v>
       </c>
@@ -4448,7 +4450,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" s="1" t="s">
         <v>461</v>
       </c>
@@ -4456,7 +4458,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="1" t="s">
         <v>463</v>
       </c>
@@ -4464,7 +4466,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="1" t="s">
         <v>465</v>
       </c>
@@ -4472,7 +4474,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" s="1" t="s">
         <v>467</v>
       </c>
@@ -4480,7 +4482,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="1" t="s">
         <v>469</v>
       </c>
@@ -4488,7 +4490,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" s="1" t="s">
         <v>471</v>
       </c>
@@ -4496,7 +4498,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A23" s="1" t="s">
         <v>473</v>
       </c>
@@ -4504,7 +4506,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A24" s="1" t="s">
         <v>475</v>
       </c>
@@ -4512,7 +4514,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A25" s="1" t="s">
         <v>477</v>
       </c>
@@ -4520,7 +4522,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A26" s="1" t="s">
         <v>479</v>
       </c>
@@ -4528,7 +4530,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A27" s="1" t="s">
         <v>481</v>
       </c>
@@ -4536,7 +4538,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A28" s="1" t="s">
         <v>483</v>
       </c>
@@ -4544,7 +4546,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A29" s="1" t="s">
         <v>485</v>
       </c>
@@ -4552,7 +4554,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A30" s="1" t="s">
         <v>487</v>
       </c>
@@ -4560,7 +4562,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A31" s="4" t="s">
         <v>489</v>
       </c>
@@ -4568,7 +4570,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A32" s="4" t="s">
         <v>491</v>
       </c>
@@ -4576,7 +4578,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A33" s="7" t="s">
         <v>493</v>
       </c>
@@ -4584,7 +4586,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A34" s="1" t="s">
         <v>495</v>
       </c>
@@ -4592,7 +4594,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A35" s="1" t="s">
         <v>390</v>
       </c>
@@ -4600,7 +4602,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A36" s="1" t="s">
         <v>498</v>
       </c>
@@ -4608,7 +4610,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A37" s="1" t="s">
         <v>500</v>
       </c>
@@ -4616,7 +4618,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A38" s="1" t="s">
         <v>502</v>
       </c>
@@ -4624,7 +4626,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A39" s="4" t="s">
         <v>504</v>
       </c>
@@ -4632,7 +4634,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A40" s="4" t="s">
         <v>506</v>
       </c>
@@ -4640,7 +4642,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A41" s="4" t="s">
         <v>508</v>
       </c>
@@ -4648,7 +4650,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A42" s="4" t="s">
         <v>510</v>
       </c>
@@ -4656,7 +4658,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A43" s="9" t="s">
         <v>512</v>
       </c>
@@ -4664,7 +4666,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A44" s="1" t="s">
         <v>539</v>
       </c>
@@ -4672,7 +4674,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A45" s="1" t="s">
         <v>600</v>
       </c>
@@ -4680,7 +4682,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A46" s="1" t="s">
         <v>602</v>
       </c>
@@ -4688,7 +4690,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A47" s="1" t="s">
         <v>604</v>
       </c>
@@ -4696,7 +4698,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A48" s="10" t="s">
         <v>606</v>
       </c>
@@ -4704,7 +4706,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A49" s="1" t="s">
         <v>608</v>
       </c>
@@ -4712,7 +4714,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A50" s="1" t="s">
         <v>610</v>
       </c>
@@ -4720,7 +4722,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A51" s="1" t="s">
         <v>624</v>
       </c>
@@ -4737,13 +4739,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="32.47265625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.62890625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32.46875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.64453125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>514</v>
       </c>
@@ -4751,7 +4753,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" s="5" t="s">
         <v>515</v>
       </c>
@@ -4759,7 +4761,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" s="5" t="s">
         <v>517</v>
       </c>
@@ -4767,7 +4769,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" s="5" t="s">
         <v>518</v>
       </c>
@@ -4775,7 +4777,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A5" s="5" t="s">
         <v>519</v>
       </c>
@@ -4783,7 +4785,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" s="5" t="s">
         <v>520</v>
       </c>
@@ -4791,7 +4793,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" s="5" t="s">
         <v>522</v>
       </c>
@@ -4799,7 +4801,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" s="5" t="s">
         <v>524</v>
       </c>
@@ -4810,7 +4812,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A9" s="5" t="s">
         <v>526</v>
       </c>
@@ -4818,12 +4820,12 @@
         <v>527</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" s="5" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A11" s="7" t="s">
         <v>529</v>
       </c>
@@ -4831,7 +4833,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A12" s="7" t="s">
         <v>531</v>
       </c>
@@ -4839,7 +4841,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A13" s="7" t="s">
         <v>533</v>
       </c>
@@ -4847,7 +4849,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>535</v>
       </c>
@@ -4855,7 +4857,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A15" s="7" t="s">
         <v>537</v>
       </c>
@@ -4863,12 +4865,12 @@
         <v>538</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" s="7" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" s="7" t="s">
         <v>588</v>
       </c>
@@ -4876,7 +4878,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" s="7" t="s">
         <v>590</v>
       </c>
@@ -4884,7 +4886,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A20" s="7" t="s">
         <v>596</v>
       </c>
@@ -4892,7 +4894,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A21" s="7" t="s">
         <v>612</v>
       </c>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB5DAE4-7375-4890-B18C-864B58626CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D164F3-F0F1-4F67-80D4-CBBCFBB2CD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="27493" windowHeight="13866" tabRatio="697" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="697" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="641">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1975,6 +1975,24 @@
   </si>
   <si>
     <t>уровни тайн, находящихся там письменных свидетельств</t>
+  </si>
+  <si>
+    <t>некая база, основание которой</t>
+  </si>
+  <si>
+    <t>некое хранилище, основание которого</t>
+  </si>
+  <si>
+    <t>Алтуфьевском дорога</t>
+  </si>
+  <si>
+    <t>Алтуфьевской дороге</t>
+  </si>
+  <si>
+    <t>полозы</t>
+  </si>
+  <si>
+    <t>пользы</t>
   </si>
 </sst>
 </file>
@@ -2247,12 +2265,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="48.1171875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2260,7 +2278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2268,7 +2286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2276,7 +2294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2284,7 +2302,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2292,7 +2310,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2300,7 +2318,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2308,7 +2326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2316,7 +2334,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2324,7 +2342,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2332,7 +2350,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2340,7 +2358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -2348,7 +2366,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2356,7 +2374,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2364,7 +2382,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -2372,7 +2390,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2380,7 +2398,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2388,7 +2406,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2396,7 +2414,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2404,7 +2422,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -2412,7 +2430,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
@@ -2420,7 +2438,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -2428,7 +2446,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,7 +2454,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>45</v>
       </c>
@@ -2444,7 +2462,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>47</v>
       </c>
@@ -2452,7 +2470,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>49</v>
       </c>
@@ -2460,7 +2478,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>51</v>
       </c>
@@ -2468,7 +2486,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>53</v>
       </c>
@@ -2476,7 +2494,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>55</v>
       </c>
@@ -2494,13 +2512,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.76171875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.17578125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>57</v>
       </c>
@@ -2519,14 +2537,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.1171875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.64453125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>73</v>
       </c>
@@ -2534,7 +2552,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>69</v>
       </c>
@@ -2542,7 +2560,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>63</v>
       </c>
@@ -2550,7 +2568,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>71</v>
       </c>
@@ -2558,7 +2576,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>75</v>
       </c>
@@ -2566,7 +2584,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>573</v>
       </c>
@@ -2574,7 +2592,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>67</v>
       </c>
@@ -2582,7 +2600,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>571</v>
       </c>
@@ -2590,7 +2608,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>59</v>
       </c>
@@ -2598,7 +2616,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>65</v>
       </c>
@@ -2606,7 +2624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>61</v>
       </c>
@@ -2614,7 +2632,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>79</v>
       </c>
@@ -2622,7 +2640,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>81</v>
       </c>
@@ -2630,7 +2648,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>623</v>
       </c>
@@ -2638,7 +2656,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>620</v>
       </c>
@@ -2646,12 +2664,20 @@
         <v>621</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -2666,13 +2692,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B191"/>
-  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.76171875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.87890625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>543</v>
       </c>
@@ -2680,7 +2706,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>553</v>
       </c>
@@ -2688,7 +2714,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>273</v>
       </c>
@@ -2696,7 +2722,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>83</v>
       </c>
@@ -2704,7 +2730,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>388</v>
       </c>
@@ -2712,7 +2738,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>85</v>
       </c>
@@ -2720,7 +2746,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>87</v>
       </c>
@@ -2728,7 +2754,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>89</v>
       </c>
@@ -2736,7 +2762,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>398</v>
       </c>
@@ -2744,7 +2770,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>335</v>
       </c>
@@ -2752,7 +2778,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.35" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>342</v>
       </c>
@@ -2760,7 +2786,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>91</v>
       </c>
@@ -2768,7 +2794,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>551</v>
       </c>
@@ -2776,7 +2802,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>115</v>
       </c>
@@ -2784,7 +2810,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>340</v>
       </c>
@@ -2792,7 +2818,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>565</v>
       </c>
@@ -2800,7 +2826,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>92</v>
       </c>
@@ -2808,7 +2834,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>338</v>
       </c>
@@ -2816,7 +2842,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>402</v>
       </c>
@@ -2824,7 +2850,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>247</v>
       </c>
@@ -2832,7 +2858,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>344</v>
       </c>
@@ -2840,7 +2866,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>183</v>
       </c>
@@ -2848,7 +2874,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>94</v>
       </c>
@@ -2856,7 +2882,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>392</v>
       </c>
@@ -2864,7 +2890,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>386</v>
       </c>
@@ -2872,7 +2898,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>245</v>
       </c>
@@ -2880,7 +2906,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>96</v>
       </c>
@@ -2888,7 +2914,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>311</v>
       </c>
@@ -2896,7 +2922,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>577</v>
       </c>
@@ -2904,7 +2930,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>251</v>
       </c>
@@ -2912,7 +2938,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>579</v>
       </c>
@@ -2920,7 +2946,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>321</v>
       </c>
@@ -2928,7 +2954,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>285</v>
       </c>
@@ -2936,7 +2962,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>325</v>
       </c>
@@ -2944,7 +2970,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>309</v>
       </c>
@@ -2952,7 +2978,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>370</v>
       </c>
@@ -2960,7 +2986,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>98</v>
       </c>
@@ -2968,7 +2994,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>313</v>
       </c>
@@ -2976,7 +3002,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>100</v>
       </c>
@@ -2984,7 +3010,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>101</v>
       </c>
@@ -2992,7 +3018,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>336</v>
       </c>
@@ -3000,7 +3026,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>103</v>
       </c>
@@ -3008,7 +3034,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>105</v>
       </c>
@@ -3016,7 +3042,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>107</v>
       </c>
@@ -3024,7 +3050,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>109</v>
       </c>
@@ -3032,7 +3058,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>111</v>
       </c>
@@ -3040,7 +3066,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>327</v>
       </c>
@@ -3048,7 +3074,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>277</v>
       </c>
@@ -3056,7 +3082,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>265</v>
       </c>
@@ -3064,7 +3090,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>267</v>
       </c>
@@ -3072,7 +3098,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>394</v>
       </c>
@@ -3080,7 +3106,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>113</v>
       </c>
@@ -3088,7 +3114,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>117</v>
       </c>
@@ -3096,7 +3122,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>118</v>
       </c>
@@ -3104,7 +3130,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>120</v>
       </c>
@@ -3112,7 +3138,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>122</v>
       </c>
@@ -3120,7 +3146,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>124</v>
       </c>
@@ -3128,7 +3154,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>126</v>
       </c>
@@ -3136,7 +3162,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>243</v>
       </c>
@@ -3144,7 +3170,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>128</v>
       </c>
@@ -3152,7 +3178,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>130</v>
       </c>
@@ -3160,7 +3186,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>132</v>
       </c>
@@ -3168,7 +3194,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>297</v>
       </c>
@@ -3176,7 +3202,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>134</v>
       </c>
@@ -3184,7 +3210,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>136</v>
       </c>
@@ -3192,7 +3218,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>382</v>
       </c>
@@ -3200,7 +3226,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>352</v>
       </c>
@@ -3208,7 +3234,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>305</v>
       </c>
@@ -3216,7 +3242,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>138</v>
       </c>
@@ -3224,7 +3250,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>366</v>
       </c>
@@ -3232,7 +3258,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>140</v>
       </c>
@@ -3240,7 +3266,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>141</v>
       </c>
@@ -3248,7 +3274,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>263</v>
       </c>
@@ -3256,7 +3282,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>143</v>
       </c>
@@ -3264,7 +3290,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>271</v>
       </c>
@@ -3272,7 +3298,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>400</v>
       </c>
@@ -3280,7 +3306,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>410</v>
       </c>
@@ -3288,7 +3314,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>307</v>
       </c>
@@ -3296,7 +3322,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>145</v>
       </c>
@@ -3304,7 +3330,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>261</v>
       </c>
@@ -3312,7 +3338,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>147</v>
       </c>
@@ -3320,7 +3346,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>255</v>
       </c>
@@ -3328,7 +3354,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>570</v>
       </c>
@@ -3336,7 +3362,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>561</v>
       </c>
@@ -3344,7 +3370,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>585</v>
       </c>
@@ -3352,7 +3378,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>291</v>
       </c>
@@ -3360,7 +3386,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>376</v>
       </c>
@@ -3368,7 +3394,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>549</v>
       </c>
@@ -3376,7 +3402,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>289</v>
       </c>
@@ -3384,7 +3410,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>149</v>
       </c>
@@ -3392,7 +3418,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>360</v>
       </c>
@@ -3400,7 +3426,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>563</v>
       </c>
@@ -3408,7 +3434,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>151</v>
       </c>
@@ -3416,7 +3442,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>592</v>
       </c>
@@ -3424,7 +3450,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>153</v>
       </c>
@@ -3432,7 +3458,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>155</v>
       </c>
@@ -3440,7 +3466,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>333</v>
       </c>
@@ -3448,7 +3474,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>157</v>
       </c>
@@ -3456,7 +3482,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>315</v>
       </c>
@@ -3464,7 +3490,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>249</v>
       </c>
@@ -3472,7 +3498,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>159</v>
       </c>
@@ -3480,7 +3506,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>161</v>
       </c>
@@ -3488,7 +3514,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>404</v>
       </c>
@@ -3496,7 +3522,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>239</v>
       </c>
@@ -3504,7 +3530,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>163</v>
       </c>
@@ -3512,7 +3538,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>165</v>
       </c>
@@ -3520,7 +3546,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
         <v>167</v>
       </c>
@@ -3528,7 +3554,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>544</v>
       </c>
@@ -3536,7 +3562,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>346</v>
       </c>
@@ -3544,7 +3570,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>372</v>
       </c>
@@ -3552,7 +3578,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
         <v>253</v>
       </c>
@@ -3560,7 +3586,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>169</v>
       </c>
@@ -3568,7 +3594,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>171</v>
       </c>
@@ -3576,7 +3602,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>358</v>
       </c>
@@ -3584,7 +3610,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>173</v>
       </c>
@@ -3592,7 +3618,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
         <v>175</v>
       </c>
@@ -3600,7 +3626,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>177</v>
       </c>
@@ -3608,7 +3634,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>179</v>
       </c>
@@ -3616,7 +3642,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>575</v>
       </c>
@@ -3624,7 +3650,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
         <v>181</v>
       </c>
@@ -3632,7 +3658,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>185</v>
       </c>
@@ -3640,7 +3666,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
         <v>187</v>
       </c>
@@ -3648,7 +3674,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>189</v>
       </c>
@@ -3656,7 +3682,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>191</v>
       </c>
@@ -3664,7 +3690,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>257</v>
       </c>
@@ -3672,7 +3698,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>269</v>
       </c>
@@ -3680,7 +3706,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>384</v>
       </c>
@@ -3688,7 +3714,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>279</v>
       </c>
@@ -3696,7 +3722,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>295</v>
       </c>
@@ -3704,7 +3730,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>547</v>
       </c>
@@ -3712,7 +3738,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>193</v>
       </c>
@@ -3720,7 +3746,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
         <v>396</v>
       </c>
@@ -3728,7 +3754,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
         <v>557</v>
       </c>
@@ -3736,7 +3762,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
         <v>195</v>
       </c>
@@ -3744,7 +3770,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
         <v>317</v>
       </c>
@@ -3752,7 +3778,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
         <v>197</v>
       </c>
@@ -3760,7 +3786,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>368</v>
       </c>
@@ -3768,7 +3794,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
         <v>331</v>
       </c>
@@ -3776,7 +3802,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="9" t="s">
         <v>406</v>
       </c>
@@ -3784,7 +3810,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
         <v>199</v>
       </c>
@@ -3792,7 +3818,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>287</v>
       </c>
@@ -3800,7 +3826,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
         <v>374</v>
       </c>
@@ -3808,7 +3834,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
         <v>201</v>
       </c>
@@ -3816,7 +3842,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>203</v>
       </c>
@@ -3824,7 +3850,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
         <v>205</v>
       </c>
@@ -3832,7 +3858,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
         <v>364</v>
       </c>
@@ -3840,7 +3866,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>207</v>
       </c>
@@ -3848,7 +3874,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>356</v>
       </c>
@@ -3856,7 +3882,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
         <v>594</v>
       </c>
@@ -3864,7 +3890,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
         <v>299</v>
       </c>
@@ -3872,7 +3898,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>618</v>
       </c>
@@ -3880,7 +3906,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>567</v>
       </c>
@@ -3888,7 +3914,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
         <v>209</v>
       </c>
@@ -3896,7 +3922,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>362</v>
       </c>
@@ -3904,7 +3930,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>354</v>
       </c>
@@ -3912,7 +3938,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
         <v>211</v>
       </c>
@@ -3920,7 +3946,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>555</v>
       </c>
@@ -3928,7 +3954,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>301</v>
       </c>
@@ -3936,7 +3962,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>350</v>
       </c>
@@ -3944,7 +3970,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
         <v>283</v>
       </c>
@@ -3952,7 +3978,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
         <v>213</v>
       </c>
@@ -3960,7 +3986,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
         <v>215</v>
       </c>
@@ -3968,7 +3994,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>303</v>
       </c>
@@ -3976,7 +4002,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>541</v>
       </c>
@@ -3984,7 +4010,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
         <v>380</v>
       </c>
@@ -3992,7 +4018,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>378</v>
       </c>
@@ -4000,7 +4026,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
         <v>217</v>
       </c>
@@ -4008,7 +4034,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
         <v>275</v>
       </c>
@@ -4016,7 +4042,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
         <v>408</v>
       </c>
@@ -4024,7 +4050,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
         <v>219</v>
       </c>
@@ -4032,7 +4058,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
         <v>221</v>
       </c>
@@ -4040,7 +4066,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
         <v>223</v>
       </c>
@@ -4048,7 +4074,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
         <v>225</v>
       </c>
@@ -4056,7 +4082,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>559</v>
       </c>
@@ -4064,7 +4090,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>583</v>
       </c>
@@ -4072,7 +4098,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>348</v>
       </c>
@@ -4080,7 +4106,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
         <v>227</v>
       </c>
@@ -4088,7 +4114,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>319</v>
       </c>
@@ -4096,7 +4122,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>293</v>
       </c>
@@ -4104,7 +4130,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
         <v>229</v>
       </c>
@@ -4112,7 +4138,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>329</v>
       </c>
@@ -4120,7 +4146,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
         <v>241</v>
       </c>
@@ -4128,7 +4154,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
         <v>231</v>
       </c>
@@ -4136,7 +4162,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
         <v>233</v>
       </c>
@@ -4144,7 +4170,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
         <v>235</v>
       </c>
@@ -4152,7 +4178,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
         <v>237</v>
       </c>
@@ -4160,7 +4186,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
         <v>323</v>
       </c>
@@ -4168,7 +4194,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
         <v>259</v>
       </c>
@@ -4176,7 +4202,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>581</v>
       </c>
@@ -4184,7 +4210,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>390</v>
       </c>
@@ -4192,7 +4218,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="s">
         <v>281</v>
       </c>
@@ -4212,13 +4238,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.3515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.76171875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="52.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>412</v>
       </c>
@@ -4226,7 +4252,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>414</v>
       </c>
@@ -4234,7 +4260,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>416</v>
       </c>
@@ -4242,7 +4268,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>418</v>
       </c>
@@ -4250,7 +4276,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>420</v>
       </c>
@@ -4258,7 +4284,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>422</v>
       </c>
@@ -4266,7 +4292,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>423</v>
       </c>
@@ -4274,7 +4300,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="38.700000000000003" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" ht="39" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>425</v>
       </c>
@@ -4282,7 +4308,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="38.700000000000003" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" ht="39" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>426</v>
       </c>
@@ -4290,7 +4316,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>428</v>
       </c>
@@ -4298,7 +4324,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>598</v>
       </c>
@@ -4315,14 +4341,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B51"/>
-  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:B52"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.64453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.87890625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>430</v>
       </c>
@@ -4330,7 +4356,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>432</v>
       </c>
@@ -4338,7 +4364,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>434</v>
       </c>
@@ -4346,7 +4372,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>436</v>
       </c>
@@ -4354,7 +4380,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>438</v>
       </c>
@@ -4362,7 +4388,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>440</v>
       </c>
@@ -4370,7 +4396,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>442</v>
       </c>
@@ -4378,7 +4404,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>444</v>
       </c>
@@ -4386,7 +4412,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>446</v>
       </c>
@@ -4394,7 +4420,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>448</v>
       </c>
@@ -4402,7 +4428,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>449</v>
       </c>
@@ -4410,7 +4436,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>451</v>
       </c>
@@ -4418,7 +4444,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>453</v>
       </c>
@@ -4426,7 +4452,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>455</v>
       </c>
@@ -4434,7 +4460,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>457</v>
       </c>
@@ -4442,7 +4468,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>459</v>
       </c>
@@ -4450,7 +4476,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>461</v>
       </c>
@@ -4458,7 +4484,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>463</v>
       </c>
@@ -4466,7 +4492,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>465</v>
       </c>
@@ -4474,7 +4500,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>467</v>
       </c>
@@ -4482,7 +4508,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>469</v>
       </c>
@@ -4490,7 +4516,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>471</v>
       </c>
@@ -4498,7 +4524,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>473</v>
       </c>
@@ -4506,7 +4532,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>475</v>
       </c>
@@ -4514,7 +4540,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>477</v>
       </c>
@@ -4522,7 +4548,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>479</v>
       </c>
@@ -4530,7 +4556,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>481</v>
       </c>
@@ -4538,7 +4564,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>483</v>
       </c>
@@ -4546,7 +4572,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>485</v>
       </c>
@@ -4554,7 +4580,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>487</v>
       </c>
@@ -4562,7 +4588,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>489</v>
       </c>
@@ -4570,7 +4596,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>491</v>
       </c>
@@ -4578,7 +4604,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>493</v>
       </c>
@@ -4586,7 +4612,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>495</v>
       </c>
@@ -4594,7 +4620,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>390</v>
       </c>
@@ -4602,7 +4628,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>498</v>
       </c>
@@ -4610,7 +4636,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>500</v>
       </c>
@@ -4618,7 +4644,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>502</v>
       </c>
@@ -4626,7 +4652,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>504</v>
       </c>
@@ -4634,7 +4660,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>506</v>
       </c>
@@ -4642,7 +4668,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>508</v>
       </c>
@@ -4650,7 +4676,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>510</v>
       </c>
@@ -4658,7 +4684,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>512</v>
       </c>
@@ -4666,7 +4692,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>539</v>
       </c>
@@ -4674,7 +4700,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>600</v>
       </c>
@@ -4682,7 +4708,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>602</v>
       </c>
@@ -4690,7 +4716,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>604</v>
       </c>
@@ -4698,7 +4724,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>606</v>
       </c>
@@ -4706,7 +4732,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>608</v>
       </c>
@@ -4714,7 +4740,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>610</v>
       </c>
@@ -4722,12 +4748,20 @@
         <v>611</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>624</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>625</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -4738,14 +4772,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.234375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.46875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.64453125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>514</v>
       </c>
@@ -4753,7 +4787,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>515</v>
       </c>
@@ -4761,7 +4795,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>517</v>
       </c>
@@ -4769,7 +4803,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>518</v>
       </c>
@@ -4777,7 +4811,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>519</v>
       </c>
@@ -4785,7 +4819,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>520</v>
       </c>
@@ -4793,7 +4827,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>522</v>
       </c>
@@ -4801,7 +4835,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>524</v>
       </c>
@@ -4812,7 +4846,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>526</v>
       </c>
@@ -4820,12 +4854,12 @@
         <v>527</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>529</v>
       </c>
@@ -4833,7 +4867,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>531</v>
       </c>
@@ -4841,7 +4875,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>533</v>
       </c>
@@ -4849,7 +4883,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>535</v>
       </c>
@@ -4857,7 +4891,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>537</v>
       </c>
@@ -4865,12 +4899,12 @@
         <v>538</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>588</v>
       </c>
@@ -4878,7 +4912,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>590</v>
       </c>
@@ -4886,7 +4920,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>596</v>
       </c>
@@ -4894,12 +4928,20 @@
         <v>597</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>612</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>613</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>640</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D164F3-F0F1-4F67-80D4-CBBCFBB2CD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9895FE27-BFBF-4146-887C-5CB060D3655A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="697" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="646">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -1993,6 +1993,21 @@
   </si>
   <si>
     <t>пользы</t>
+  </si>
+  <si>
+    <t>общий</t>
+  </si>
+  <si>
+    <t>Моей опекой мадам</t>
+  </si>
+  <si>
+    <t>Моей опекой были мадам</t>
+  </si>
+  <si>
+    <t>совершенно другой атаки</t>
+  </si>
+  <si>
+    <t>совершенно другое развитие</t>
   </si>
 </sst>
 </file>
@@ -2049,7 +2064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -2071,6 +2086,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2265,12 +2284,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="48.140625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2278,7 +2297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2286,7 +2305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2294,7 +2313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2302,7 +2321,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2310,7 +2329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2318,7 +2337,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2326,7 +2345,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2334,7 +2353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2342,7 +2361,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2350,7 +2369,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2358,7 +2377,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -2366,7 +2385,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2374,7 +2393,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2382,7 +2401,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -2390,7 +2409,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2398,7 +2417,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2406,7 +2425,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2414,7 +2433,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2422,7 +2441,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -2430,7 +2449,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
@@ -2438,7 +2457,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -2446,7 +2465,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -2454,7 +2473,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>45</v>
       </c>
@@ -2462,7 +2481,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>47</v>
       </c>
@@ -2470,7 +2489,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>49</v>
       </c>
@@ -2478,7 +2497,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>51</v>
       </c>
@@ -2486,7 +2505,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>53</v>
       </c>
@@ -2494,7 +2513,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>55</v>
       </c>
@@ -2512,13 +2531,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="44.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.7265625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>57</v>
       </c>
@@ -2538,13 +2557,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>73</v>
       </c>
@@ -2552,7 +2571,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>69</v>
       </c>
@@ -2560,7 +2579,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>63</v>
       </c>
@@ -2568,7 +2587,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>71</v>
       </c>
@@ -2576,7 +2595,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>75</v>
       </c>
@@ -2584,7 +2603,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>573</v>
       </c>
@@ -2592,7 +2611,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>67</v>
       </c>
@@ -2600,7 +2619,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>571</v>
       </c>
@@ -2608,7 +2627,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>59</v>
       </c>
@@ -2616,7 +2635,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>65</v>
       </c>
@@ -2624,7 +2643,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>61</v>
       </c>
@@ -2632,7 +2651,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>79</v>
       </c>
@@ -2640,7 +2659,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>81</v>
       </c>
@@ -2648,7 +2667,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>623</v>
       </c>
@@ -2656,7 +2675,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>620</v>
       </c>
@@ -2664,7 +2683,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>77</v>
       </c>
@@ -2672,7 +2691,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>637</v>
       </c>
@@ -2692,13 +2711,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B191"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.7265625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.81640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>543</v>
       </c>
@@ -2706,7 +2725,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>553</v>
       </c>
@@ -2714,7 +2733,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>273</v>
       </c>
@@ -2722,7 +2741,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>83</v>
       </c>
@@ -2730,7 +2749,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>388</v>
       </c>
@@ -2738,7 +2757,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>85</v>
       </c>
@@ -2746,7 +2765,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>87</v>
       </c>
@@ -2754,7 +2773,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>89</v>
       </c>
@@ -2762,7 +2781,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>398</v>
       </c>
@@ -2770,7 +2789,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>335</v>
       </c>
@@ -2778,7 +2797,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>342</v>
       </c>
@@ -2786,7 +2805,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>91</v>
       </c>
@@ -2794,7 +2813,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>551</v>
       </c>
@@ -2802,7 +2821,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>115</v>
       </c>
@@ -2810,7 +2829,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>340</v>
       </c>
@@ -2818,7 +2837,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>565</v>
       </c>
@@ -2826,7 +2845,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>92</v>
       </c>
@@ -2834,7 +2853,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>338</v>
       </c>
@@ -2842,7 +2861,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>402</v>
       </c>
@@ -2850,7 +2869,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>247</v>
       </c>
@@ -2858,7 +2877,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>344</v>
       </c>
@@ -2866,7 +2885,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>183</v>
       </c>
@@ -2874,7 +2893,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>94</v>
       </c>
@@ -2882,7 +2901,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>392</v>
       </c>
@@ -2890,7 +2909,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>386</v>
       </c>
@@ -2898,7 +2917,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>245</v>
       </c>
@@ -2906,7 +2925,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>96</v>
       </c>
@@ -2914,7 +2933,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>311</v>
       </c>
@@ -2922,7 +2941,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>577</v>
       </c>
@@ -2930,7 +2949,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>251</v>
       </c>
@@ -2938,7 +2957,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>579</v>
       </c>
@@ -2946,7 +2965,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>321</v>
       </c>
@@ -2954,7 +2973,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>285</v>
       </c>
@@ -2962,7 +2981,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>325</v>
       </c>
@@ -2970,7 +2989,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>309</v>
       </c>
@@ -2978,7 +2997,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>370</v>
       </c>
@@ -2986,7 +3005,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>98</v>
       </c>
@@ -2994,7 +3013,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>313</v>
       </c>
@@ -3002,7 +3021,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>100</v>
       </c>
@@ -3010,7 +3029,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>101</v>
       </c>
@@ -3018,7 +3037,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>336</v>
       </c>
@@ -3026,7 +3045,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>103</v>
       </c>
@@ -3034,7 +3053,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>105</v>
       </c>
@@ -3042,7 +3061,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>107</v>
       </c>
@@ -3050,7 +3069,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>109</v>
       </c>
@@ -3058,7 +3077,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>111</v>
       </c>
@@ -3066,7 +3085,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>327</v>
       </c>
@@ -3074,7 +3093,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>277</v>
       </c>
@@ -3082,7 +3101,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>265</v>
       </c>
@@ -3090,7 +3109,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>267</v>
       </c>
@@ -3098,7 +3117,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>394</v>
       </c>
@@ -3106,7 +3125,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>113</v>
       </c>
@@ -3114,7 +3133,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>117</v>
       </c>
@@ -3122,7 +3141,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>118</v>
       </c>
@@ -3130,7 +3149,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>120</v>
       </c>
@@ -3138,7 +3157,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>122</v>
       </c>
@@ -3146,7 +3165,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>124</v>
       </c>
@@ -3154,7 +3173,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>126</v>
       </c>
@@ -3162,7 +3181,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>243</v>
       </c>
@@ -3170,7 +3189,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>128</v>
       </c>
@@ -3178,7 +3197,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>130</v>
       </c>
@@ -3186,7 +3205,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>132</v>
       </c>
@@ -3194,7 +3213,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>297</v>
       </c>
@@ -3202,7 +3221,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>134</v>
       </c>
@@ -3210,7 +3229,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>136</v>
       </c>
@@ -3218,7 +3237,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>382</v>
       </c>
@@ -3226,7 +3245,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>352</v>
       </c>
@@ -3234,7 +3253,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>305</v>
       </c>
@@ -3242,7 +3261,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>138</v>
       </c>
@@ -3250,7 +3269,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>366</v>
       </c>
@@ -3258,7 +3277,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>140</v>
       </c>
@@ -3266,7 +3285,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>141</v>
       </c>
@@ -3274,7 +3293,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>263</v>
       </c>
@@ -3282,7 +3301,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>143</v>
       </c>
@@ -3290,7 +3309,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>271</v>
       </c>
@@ -3298,7 +3317,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
         <v>400</v>
       </c>
@@ -3306,7 +3325,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>410</v>
       </c>
@@ -3314,7 +3333,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>307</v>
       </c>
@@ -3322,7 +3341,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>145</v>
       </c>
@@ -3330,7 +3349,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>261</v>
       </c>
@@ -3338,7 +3357,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>147</v>
       </c>
@@ -3346,7 +3365,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>255</v>
       </c>
@@ -3354,7 +3373,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>570</v>
       </c>
@@ -3362,7 +3381,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>561</v>
       </c>
@@ -3370,7 +3389,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>585</v>
       </c>
@@ -3378,7 +3397,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>291</v>
       </c>
@@ -3386,7 +3405,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
         <v>376</v>
       </c>
@@ -3394,7 +3413,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
         <v>549</v>
       </c>
@@ -3402,7 +3421,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>289</v>
       </c>
@@ -3410,7 +3429,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>149</v>
       </c>
@@ -3418,7 +3437,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>360</v>
       </c>
@@ -3426,7 +3445,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>563</v>
       </c>
@@ -3434,7 +3453,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>151</v>
       </c>
@@ -3442,7 +3461,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>592</v>
       </c>
@@ -3450,7 +3469,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>153</v>
       </c>
@@ -3458,7 +3477,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>155</v>
       </c>
@@ -3466,7 +3485,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>333</v>
       </c>
@@ -3474,7 +3493,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>157</v>
       </c>
@@ -3482,7 +3501,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>315</v>
       </c>
@@ -3490,7 +3509,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>249</v>
       </c>
@@ -3498,7 +3517,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
         <v>159</v>
       </c>
@@ -3506,7 +3525,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
         <v>161</v>
       </c>
@@ -3514,7 +3533,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>404</v>
       </c>
@@ -3522,7 +3541,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>239</v>
       </c>
@@ -3530,7 +3549,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>163</v>
       </c>
@@ -3538,7 +3557,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>165</v>
       </c>
@@ -3546,7 +3565,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>167</v>
       </c>
@@ -3554,7 +3573,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>544</v>
       </c>
@@ -3562,7 +3581,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>346</v>
       </c>
@@ -3570,7 +3589,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>372</v>
       </c>
@@ -3578,7 +3597,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
         <v>253</v>
       </c>
@@ -3586,7 +3605,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>169</v>
       </c>
@@ -3594,7 +3613,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
         <v>171</v>
       </c>
@@ -3602,7 +3621,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>358</v>
       </c>
@@ -3610,7 +3629,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
         <v>173</v>
       </c>
@@ -3618,7 +3637,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="6" t="s">
         <v>175</v>
       </c>
@@ -3626,7 +3645,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>177</v>
       </c>
@@ -3634,7 +3653,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>179</v>
       </c>
@@ -3642,7 +3661,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>575</v>
       </c>
@@ -3650,7 +3669,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="5" t="s">
         <v>181</v>
       </c>
@@ -3658,7 +3677,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
         <v>185</v>
       </c>
@@ -3666,7 +3685,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="6" t="s">
         <v>187</v>
       </c>
@@ -3674,7 +3693,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>189</v>
       </c>
@@ -3682,7 +3701,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>191</v>
       </c>
@@ -3690,7 +3709,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
         <v>257</v>
       </c>
@@ -3698,7 +3717,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
         <v>269</v>
       </c>
@@ -3706,7 +3725,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>384</v>
       </c>
@@ -3714,7 +3733,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
         <v>279</v>
       </c>
@@ -3722,7 +3741,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
         <v>295</v>
       </c>
@@ -3730,7 +3749,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>547</v>
       </c>
@@ -3738,7 +3757,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>193</v>
       </c>
@@ -3746,7 +3765,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="7" t="s">
         <v>396</v>
       </c>
@@ -3754,7 +3773,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
         <v>557</v>
       </c>
@@ -3762,7 +3781,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
         <v>195</v>
       </c>
@@ -3770,7 +3789,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
         <v>317</v>
       </c>
@@ -3778,7 +3797,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
         <v>197</v>
       </c>
@@ -3786,7 +3805,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
         <v>368</v>
       </c>
@@ -3794,7 +3813,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>331</v>
       </c>
@@ -3802,7 +3821,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>406</v>
       </c>
@@ -3810,7 +3829,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>199</v>
       </c>
@@ -3818,7 +3837,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="6" t="s">
         <v>287</v>
       </c>
@@ -3826,7 +3845,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
         <v>374</v>
       </c>
@@ -3834,7 +3853,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
         <v>201</v>
       </c>
@@ -3842,7 +3861,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
         <v>203</v>
       </c>
@@ -3850,7 +3869,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
         <v>205</v>
       </c>
@@ -3858,7 +3877,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="7" t="s">
         <v>364</v>
       </c>
@@ -3866,7 +3885,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
         <v>207</v>
       </c>
@@ -3874,7 +3893,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
         <v>356</v>
       </c>
@@ -3882,7 +3901,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>594</v>
       </c>
@@ -3890,7 +3909,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>299</v>
       </c>
@@ -3898,7 +3917,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
         <v>618</v>
       </c>
@@ -3906,7 +3925,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
         <v>567</v>
       </c>
@@ -3914,7 +3933,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="5" t="s">
         <v>209</v>
       </c>
@@ -3922,7 +3941,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
         <v>362</v>
       </c>
@@ -3930,7 +3949,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
         <v>354</v>
       </c>
@@ -3938,7 +3957,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
         <v>211</v>
       </c>
@@ -3946,7 +3965,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="7" t="s">
         <v>555</v>
       </c>
@@ -3954,7 +3973,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
         <v>301</v>
       </c>
@@ -3962,7 +3981,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
         <v>350</v>
       </c>
@@ -3970,7 +3989,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
         <v>283</v>
       </c>
@@ -3978,7 +3997,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
         <v>213</v>
       </c>
@@ -3986,7 +4005,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
         <v>215</v>
       </c>
@@ -3994,7 +4013,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" s="7" t="s">
         <v>303</v>
       </c>
@@ -4002,7 +4021,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
         <v>541</v>
       </c>
@@ -4010,7 +4029,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="7" t="s">
         <v>380</v>
       </c>
@@ -4018,7 +4037,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="7" t="s">
         <v>378</v>
       </c>
@@ -4026,7 +4045,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
         <v>217</v>
       </c>
@@ -4034,7 +4053,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
         <v>275</v>
       </c>
@@ -4042,7 +4061,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
         <v>408</v>
       </c>
@@ -4050,7 +4069,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
         <v>219</v>
       </c>
@@ -4058,7 +4077,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
         <v>221</v>
       </c>
@@ -4066,7 +4085,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
         <v>223</v>
       </c>
@@ -4074,7 +4093,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
         <v>225</v>
       </c>
@@ -4082,7 +4101,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
         <v>559</v>
       </c>
@@ -4090,7 +4109,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
         <v>583</v>
       </c>
@@ -4098,7 +4117,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
         <v>348</v>
       </c>
@@ -4106,7 +4125,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
         <v>227</v>
       </c>
@@ -4114,7 +4133,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" s="7" t="s">
         <v>319</v>
       </c>
@@ -4122,7 +4141,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>293</v>
       </c>
@@ -4130,7 +4149,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="5" t="s">
         <v>229</v>
       </c>
@@ -4138,7 +4157,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>329</v>
       </c>
@@ -4146,7 +4165,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="5" t="s">
         <v>241</v>
       </c>
@@ -4154,7 +4173,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" s="5" t="s">
         <v>231</v>
       </c>
@@ -4162,7 +4181,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" s="5" t="s">
         <v>233</v>
       </c>
@@ -4170,7 +4189,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
         <v>235</v>
       </c>
@@ -4178,7 +4197,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" s="5" t="s">
         <v>237</v>
       </c>
@@ -4186,7 +4205,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" s="7" t="s">
         <v>323</v>
       </c>
@@ -4194,7 +4213,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" s="5" t="s">
         <v>259</v>
       </c>
@@ -4202,7 +4221,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" s="7" t="s">
         <v>581</v>
       </c>
@@ -4210,7 +4229,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>390</v>
       </c>
@@ -4218,7 +4237,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" s="5" t="s">
         <v>281</v>
       </c>
@@ -4238,13 +4257,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="52.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.7265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>412</v>
       </c>
@@ -4252,7 +4271,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>414</v>
       </c>
@@ -4260,7 +4279,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>416</v>
       </c>
@@ -4268,7 +4287,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>418</v>
       </c>
@@ -4276,7 +4295,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>420</v>
       </c>
@@ -4284,7 +4303,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>422</v>
       </c>
@@ -4292,7 +4311,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>423</v>
       </c>
@@ -4300,7 +4319,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>425</v>
       </c>
@@ -4308,7 +4327,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>426</v>
       </c>
@@ -4316,7 +4335,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>428</v>
       </c>
@@ -4324,7 +4343,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>598</v>
       </c>
@@ -4342,13 +4361,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.81640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>430</v>
       </c>
@@ -4356,7 +4375,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>432</v>
       </c>
@@ -4364,7 +4383,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>434</v>
       </c>
@@ -4372,7 +4391,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>436</v>
       </c>
@@ -4380,7 +4399,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>438</v>
       </c>
@@ -4388,7 +4407,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>440</v>
       </c>
@@ -4396,7 +4415,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>442</v>
       </c>
@@ -4404,7 +4423,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>444</v>
       </c>
@@ -4412,7 +4431,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>446</v>
       </c>
@@ -4420,7 +4439,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>448</v>
       </c>
@@ -4428,7 +4447,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>449</v>
       </c>
@@ -4436,7 +4455,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>451</v>
       </c>
@@ -4444,7 +4463,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>453</v>
       </c>
@@ -4452,7 +4471,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>455</v>
       </c>
@@ -4460,7 +4479,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>457</v>
       </c>
@@ -4468,7 +4487,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>459</v>
       </c>
@@ -4476,7 +4495,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>461</v>
       </c>
@@ -4484,7 +4503,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>463</v>
       </c>
@@ -4492,7 +4511,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>465</v>
       </c>
@@ -4500,7 +4519,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>467</v>
       </c>
@@ -4508,7 +4527,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>469</v>
       </c>
@@ -4516,7 +4535,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>471</v>
       </c>
@@ -4524,7 +4543,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>473</v>
       </c>
@@ -4532,7 +4551,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>475</v>
       </c>
@@ -4540,7 +4559,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>477</v>
       </c>
@@ -4548,7 +4567,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>479</v>
       </c>
@@ -4556,7 +4575,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>481</v>
       </c>
@@ -4564,7 +4583,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>483</v>
       </c>
@@ -4572,7 +4591,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>485</v>
       </c>
@@ -4580,7 +4599,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>487</v>
       </c>
@@ -4588,7 +4607,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>489</v>
       </c>
@@ -4596,7 +4615,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>491</v>
       </c>
@@ -4604,7 +4623,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>493</v>
       </c>
@@ -4612,7 +4631,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>495</v>
       </c>
@@ -4620,7 +4639,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>390</v>
       </c>
@@ -4628,7 +4647,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>498</v>
       </c>
@@ -4636,7 +4655,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>500</v>
       </c>
@@ -4644,7 +4663,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>502</v>
       </c>
@@ -4652,7 +4671,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>504</v>
       </c>
@@ -4660,7 +4679,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>506</v>
       </c>
@@ -4668,7 +4687,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>508</v>
       </c>
@@ -4676,7 +4695,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>510</v>
       </c>
@@ -4684,7 +4703,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>512</v>
       </c>
@@ -4692,7 +4711,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>539</v>
       </c>
@@ -4700,7 +4719,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>600</v>
       </c>
@@ -4708,7 +4727,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>602</v>
       </c>
@@ -4716,7 +4735,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>604</v>
       </c>
@@ -4724,7 +4743,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>606</v>
       </c>
@@ -4732,7 +4751,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>608</v>
       </c>
@@ -4740,7 +4759,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>610</v>
       </c>
@@ -4748,7 +4767,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>624</v>
       </c>
@@ -4756,7 +4775,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>635</v>
       </c>
@@ -4772,14 +4791,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.7265625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>514</v>
       </c>
@@ -4787,7 +4806,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>515</v>
       </c>
@@ -4795,7 +4814,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>517</v>
       </c>
@@ -4803,7 +4822,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>518</v>
       </c>
@@ -4811,7 +4830,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>519</v>
       </c>
@@ -4819,7 +4838,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>520</v>
       </c>
@@ -4827,7 +4846,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>522</v>
       </c>
@@ -4835,7 +4854,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>524</v>
       </c>
@@ -4846,7 +4865,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>526</v>
       </c>
@@ -4854,12 +4873,12 @@
         <v>527</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>529</v>
       </c>
@@ -4867,7 +4886,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>531</v>
       </c>
@@ -4875,7 +4894,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>533</v>
       </c>
@@ -4883,7 +4902,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>535</v>
       </c>
@@ -4891,7 +4910,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>537</v>
       </c>
@@ -4899,12 +4918,12 @@
         <v>538</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>588</v>
       </c>
@@ -4912,7 +4931,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>590</v>
       </c>
@@ -4920,7 +4939,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>596</v>
       </c>
@@ -4928,7 +4947,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>612</v>
       </c>
@@ -4936,7 +4955,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>639</v>
       </c>
@@ -4944,7 +4963,32 @@
         <v>640</v>
       </c>
     </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="C24" s="11"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>645</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B24:C24"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9895FE27-BFBF-4146-887C-5CB060D3655A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5952857-37C8-414C-AAF5-3C873B530013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="697" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="652">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -2008,6 +2008,24 @@
   </si>
   <si>
     <t>совершенно другое развитие</t>
+  </si>
+  <si>
+    <t>привёло</t>
+  </si>
+  <si>
+    <t>привело</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чётко соответствовала истине, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">чётко соответствовало истине, </t>
+  </si>
+  <si>
+    <t>в помещении бань на Гребном канале</t>
+  </si>
+  <si>
+    <t>в помещении на Гребном канале</t>
   </si>
 </sst>
 </file>
@@ -2086,10 +2104,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2284,12 +2302,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2297,7 +2315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2305,7 +2323,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2313,7 +2331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2321,7 +2339,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2329,7 +2347,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2337,7 +2355,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2345,7 +2363,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2353,7 +2371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2361,7 +2379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2369,7 +2387,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2377,7 +2395,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -2385,7 +2403,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2393,7 +2411,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,7 +2419,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -2409,7 +2427,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2417,7 +2435,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2425,7 +2443,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2433,7 +2451,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2441,7 +2459,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -2449,7 +2467,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
@@ -2457,7 +2475,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -2465,7 +2483,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -2473,7 +2491,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>45</v>
       </c>
@@ -2481,7 +2499,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>47</v>
       </c>
@@ -2489,7 +2507,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>49</v>
       </c>
@@ -2497,7 +2515,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>51</v>
       </c>
@@ -2505,7 +2523,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>53</v>
       </c>
@@ -2513,7 +2531,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>55</v>
       </c>
@@ -2531,13 +2549,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.7265625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>57</v>
       </c>
@@ -2557,13 +2575,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.1796875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.7265625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>73</v>
       </c>
@@ -2571,7 +2589,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>69</v>
       </c>
@@ -2579,7 +2597,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>63</v>
       </c>
@@ -2587,7 +2605,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>71</v>
       </c>
@@ -2595,7 +2613,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>75</v>
       </c>
@@ -2603,7 +2621,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>573</v>
       </c>
@@ -2611,7 +2629,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>67</v>
       </c>
@@ -2619,7 +2637,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>571</v>
       </c>
@@ -2627,7 +2645,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>59</v>
       </c>
@@ -2635,7 +2653,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>65</v>
       </c>
@@ -2643,7 +2661,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>61</v>
       </c>
@@ -2651,7 +2669,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>79</v>
       </c>
@@ -2659,7 +2677,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>81</v>
       </c>
@@ -2667,7 +2685,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>623</v>
       </c>
@@ -2675,7 +2693,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>620</v>
       </c>
@@ -2683,7 +2701,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>77</v>
       </c>
@@ -2691,7 +2709,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>637</v>
       </c>
@@ -2711,13 +2729,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B191"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.7265625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.81640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>543</v>
       </c>
@@ -2725,7 +2743,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>553</v>
       </c>
@@ -2733,7 +2751,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>273</v>
       </c>
@@ -2741,7 +2759,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>83</v>
       </c>
@@ -2749,7 +2767,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>388</v>
       </c>
@@ -2757,7 +2775,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>85</v>
       </c>
@@ -2765,7 +2783,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>87</v>
       </c>
@@ -2773,7 +2791,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>89</v>
       </c>
@@ -2781,7 +2799,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>398</v>
       </c>
@@ -2789,7 +2807,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>335</v>
       </c>
@@ -2797,7 +2815,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>342</v>
       </c>
@@ -2805,7 +2823,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>91</v>
       </c>
@@ -2813,7 +2831,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>551</v>
       </c>
@@ -2821,7 +2839,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>115</v>
       </c>
@@ -2829,7 +2847,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>340</v>
       </c>
@@ -2837,7 +2855,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>565</v>
       </c>
@@ -2845,7 +2863,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>92</v>
       </c>
@@ -2853,7 +2871,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>338</v>
       </c>
@@ -2861,7 +2879,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>402</v>
       </c>
@@ -2869,7 +2887,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>247</v>
       </c>
@@ -2877,7 +2895,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>344</v>
       </c>
@@ -2885,7 +2903,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>183</v>
       </c>
@@ -2893,7 +2911,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>94</v>
       </c>
@@ -2901,7 +2919,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>392</v>
       </c>
@@ -2909,7 +2927,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>386</v>
       </c>
@@ -2917,7 +2935,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>245</v>
       </c>
@@ -2925,7 +2943,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>96</v>
       </c>
@@ -2933,7 +2951,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>311</v>
       </c>
@@ -2941,7 +2959,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>577</v>
       </c>
@@ -2949,7 +2967,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>251</v>
       </c>
@@ -2957,7 +2975,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>579</v>
       </c>
@@ -2965,7 +2983,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>321</v>
       </c>
@@ -2973,7 +2991,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>285</v>
       </c>
@@ -2981,7 +2999,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>325</v>
       </c>
@@ -2989,7 +3007,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>309</v>
       </c>
@@ -2997,7 +3015,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>370</v>
       </c>
@@ -3005,7 +3023,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>98</v>
       </c>
@@ -3013,7 +3031,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>313</v>
       </c>
@@ -3021,7 +3039,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>100</v>
       </c>
@@ -3029,7 +3047,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>101</v>
       </c>
@@ -3037,7 +3055,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>336</v>
       </c>
@@ -3045,7 +3063,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>103</v>
       </c>
@@ -3053,7 +3071,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>105</v>
       </c>
@@ -3061,7 +3079,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>107</v>
       </c>
@@ -3069,7 +3087,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>109</v>
       </c>
@@ -3077,7 +3095,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>111</v>
       </c>
@@ -3085,7 +3103,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>327</v>
       </c>
@@ -3093,7 +3111,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>277</v>
       </c>
@@ -3101,7 +3119,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>265</v>
       </c>
@@ -3109,7 +3127,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>267</v>
       </c>
@@ -3117,7 +3135,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>394</v>
       </c>
@@ -3125,7 +3143,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>113</v>
       </c>
@@ -3133,7 +3151,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>117</v>
       </c>
@@ -3141,7 +3159,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>118</v>
       </c>
@@ -3149,7 +3167,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>120</v>
       </c>
@@ -3157,7 +3175,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>122</v>
       </c>
@@ -3165,7 +3183,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>124</v>
       </c>
@@ -3173,7 +3191,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>126</v>
       </c>
@@ -3181,7 +3199,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>243</v>
       </c>
@@ -3189,7 +3207,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>128</v>
       </c>
@@ -3197,7 +3215,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>130</v>
       </c>
@@ -3205,7 +3223,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>132</v>
       </c>
@@ -3213,7 +3231,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>297</v>
       </c>
@@ -3221,7 +3239,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>134</v>
       </c>
@@ -3229,7 +3247,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>136</v>
       </c>
@@ -3237,7 +3255,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>382</v>
       </c>
@@ -3245,7 +3263,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>352</v>
       </c>
@@ -3253,7 +3271,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>305</v>
       </c>
@@ -3261,7 +3279,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>138</v>
       </c>
@@ -3269,7 +3287,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>366</v>
       </c>
@@ -3277,7 +3295,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>140</v>
       </c>
@@ -3285,7 +3303,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>141</v>
       </c>
@@ -3293,7 +3311,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>263</v>
       </c>
@@ -3301,7 +3319,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>143</v>
       </c>
@@ -3309,7 +3327,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>271</v>
       </c>
@@ -3317,7 +3335,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>400</v>
       </c>
@@ -3325,7 +3343,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>410</v>
       </c>
@@ -3333,7 +3351,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>307</v>
       </c>
@@ -3341,7 +3359,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>145</v>
       </c>
@@ -3349,7 +3367,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>261</v>
       </c>
@@ -3357,7 +3375,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>147</v>
       </c>
@@ -3365,7 +3383,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>255</v>
       </c>
@@ -3373,7 +3391,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>570</v>
       </c>
@@ -3381,7 +3399,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>561</v>
       </c>
@@ -3389,7 +3407,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>585</v>
       </c>
@@ -3397,7 +3415,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>291</v>
       </c>
@@ -3405,7 +3423,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>376</v>
       </c>
@@ -3413,7 +3431,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>549</v>
       </c>
@@ -3421,7 +3439,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>289</v>
       </c>
@@ -3429,7 +3447,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>149</v>
       </c>
@@ -3437,7 +3455,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>360</v>
       </c>
@@ -3445,7 +3463,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>563</v>
       </c>
@@ -3453,7 +3471,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>151</v>
       </c>
@@ -3461,7 +3479,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>592</v>
       </c>
@@ -3469,7 +3487,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>153</v>
       </c>
@@ -3477,7 +3495,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>155</v>
       </c>
@@ -3485,7 +3503,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>333</v>
       </c>
@@ -3493,7 +3511,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>157</v>
       </c>
@@ -3501,7 +3519,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>315</v>
       </c>
@@ -3509,7 +3527,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>249</v>
       </c>
@@ -3517,7 +3535,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>159</v>
       </c>
@@ -3525,7 +3543,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>161</v>
       </c>
@@ -3533,7 +3551,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>404</v>
       </c>
@@ -3541,7 +3559,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>239</v>
       </c>
@@ -3549,7 +3567,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>163</v>
       </c>
@@ -3557,7 +3575,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>165</v>
       </c>
@@ -3565,7 +3583,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
         <v>167</v>
       </c>
@@ -3573,7 +3591,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>544</v>
       </c>
@@ -3581,7 +3599,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>346</v>
       </c>
@@ -3589,7 +3607,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>372</v>
       </c>
@@ -3597,7 +3615,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
         <v>253</v>
       </c>
@@ -3605,7 +3623,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>169</v>
       </c>
@@ -3613,7 +3631,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>171</v>
       </c>
@@ -3621,7 +3639,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>358</v>
       </c>
@@ -3629,7 +3647,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>173</v>
       </c>
@@ -3637,7 +3655,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
         <v>175</v>
       </c>
@@ -3645,7 +3663,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>177</v>
       </c>
@@ -3653,7 +3671,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>179</v>
       </c>
@@ -3661,7 +3679,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>575</v>
       </c>
@@ -3669,7 +3687,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
         <v>181</v>
       </c>
@@ -3677,7 +3695,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>185</v>
       </c>
@@ -3685,7 +3703,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
         <v>187</v>
       </c>
@@ -3693,7 +3711,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>189</v>
       </c>
@@ -3701,7 +3719,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>191</v>
       </c>
@@ -3709,7 +3727,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>257</v>
       </c>
@@ -3717,7 +3735,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>269</v>
       </c>
@@ -3725,7 +3743,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>384</v>
       </c>
@@ -3733,7 +3751,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>279</v>
       </c>
@@ -3741,7 +3759,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>295</v>
       </c>
@@ -3749,7 +3767,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>547</v>
       </c>
@@ -3757,7 +3775,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>193</v>
       </c>
@@ -3765,7 +3783,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
         <v>396</v>
       </c>
@@ -3773,7 +3791,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
         <v>557</v>
       </c>
@@ -3781,7 +3799,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
         <v>195</v>
       </c>
@@ -3789,7 +3807,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
         <v>317</v>
       </c>
@@ -3797,7 +3815,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
         <v>197</v>
       </c>
@@ -3805,7 +3823,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>368</v>
       </c>
@@ -3813,7 +3831,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
         <v>331</v>
       </c>
@@ -3821,7 +3839,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="9" t="s">
         <v>406</v>
       </c>
@@ -3829,7 +3847,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
         <v>199</v>
       </c>
@@ -3837,7 +3855,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>287</v>
       </c>
@@ -3845,7 +3863,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
         <v>374</v>
       </c>
@@ -3853,7 +3871,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
         <v>201</v>
       </c>
@@ -3861,7 +3879,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>203</v>
       </c>
@@ -3869,7 +3887,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
         <v>205</v>
       </c>
@@ -3877,7 +3895,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
         <v>364</v>
       </c>
@@ -3885,7 +3903,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>207</v>
       </c>
@@ -3893,7 +3911,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>356</v>
       </c>
@@ -3901,7 +3919,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
         <v>594</v>
       </c>
@@ -3909,7 +3927,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
         <v>299</v>
       </c>
@@ -3917,7 +3935,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>618</v>
       </c>
@@ -3925,7 +3943,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>567</v>
       </c>
@@ -3933,7 +3951,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
         <v>209</v>
       </c>
@@ -3941,7 +3959,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>362</v>
       </c>
@@ -3949,7 +3967,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>354</v>
       </c>
@@ -3957,7 +3975,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
         <v>211</v>
       </c>
@@ -3965,7 +3983,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>555</v>
       </c>
@@ -3973,7 +3991,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>301</v>
       </c>
@@ -3981,7 +3999,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>350</v>
       </c>
@@ -3989,7 +4007,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
         <v>283</v>
       </c>
@@ -3997,7 +4015,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
         <v>213</v>
       </c>
@@ -4005,7 +4023,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
         <v>215</v>
       </c>
@@ -4013,7 +4031,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>303</v>
       </c>
@@ -4021,7 +4039,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>541</v>
       </c>
@@ -4029,7 +4047,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
         <v>380</v>
       </c>
@@ -4037,7 +4055,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>378</v>
       </c>
@@ -4045,7 +4063,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
         <v>217</v>
       </c>
@@ -4053,7 +4071,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
         <v>275</v>
       </c>
@@ -4061,7 +4079,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
         <v>408</v>
       </c>
@@ -4069,7 +4087,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
         <v>219</v>
       </c>
@@ -4077,7 +4095,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
         <v>221</v>
       </c>
@@ -4085,7 +4103,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
         <v>223</v>
       </c>
@@ -4093,7 +4111,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
         <v>225</v>
       </c>
@@ -4101,7 +4119,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>559</v>
       </c>
@@ -4109,7 +4127,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>583</v>
       </c>
@@ -4117,7 +4135,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>348</v>
       </c>
@@ -4125,7 +4143,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
         <v>227</v>
       </c>
@@ -4133,7 +4151,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>319</v>
       </c>
@@ -4141,7 +4159,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>293</v>
       </c>
@@ -4149,7 +4167,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
         <v>229</v>
       </c>
@@ -4157,7 +4175,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>329</v>
       </c>
@@ -4165,7 +4183,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
         <v>241</v>
       </c>
@@ -4173,7 +4191,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
         <v>231</v>
       </c>
@@ -4181,7 +4199,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
         <v>233</v>
       </c>
@@ -4189,7 +4207,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
         <v>235</v>
       </c>
@@ -4197,7 +4215,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
         <v>237</v>
       </c>
@@ -4205,7 +4223,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
         <v>323</v>
       </c>
@@ -4213,7 +4231,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
         <v>259</v>
       </c>
@@ -4221,7 +4239,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>581</v>
       </c>
@@ -4229,7 +4247,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>390</v>
       </c>
@@ -4237,7 +4255,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="s">
         <v>281</v>
       </c>
@@ -4257,13 +4275,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.26953125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.7265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="52.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>412</v>
       </c>
@@ -4271,7 +4289,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>414</v>
       </c>
@@ -4279,7 +4297,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>416</v>
       </c>
@@ -4287,7 +4305,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>418</v>
       </c>
@@ -4295,7 +4313,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>420</v>
       </c>
@@ -4303,7 +4321,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>422</v>
       </c>
@@ -4311,7 +4329,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>423</v>
       </c>
@@ -4319,7 +4337,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="39" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>425</v>
       </c>
@@ -4327,7 +4345,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="39" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>426</v>
       </c>
@@ -4335,7 +4353,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>428</v>
       </c>
@@ -4343,7 +4361,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>598</v>
       </c>
@@ -4360,14 +4378,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B54"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.7265625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>430</v>
       </c>
@@ -4375,7 +4393,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>432</v>
       </c>
@@ -4383,7 +4401,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>434</v>
       </c>
@@ -4391,7 +4409,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>436</v>
       </c>
@@ -4399,7 +4417,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>438</v>
       </c>
@@ -4407,7 +4425,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>440</v>
       </c>
@@ -4415,7 +4433,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>442</v>
       </c>
@@ -4423,7 +4441,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>444</v>
       </c>
@@ -4431,7 +4449,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>446</v>
       </c>
@@ -4439,7 +4457,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>448</v>
       </c>
@@ -4447,7 +4465,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>449</v>
       </c>
@@ -4455,7 +4473,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>451</v>
       </c>
@@ -4463,7 +4481,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>453</v>
       </c>
@@ -4471,7 +4489,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>455</v>
       </c>
@@ -4479,7 +4497,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>457</v>
       </c>
@@ -4487,7 +4505,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>459</v>
       </c>
@@ -4495,7 +4513,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>461</v>
       </c>
@@ -4503,7 +4521,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>463</v>
       </c>
@@ -4511,7 +4529,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>465</v>
       </c>
@@ -4519,7 +4537,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>467</v>
       </c>
@@ -4527,7 +4545,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>469</v>
       </c>
@@ -4535,7 +4553,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>471</v>
       </c>
@@ -4543,7 +4561,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>473</v>
       </c>
@@ -4551,7 +4569,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>475</v>
       </c>
@@ -4559,7 +4577,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>477</v>
       </c>
@@ -4567,7 +4585,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>479</v>
       </c>
@@ -4575,7 +4593,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>481</v>
       </c>
@@ -4583,7 +4601,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>483</v>
       </c>
@@ -4591,7 +4609,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>485</v>
       </c>
@@ -4599,7 +4617,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>487</v>
       </c>
@@ -4607,7 +4625,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>489</v>
       </c>
@@ -4615,7 +4633,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>491</v>
       </c>
@@ -4623,7 +4641,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>493</v>
       </c>
@@ -4631,7 +4649,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>495</v>
       </c>
@@ -4639,7 +4657,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>390</v>
       </c>
@@ -4647,7 +4665,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>498</v>
       </c>
@@ -4655,7 +4673,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>500</v>
       </c>
@@ -4663,7 +4681,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>502</v>
       </c>
@@ -4671,7 +4689,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>504</v>
       </c>
@@ -4679,7 +4697,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>506</v>
       </c>
@@ -4687,7 +4705,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>508</v>
       </c>
@@ -4695,7 +4713,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>510</v>
       </c>
@@ -4703,7 +4721,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>512</v>
       </c>
@@ -4711,7 +4729,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>539</v>
       </c>
@@ -4719,7 +4737,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>600</v>
       </c>
@@ -4727,7 +4745,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>602</v>
       </c>
@@ -4735,7 +4753,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>604</v>
       </c>
@@ -4743,7 +4761,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>606</v>
       </c>
@@ -4751,7 +4769,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>608</v>
       </c>
@@ -4759,7 +4777,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>610</v>
       </c>
@@ -4767,7 +4785,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>624</v>
       </c>
@@ -4775,12 +4793,28 @@
         <v>625</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>635</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>636</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>651</v>
       </c>
     </row>
   </sheetData>
@@ -4791,14 +4825,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.7265625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>514</v>
       </c>
@@ -4806,7 +4840,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>515</v>
       </c>
@@ -4814,7 +4848,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>517</v>
       </c>
@@ -4822,7 +4856,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>518</v>
       </c>
@@ -4830,7 +4864,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>519</v>
       </c>
@@ -4838,7 +4872,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>520</v>
       </c>
@@ -4846,7 +4880,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>522</v>
       </c>
@@ -4854,7 +4888,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>524</v>
       </c>
@@ -4865,7 +4899,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>526</v>
       </c>
@@ -4873,12 +4907,12 @@
         <v>527</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>529</v>
       </c>
@@ -4886,7 +4920,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>531</v>
       </c>
@@ -4894,7 +4928,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>533</v>
       </c>
@@ -4902,7 +4936,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>535</v>
       </c>
@@ -4910,7 +4944,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>537</v>
       </c>
@@ -4918,12 +4952,12 @@
         <v>538</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>588</v>
       </c>
@@ -4931,7 +4965,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>590</v>
       </c>
@@ -4939,7 +4973,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>596</v>
       </c>
@@ -4947,7 +4981,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>612</v>
       </c>
@@ -4955,7 +4989,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>639</v>
       </c>
@@ -4963,26 +4997,34 @@
         <v>640</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B24" s="11" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
         <v>641</v>
       </c>
-      <c r="C24" s="11"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C24" s="12"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>642</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="11" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="11" t="s">
         <v>645</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>647</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5952857-37C8-414C-AAF5-3C873B530013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BF9FB0-3466-45FC-8D39-679D60BB886D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="697" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="ошибки" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">неизменные!$A$1:$B$191</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">неизменные_длинные!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные_важные!$A$1:$B$22</definedName>
   </definedNames>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="654">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -655,9 +656,6 @@
   </si>
   <si>
     <t>психики – она архинормальна, архистабильна, хотя и вся расшатана</t>
-  </si>
-  <si>
-    <t>разум – она крайне обычен, крайне безотказен, хотя и весь расшатан</t>
   </si>
   <si>
     <t>пять номеров,</t>
@@ -2026,6 +2024,15 @@
   </si>
   <si>
     <t>в помещении на Гребном канале</t>
+  </si>
+  <si>
+    <t>разум – он крайне обычен, крайне безотказен, хотя и весь расшатан</t>
+  </si>
+  <si>
+    <t>с арсеналом и мадам</t>
+  </si>
+  <si>
+    <t>со складом и замужней женщиной</t>
   </si>
 </sst>
 </file>
@@ -2302,12 +2309,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="48.140625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2315,7 +2322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2323,7 +2330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2331,7 +2338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2339,7 +2346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2347,7 +2354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2355,7 +2362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2363,7 +2370,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2371,7 +2378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2379,7 +2386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2387,7 +2394,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2395,7 +2402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -2403,7 +2410,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2411,7 +2418,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2419,7 +2426,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -2427,7 +2434,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2435,7 +2442,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2443,7 +2450,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2451,15 +2458,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -2467,7 +2474,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
@@ -2475,7 +2482,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -2483,7 +2490,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -2491,7 +2498,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>45</v>
       </c>
@@ -2499,7 +2506,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>47</v>
       </c>
@@ -2507,7 +2514,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>49</v>
       </c>
@@ -2515,7 +2522,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>51</v>
       </c>
@@ -2523,7 +2530,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>53</v>
       </c>
@@ -2531,7 +2538,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>55</v>
       </c>
@@ -2549,13 +2556,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="44.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="44.7265625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>57</v>
       </c>
@@ -2575,13 +2582,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>73</v>
       </c>
@@ -2589,7 +2596,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>69</v>
       </c>
@@ -2597,7 +2604,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>63</v>
       </c>
@@ -2605,7 +2612,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>71</v>
       </c>
@@ -2613,7 +2620,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>75</v>
       </c>
@@ -2621,15 +2628,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>67</v>
       </c>
@@ -2637,15 +2644,15 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>59</v>
       </c>
@@ -2653,7 +2660,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>65</v>
       </c>
@@ -2661,7 +2668,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>61</v>
       </c>
@@ -2669,7 +2676,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>79</v>
       </c>
@@ -2677,7 +2684,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>81</v>
       </c>
@@ -2685,23 +2692,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>77</v>
       </c>
@@ -2709,12 +2716,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>637</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -2728,38 +2735,38 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B191"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B166"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.7265625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.81640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>83</v>
       </c>
@@ -2767,15 +2774,15 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>85</v>
       </c>
@@ -2783,7 +2790,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>87</v>
       </c>
@@ -2791,7 +2798,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>89</v>
       </c>
@@ -2799,47 +2806,47 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="26.25" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>91</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>115</v>
       </c>
@@ -2847,23 +2854,23 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>92</v>
       </c>
@@ -2871,39 +2878,39 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>183</v>
       </c>
@@ -2911,7 +2918,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>94</v>
       </c>
@@ -2919,31 +2926,31 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>96</v>
       </c>
@@ -2951,79 +2958,79 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="B29" s="7" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="B31" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>98</v>
       </c>
@@ -3031,23 +3038,23 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>101</v>
       </c>
@@ -3055,15 +3062,15 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>103</v>
       </c>
@@ -3071,7 +3078,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>105</v>
       </c>
@@ -3079,7 +3086,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>107</v>
       </c>
@@ -3087,7 +3094,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>109</v>
       </c>
@@ -3095,7 +3102,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>111</v>
       </c>
@@ -3103,47 +3110,47 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B49" s="5" t="s">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="5" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+      <c r="B50" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>113</v>
       </c>
@@ -3151,15 +3158,15 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>117</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>118</v>
       </c>
@@ -3167,7 +3174,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>120</v>
       </c>
@@ -3175,7 +3182,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>122</v>
       </c>
@@ -3183,7 +3190,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>124</v>
       </c>
@@ -3191,7 +3198,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>126</v>
       </c>
@@ -3199,15 +3206,15 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>128</v>
       </c>
@@ -3215,7 +3222,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>130</v>
       </c>
@@ -3223,7 +3230,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>132</v>
       </c>
@@ -3231,15 +3238,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>134</v>
       </c>
@@ -3247,7 +3254,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>136</v>
       </c>
@@ -3255,1017 +3262,818 @@
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B66" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="B66" s="7" t="s">
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A92" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" s="7" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="B67" s="7" t="s">
+      <c r="B120" s="7" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" s="7" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B86" s="5" t="s">
+      <c r="B138" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" s="1" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
-        <v>592</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B104" s="5" t="s">
+      <c r="B156" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159" s="5" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B110" s="7" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B125" s="6" t="s">
+      <c r="B159" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A162" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A163" s="5" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B128" s="5" t="s">
+      <c r="B163" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A164" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A166" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="7" t="s">
-        <v>594</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B159" s="7" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="B163" s="7" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="B165" s="7" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="B166" s="7" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A167" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A168" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A169" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B169" s="7" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A170" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A172" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A173" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A174" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A175" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="B175" s="7" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A176" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="B176" s="7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A178" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B181" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A184" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A185" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A186" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A187" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="B187" s="7" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" s="7" t="s">
-        <v>581</v>
-      </c>
-      <c r="B189" s="7" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" s="5" t="s">
+      <c r="B166" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B191" s="5" t="s">
-        <v>282</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B192">
-    <sortCondition ref="A1:A192"/>
+  <autoFilter ref="A1:B191" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B191">
+    <sortCondition ref="A1:A191"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4275,98 +4083,98 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="52.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.7265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="39" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="39" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -4378,443 +4186,651 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B54"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B80"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.81640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B23" s="1" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B24" s="1" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B25" s="1" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B26" s="1" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B27" s="1" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B28" s="1" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B29" s="1" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B30" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="B31" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="B31" s="4" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="B32" s="4" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="7" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="B33" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="B33" s="7" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B34" s="1" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B36" s="1" t="s">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B37" s="1" t="s">
+    </row>
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="B38" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="B38" s="6" t="s">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="B39" s="4" t="s">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="B40" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="B40" s="8" t="s">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="B41" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B41" s="1" t="s">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="B42" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="B42" s="4" t="s">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="9" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
+      <c r="B43" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="B45" s="10" t="s">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B46" s="1" t="s">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="B47" s="1" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="10" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
+      <c r="B48" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="B48" s="10" t="s">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B49" s="1" t="s">
+    </row>
+    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B53" s="1" t="s">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>651</v>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -4826,205 +4842,205 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.7265625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="C1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" s="5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="B6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="B7" s="5" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="C8" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="B9" s="5" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="B11" s="7" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="B12" s="7" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="B13" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="B13" s="7" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="B18" s="5" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="B22" s="5" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" s="12" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
+      <c r="C24" s="12"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
         <v>641</v>
       </c>
-      <c r="C24" s="12"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="B25" s="11" t="s">
         <v>642</v>
       </c>
-      <c r="B25" s="11" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="B26" s="11" t="s">
         <v>644</v>
       </c>
-      <c r="B26" s="11" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="B27" s="11" t="s">
         <v>646</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>647</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BF9FB0-3466-45FC-8D39-679D60BB886D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FE663B-A83F-438B-AA20-D5A1092B5EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="697" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
-    <sheet name="простые" sheetId="2" r:id="rId2"/>
-    <sheet name="Составные" sheetId="3" r:id="rId3"/>
+    <sheet name="Составные" sheetId="3" r:id="rId2"/>
+    <sheet name="простые" sheetId="8" r:id="rId3"/>
     <sheet name="неизменные" sheetId="4" r:id="rId4"/>
     <sheet name="неизменные_длинные" sheetId="5" r:id="rId5"/>
     <sheet name="неизменные_короткие" sheetId="6" r:id="rId6"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="660">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -461,9 +461,6 @@
   </si>
   <si>
     <t>Комитетовский банк</t>
-  </si>
-  <si>
-    <t>денежное хранилище Совета</t>
   </si>
   <si>
     <t>кучей номеров и</t>
@@ -2033,6 +2030,27 @@
   </si>
   <si>
     <t>со складом и замужней женщиной</t>
+  </si>
+  <si>
+    <t>в центральном ресторане города, находящегося</t>
+  </si>
+  <si>
+    <t>в главной городской харчёвне для дворян, находящейся</t>
+  </si>
+  <si>
+    <t>на данного моего паспорта</t>
+  </si>
+  <si>
+    <t>на данные моего паспорта</t>
+  </si>
+  <si>
+    <t>достаточная на месяц сумма, думаю, помогла</t>
+  </si>
+  <si>
+    <t>достаточное на месяц количесво денежных средств, думаю, помогло</t>
+  </si>
+  <si>
+    <t>денежное хранилище под покровительством КГБ</t>
   </si>
 </sst>
 </file>
@@ -2309,12 +2327,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2322,7 +2340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2330,7 +2348,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2338,7 +2356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2346,7 +2364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2354,7 +2372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2362,7 +2380,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2370,7 +2388,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2378,7 +2396,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2386,7 +2404,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2394,7 +2412,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2402,7 +2420,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -2410,7 +2428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2418,7 +2436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -2426,7 +2444,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -2434,7 +2452,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -2442,7 +2460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
@@ -2450,7 +2468,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2458,15 +2476,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -2474,7 +2492,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
@@ -2482,7 +2500,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -2490,7 +2508,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -2498,7 +2516,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>45</v>
       </c>
@@ -2506,7 +2524,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>47</v>
       </c>
@@ -2514,7 +2532,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>49</v>
       </c>
@@ -2522,7 +2540,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>51</v>
       </c>
@@ -2530,7 +2548,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>53</v>
       </c>
@@ -2538,7 +2556,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>55</v>
       </c>
@@ -2554,25 +2572,137 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.7265625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>58</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>636</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B1">
-    <sortCondition ref="A1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B17">
+    <sortCondition ref="A1:A17"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2580,193 +2710,57 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="26.1796875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.7265625" style="5" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76C830F-D298-443C-B559-8038A360E6EC}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>637</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B18">
-    <sortCondition ref="A1:A18"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B166"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B169"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.7265625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.81640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>83</v>
       </c>
@@ -2774,15 +2768,15 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>85</v>
       </c>
@@ -2790,7 +2784,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>87</v>
       </c>
@@ -2798,7 +2792,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>89</v>
       </c>
@@ -2806,47 +2800,47 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>91</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>550</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>115</v>
       </c>
@@ -2854,23 +2848,23 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>564</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>92</v>
       </c>
@@ -2878,47 +2872,47 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>94</v>
       </c>
@@ -2926,31 +2920,31 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>96</v>
       </c>
@@ -2958,79 +2952,79 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="B29" s="7" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="7" t="s">
+      <c r="B31" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>98</v>
       </c>
@@ -3038,23 +3032,23 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>101</v>
       </c>
@@ -3062,15 +3056,15 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>103</v>
       </c>
@@ -3078,7 +3072,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>105</v>
       </c>
@@ -3086,7 +3080,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>107</v>
       </c>
@@ -3094,7 +3088,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>109</v>
       </c>
@@ -3102,7 +3096,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>111</v>
       </c>
@@ -3110,47 +3104,47 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B49" s="5" t="s">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="5" t="s">
+      <c r="B50" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>113</v>
       </c>
@@ -3158,15 +3152,15 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>117</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>118</v>
       </c>
@@ -3174,7 +3168,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>120</v>
       </c>
@@ -3182,7 +3176,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>122</v>
       </c>
@@ -3190,7 +3184,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>124</v>
       </c>
@@ -3198,7 +3192,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>126</v>
       </c>
@@ -3206,15 +3200,15 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>128</v>
       </c>
@@ -3222,7 +3216,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>130</v>
       </c>
@@ -3230,7 +3224,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>132</v>
       </c>
@@ -3238,15 +3232,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>134</v>
       </c>
@@ -3254,820 +3248,844 @@
         <v>135</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>136</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="B66" s="7" t="s">
+      <c r="B68" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="7" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="B67" s="7" t="s">
+      <c r="B120" s="7" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="7" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B85" s="5" t="s">
+      <c r="B138" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A92" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" s="7" t="s">
-        <v>591</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A103" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B103" s="5" t="s">
+      <c r="B156" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="5" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A105" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A114" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A115" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A116" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A117" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A119" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="B119" s="6" t="s">
+      <c r="B159" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="5" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A121" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B121" s="5" t="s">
+      <c r="B163" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="5" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A122" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A123" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A124" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A125" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A126" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A127" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A128" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A130" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A131" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A132" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A133" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A134" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A135" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A136" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A137" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A138" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A139" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A140" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A141" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A142" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A143" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="B143" s="7" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A144" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A145" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A146" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A147" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A148" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A149" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A150" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A151" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A152" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A153" s="7" t="s">
-        <v>582</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A154" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A155" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A156" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A157" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A158" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A159" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A160" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A161" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A162" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A163" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A164" s="7" t="s">
-        <v>580</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A165" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A166" s="5" t="s">
+      <c r="B166" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B166" s="5" t="s">
-        <v>281</v>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="B168" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -4083,98 +4101,98 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.26953125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.7265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="52.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="39" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="39" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>597</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -4186,651 +4204,659 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B80"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B83"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.7265625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B23" s="1" t="s">
+    </row>
+    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B24" s="1" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B25" s="1" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B26" s="1" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B27" s="1" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B28" s="1" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B29" s="1" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B30" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
+      <c r="B31" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="B31" s="4" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="B32" s="4" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
+      <c r="B33" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="B33" s="7" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B34" s="1" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B36" s="1" t="s">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B37" s="1" t="s">
+    </row>
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
+      <c r="B38" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="B38" s="6" t="s">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="B39" s="4" t="s">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
+      <c r="B40" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="B40" s="8" t="s">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
+      <c r="B41" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B41" s="1" t="s">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
+      <c r="B42" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="B42" s="4" t="s">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="9" t="s">
+      <c r="B43" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>599</v>
       </c>
-      <c r="B45" s="10" t="s">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B46" s="1" t="s">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B47" s="1" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="10" t="s">
+      <c r="B48" s="10" t="s">
         <v>605</v>
       </c>
-      <c r="B48" s="10" t="s">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B49" s="1" t="s">
+    </row>
+    <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B53" s="1" t="s">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B56" s="5" t="s">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B57" s="5" t="s">
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B59" s="5" t="s">
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="7" t="s">
-        <v>593</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="B63" s="7" t="s">
+      <c r="B65" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>305</v>
+      <c r="B83" s="5" t="s">
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -4841,206 +4867,214 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.7265625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="C1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" s="5" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="B6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B7" s="5" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="C8" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="B9" s="5" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>528</v>
       </c>
-      <c r="B11" s="7" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="B12" s="7" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+      <c r="B13" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="B13" s="7" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="B18" s="5" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="B22" s="5" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B24" s="12" t="s">
+      <c r="C24" s="12"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>640</v>
       </c>
-      <c r="C24" s="12"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
+      <c r="B25" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="B25" s="11" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
+      <c r="B26" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="B26" s="11" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="7" t="s">
+      <c r="B27" s="11" t="s">
         <v>645</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>646</v>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>656</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FE663B-A83F-438B-AA20-D5A1092B5EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90866FAE-1253-4A5D-92BB-A18D2EF7488A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="697" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -127,9 +127,6 @@
     <t>суммой фактического кредита</t>
   </si>
   <si>
-    <t>количеством денежных средств взятого долга в рост</t>
-  </si>
-  <si>
     <t>мягкому, но шумовому фону</t>
   </si>
   <si>
@@ -2051,6 +2048,9 @@
   </si>
   <si>
     <t>денежное хранилище под покровительством КГБ</t>
+  </si>
+  <si>
+    <t>количества денежных средств для взятого долга в рост</t>
   </si>
 </sst>
 </file>
@@ -2327,12 +2327,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="48.140625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -2428,140 +2428,140 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="1" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="1" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="4" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="4" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="B27" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="1" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="B28" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="4" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="B29" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2574,130 +2574,130 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="B9" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>635</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -2712,14 +2712,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76C830F-D298-443C-B559-8038A360E6EC}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2730,1362 +2730,1362 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B169"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="55.85546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="48.7265625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.81640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A92" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B107" s="7" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" s="7" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="B123" s="7" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" s="7" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="B140" s="7" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" s="5" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="B146" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A162" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A163" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A164" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="B121" s="5" t="s">
+      <c r="B165" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A166" s="5" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="B143" s="7" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" s="7" t="s">
-        <v>581</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A166" s="5" t="s">
+      <c r="B166" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B166" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B167" s="5" t="s">
         <v>653</v>
       </c>
-      <c r="B167" s="5" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="B168" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="B168" s="10" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -4101,98 +4101,98 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="52.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.7265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="39" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="39" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -4205,658 +4205,658 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B83"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.81640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B23" s="1" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B24" s="1" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B25" s="1" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B26" s="1" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B27" s="1" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B28" s="1" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B29" s="1" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B30" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="B31" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="B31" s="4" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="B32" s="4" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="7" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="B33" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="B33" s="7" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B34" s="1" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B36" s="1" t="s">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B37" s="1" t="s">
+    </row>
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="B38" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="B38" s="6" t="s">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="B39" s="4" t="s">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="B40" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="B40" s="8" t="s">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="B41" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B41" s="1" t="s">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="B42" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B42" s="4" t="s">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="9" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
+      <c r="B43" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="B45" s="10" t="s">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B46" s="1" t="s">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B47" s="1" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="10" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
+      <c r="B48" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="B48" s="10" t="s">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B49" s="1" t="s">
+    </row>
+    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B53" s="1" t="s">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B56" s="5" t="s">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="5" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B57" s="5" t="s">
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="5" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B59" s="5" t="s">
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="5" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>592</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="B63" s="7" t="s">
+      <c r="B65" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="5" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
+      <c r="B83" s="5" t="s">
         <v>618</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -4868,213 +4868,213 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.7265625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" s="5" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="B6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="B7" s="5" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="C8" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="B9" s="5" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="B11" s="7" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="B12" s="7" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="B13" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="B13" s="7" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="B18" s="5" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="B22" s="5" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" s="12" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
+      <c r="C24" s="12"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
         <v>639</v>
       </c>
-      <c r="C24" s="12"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="B25" s="11" t="s">
         <v>640</v>
       </c>
-      <c r="B25" s="11" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="B26" s="11" t="s">
         <v>642</v>
       </c>
-      <c r="B26" s="11" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="B27" s="11" t="s">
         <v>644</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>655</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>656</v>
       </c>
     </row>
   </sheetData>
